--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -54,7 +54,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 16, 2026</t>
+    <t>March 17, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -261,7 +261,7 @@
     <t>Total PUBLIC FUNDING</t>
   </si>
   <si>
-    <t>GRANTS, CONTRIBUTIONS &amp; OTHER SUPPORT</t>
+    <t>PHILANTHROPY</t>
   </si>
   <si>
     <t>CSP Startup Grant</t>
@@ -270,7 +270,7 @@
     <t>Annual Fundraising</t>
   </si>
   <si>
-    <t>Total GRANTS, CONTRIBUTIONS &amp; OTHER SUPPORT</t>
+    <t>Total PHILANTHROPY</t>
   </si>
   <si>
     <t>OTHER REVENUE</t>
@@ -565,7 +565,7 @@
     </font>
     <font>
       <color rgb="FF94A3B8"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -609,7 +609,7 @@
     <font>
       <i/>
       <color rgb="FF9CA3AF"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -633,7 +633,7 @@
     <font>
       <i/>
       <color rgb="FF888888"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1574,25 +1574,25 @@
       <c r="A11" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="27" t="str">
         <f>SUM(B9:B10)</f>
-        <v>130000</v>
-      </c>
-      <c r="C11" s="27">
+        <v>0</v>
+      </c>
+      <c r="C11" s="27" t="str">
         <f>SUM(C9:C10)</f>
-        <v>115000</v>
-      </c>
-      <c r="D11" s="27">
+        <v>0</v>
+      </c>
+      <c r="D11" s="27" t="str">
         <f>SUM(D9:D10)</f>
-        <v>100000</v>
-      </c>
-      <c r="E11" s="27">
+        <v>0</v>
+      </c>
+      <c r="E11" s="27" t="str">
         <f>SUM(E9:E10)</f>
-        <v>60000</v>
-      </c>
-      <c r="F11" s="27">
+        <v>0</v>
+      </c>
+      <c r="F11" s="27" t="str">
         <f>SUM(F9:F10)</f>
-        <v>70000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -102,7 +102,7 @@
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Assumptions</t>
+    <t>SchoolStack Budget - Assumptions</t>
   </si>
   <si>
     <t>SCHOOL INFORMATION</t>
@@ -285,7 +285,7 @@
     <t>TOTAL NET REVENUE</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Staffing &amp; Personnel</t>
+    <t>SchoolStack Budget - Staffing &amp; Personnel</t>
   </si>
   <si>
     <t>Role</t>
@@ -501,7 +501,7 @@
     <t>Enrollment Growth %</t>
   </si>
   <si>
-    <t>—</t>
+    <t>-</t>
   </si>
   <si>
     <t>KEY RATIOS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -54,7 +54,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 17, 2026</t>
+    <t>March 18, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -54,7 +54,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 18, 2026</t>
+    <t>March 26, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -543,7 +543,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -619,6 +619,16 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -643,7 +653,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -662,6 +672,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
@@ -671,7 +686,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -704,6 +719,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF93C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
       </left>
@@ -722,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -743,11 +767,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -757,16 +782,17 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="18" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1336,7 +1362,7 @@
       <c r="A32" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="24" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1366,22 +1392,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1389,23 +1415,23 @@
       <c r="A2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="26">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="26">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="26">
         <f>Assumptions!B25</f>
         <v>375</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="26">
         <f>Assumptions!B26</f>
         <v>400</v>
       </c>
@@ -1424,23 +1450,23 @@
       <c r="A4" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>9500*Assumptions!B22</f>
         <v>1140000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>9690*Assumptions!B23</f>
         <v>1938000</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>9884*Assumptions!B24</f>
         <v>2965200</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>10081*Assumptions!B25</f>
         <v>3780375</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>10283*Assumptions!B26</f>
         <v>4113200</v>
       </c>
@@ -1449,23 +1475,23 @@
       <c r="A5" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>800*Assumptions!B22</f>
         <v>96000</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>816*Assumptions!B23</f>
         <v>163200</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>832*Assumptions!B24</f>
         <v>249600</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>849*Assumptions!B25</f>
         <v>318375</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>866*Assumptions!B26</f>
         <v>346400</v>
       </c>
@@ -1474,23 +1500,23 @@
       <c r="A6" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <f>1200*Assumptions!B22</f>
         <v>144000</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>1224*Assumptions!B23</f>
         <v>244800</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>1248*Assumptions!B24</f>
         <v>374400</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>1273*Assumptions!B25</f>
         <v>477375</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>1299*Assumptions!B26</f>
         <v>519600</v>
       </c>
@@ -1499,23 +1525,23 @@
       <c r="A7" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>SUM(B4:B6)</f>
         <v>1380000</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>SUM(C4:C6)</f>
         <v>2346000</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>SUM(D4:D6)</f>
         <v>3589200</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <f>SUM(E4:E6)</f>
         <v>4576125</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <f>SUM(F4:F6)</f>
         <v>4979200</v>
       </c>
@@ -1534,19 +1560,19 @@
       <c r="A9" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <v>100000</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <v>75000</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <v>50000</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <v>0</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <v>0</v>
       </c>
     </row>
@@ -1554,19 +1580,19 @@
       <c r="A10" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>30000</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <v>40000</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <v>50000</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <v>60000</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <v>70000</v>
       </c>
     </row>
@@ -1574,23 +1600,23 @@
       <c r="A11" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="28" t="str">
         <f>SUM(B9:B10)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="27" t="str">
+      <c r="C11" s="28" t="str">
         <f>SUM(C9:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="27" t="str">
+      <c r="D11" s="28" t="str">
         <f>SUM(D9:D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="27" t="str">
+      <c r="E11" s="28" t="str">
         <f>SUM(E9:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="27" t="str">
+      <c r="F11" s="28" t="str">
         <f>SUM(F9:F10)</f>
         <v>0</v>
       </c>
@@ -1609,23 +1635,23 @@
       <c r="A13" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <f>300*Assumptions!B22</f>
         <v>36000</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <f>309*Assumptions!B23</f>
         <v>61800</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>318*Assumptions!B24</f>
         <v>95400</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>328*Assumptions!B25</f>
         <v>123000</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>338*Assumptions!B26</f>
         <v>135200</v>
       </c>
@@ -1634,23 +1660,23 @@
       <c r="A14" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <f>SUM(B13:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>SUM(C13:C13)</f>
         <v>61800</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>SUM(D13:D13)</f>
         <v>95400</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>SUM(E13:E13)</f>
         <v>123000</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <f>SUM(F13:F13)</f>
         <v>135200</v>
       </c>
@@ -1659,23 +1685,23 @@
       <c r="A16" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="28">
         <f>B7+B11+B14</f>
         <v>1546000</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="28">
         <f>C7+C11+C14</f>
         <v>2522800</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>D7+D11+D14</f>
         <v>3784600</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>E7+E11+E14</f>
         <v>4759125</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <f>F7+F11+F14</f>
         <v>5184400</v>
       </c>
@@ -1715,28 +1741,28 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="25" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1750,19 +1776,19 @@
       <c r="C4" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <v>1</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>110000</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>0.28</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="32">
         <v>149215</v>
       </c>
     </row>
@@ -1776,19 +1802,19 @@
       <c r="C5" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <v>1</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>90000</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>0.28</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <v>122085</v>
       </c>
     </row>
@@ -1802,19 +1828,19 @@
       <c r="C6" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <v>1</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>72000</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>0.28</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <v>97668</v>
       </c>
     </row>
@@ -1828,19 +1854,19 @@
       <c r="C7" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <v>6</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>52000</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>0.28</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <v>423228</v>
       </c>
     </row>
@@ -1854,19 +1880,19 @@
       <c r="C8" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <v>1</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>55000</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>0.28</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <v>74607.5</v>
       </c>
     </row>
@@ -1880,19 +1906,19 @@
       <c r="C9" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>3</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>30000</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>0.2</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <v>114885</v>
       </c>
     </row>
@@ -1906,19 +1932,19 @@
       <c r="C10" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <v>1</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>55000</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>0.28</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <v>74607.5</v>
       </c>
     </row>
@@ -1932,19 +1958,19 @@
       <c r="C11" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="29">
         <v>1</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>55000</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>0.28</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <v>74607.5</v>
       </c>
     </row>
@@ -1958,19 +1984,19 @@
       <c r="C12" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <v>2</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>38000</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>0.25</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="32">
         <v>100814</v>
       </c>
     </row>
@@ -1990,7 +2016,7 @@
       <c r="A15" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="33">
         <v>9</v>
       </c>
     </row>
@@ -1998,7 +2024,7 @@
       <c r="A16" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="33">
         <v>17</v>
       </c>
     </row>
@@ -2006,7 +2032,7 @@
       <c r="A17" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <v>915000</v>
       </c>
     </row>
@@ -2014,7 +2040,7 @@
       <c r="A18" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <v>246720</v>
       </c>
     </row>
@@ -2022,7 +2048,7 @@
       <c r="A19" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <v>69998</v>
       </c>
     </row>
@@ -2030,15 +2056,15 @@
       <c r="A20" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="32">
         <v>1231718</v>
       </c>
     </row>
@@ -2053,22 +2079,22 @@
       <c r="F23" s="8"/>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2076,19 +2102,19 @@
       <c r="A25" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <v>1231718</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <v>1231718</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <v>1231718</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <v>1231718</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="27">
         <v>1231718</v>
       </c>
     </row>
@@ -2096,23 +2122,23 @@
       <c r="A26" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="34">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="34">
         <f>(1+Assumptions!B29)^1</f>
         <v>1</v>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="34">
         <f>(1+Assumptions!B29)^2</f>
         <v>1</v>
       </c>
-      <c r="E26" s="32">
+      <c r="E26" s="34">
         <f>(1+Assumptions!B29)^3</f>
         <v>1</v>
       </c>
-      <c r="F26" s="32">
+      <c r="F26" s="34">
         <f>(1+Assumptions!B29)^4</f>
         <v>1</v>
       </c>
@@ -2121,20 +2147,20 @@
       <c r="A27" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="35">
         <f>Assumptions!B31</f>
         <v>0.8333333333333334</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="35">
         <v>1</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="35">
         <v>1</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="35">
         <v>1</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="35">
         <v>1</v>
       </c>
     </row>
@@ -2142,23 +2168,23 @@
       <c r="A28" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="28">
         <f>B25*B26*B27</f>
         <v>1026431</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="28">
         <f>C25*C26*C27</f>
         <v>1231718</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="28">
         <f>D25*D26*D27</f>
         <v>1231718</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>E25*E26*E27</f>
         <v>1231718</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="28">
         <f>F25*F26*F27</f>
         <v>1231718</v>
       </c>
@@ -2189,22 +2215,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2212,23 +2238,23 @@
       <c r="A2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="26">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="26">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="26">
         <f>Assumptions!B25</f>
         <v>375</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="26">
         <f>Assumptions!B26</f>
         <v>400</v>
       </c>
@@ -2247,23 +2273,23 @@
       <c r="A4" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>700*Assumptions!B22</f>
         <v>84000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>721*Assumptions!B23</f>
         <v>144200</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>743*Assumptions!B24</f>
         <v>222900</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>765*Assumptions!B25</f>
         <v>286875</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>788*Assumptions!B26</f>
         <v>315200</v>
       </c>
@@ -2272,23 +2298,23 @@
       <c r="A5" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <f>SUM(B4:B4)</f>
         <v>84000</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <f>SUM(C4:C4)</f>
         <v>144200</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <f>SUM(D4:D4)</f>
         <v>222900</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <f>SUM(E4:E4)</f>
         <v>286875</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <f>SUM(F4:F4)</f>
         <v>315200</v>
       </c>
@@ -2307,23 +2333,23 @@
       <c r="A7" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>500*Assumptions!B22</f>
         <v>60000</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>515*Assumptions!B23</f>
         <v>103000</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>530*Assumptions!B24</f>
         <v>159000</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>546*Assumptions!B25</f>
         <v>204750</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>562*Assumptions!B26</f>
         <v>224800</v>
       </c>
@@ -2332,23 +2358,23 @@
       <c r="A8" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <f>SUM(B7:B7)</f>
         <v>60000</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f>SUM(C7:C7)</f>
         <v>103000</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>SUM(D7:D7)</f>
         <v>159000</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>SUM(E7:E7)</f>
         <v>204750</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f>SUM(F7:F7)</f>
         <v>224800</v>
       </c>
@@ -2367,23 +2393,23 @@
       <c r="A10" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>18000*12</f>
         <v>216000</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>18540*12</f>
         <v>222480</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>19096*12</f>
         <v>229152</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>19669*12</f>
         <v>236028</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>20259*12</f>
         <v>243108</v>
       </c>
@@ -2392,23 +2418,23 @@
       <c r="A11" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>2500*12</f>
         <v>30000</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>2575*12</f>
         <v>30900</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>2652*12</f>
         <v>31824</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>2732*12</f>
         <v>32784</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>2814*12</f>
         <v>33768</v>
       </c>
@@ -2417,19 +2443,19 @@
       <c r="A12" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <v>18000</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <v>18540</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <v>19096</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <v>19669</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <v>20259</v>
       </c>
     </row>
@@ -2437,23 +2463,23 @@
       <c r="A13" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <f>1500*12</f>
         <v>18000</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <f>1545*12</f>
         <v>18540</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>1591*12</f>
         <v>19092</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>1639*12</f>
         <v>19668</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>1688*12</f>
         <v>20256</v>
       </c>
@@ -2462,23 +2488,23 @@
       <c r="A14" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <f>SUM(B10:B13)</f>
         <v>282000</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>SUM(C10:C13)</f>
         <v>290460</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>SUM(D10:D13)</f>
         <v>299164</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>SUM(E10:E13)</f>
         <v>308149</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <f>SUM(F10:F13)</f>
         <v>317391</v>
       </c>
@@ -2497,19 +2523,19 @@
       <c r="A16" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="27">
         <v>25000</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="27">
         <v>25750</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="27">
         <v>26523</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="27">
         <v>27318</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="27">
         <v>28138</v>
       </c>
     </row>
@@ -2517,19 +2543,19 @@
       <c r="A17" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="27">
         <v>15000</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <v>15450</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <v>15914</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <v>16391</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="27">
         <v>16883</v>
       </c>
     </row>
@@ -2537,19 +2563,19 @@
       <c r="A18" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="27">
         <v>20000</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <v>20600</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <v>21218</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <v>21855</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="27">
         <v>22510</v>
       </c>
     </row>
@@ -2557,23 +2583,23 @@
       <c r="A19" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="27">
         <f>800*Assumptions!B22</f>
         <v>96000</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="27">
         <f>824*Assumptions!B23</f>
         <v>164800</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="27">
         <f>849*Assumptions!B24</f>
         <v>254700</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="27">
         <f>874*Assumptions!B25</f>
         <v>327750</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="27">
         <f>900*Assumptions!B26</f>
         <v>360000</v>
       </c>
@@ -2582,23 +2608,23 @@
       <c r="A20" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <f>600*Assumptions!B22</f>
         <v>72000</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <f>618*Assumptions!B23</f>
         <v>123600</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f>637*Assumptions!B24</f>
         <v>191100</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f>656*Assumptions!B25</f>
         <v>246000</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f>675*Assumptions!B26</f>
         <v>270000</v>
       </c>
@@ -2607,23 +2633,23 @@
       <c r="A21" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="28">
         <f>SUM(B16:B20)</f>
         <v>228000</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <f>SUM(C16:C20)</f>
         <v>350200</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>SUM(D16:D20)</f>
         <v>509455</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>SUM(E16:E20)</f>
         <v>639314</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="28">
         <f>SUM(F16:F20)</f>
         <v>697531</v>
       </c>
@@ -2632,23 +2658,23 @@
       <c r="A23" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="28">
         <f>B5+B8+B14+B21</f>
         <v>654000</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="28">
         <f>C5+C8+C14+C21</f>
         <v>887860</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>D5+D8+D14+D21</f>
         <v>1190519</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>E5+E8+E14+E21</f>
         <v>1439088</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="28">
         <f>F5+F8+F14+F21</f>
         <v>1554922</v>
       </c>
@@ -2676,22 +2702,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2709,19 +2735,19 @@
       <c r="A3" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <v>49824.605221179416</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <v>49824.605221179416</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <v>49824.605221179416</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <v>49824.605221179416</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <v>49824.605221179416</v>
       </c>
     </row>
@@ -2729,19 +2755,19 @@
       <c r="A4" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <v>75000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <v>25000</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <v>30000</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <v>15000</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <v>10000</v>
       </c>
     </row>
@@ -2749,19 +2775,19 @@
       <c r="A5" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <v>40000</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <v>15000</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <v>10000</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <v>10000</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <v>10000</v>
       </c>
     </row>
@@ -2769,23 +2795,23 @@
       <c r="A6" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>SUM(B3:B5)</f>
         <v>164825</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>SUM(C3:C5)</f>
         <v>89825</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>SUM(D3:D5)</f>
         <v>89825</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>SUM(E3:E5)</f>
         <v>74825</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>SUM(F3:F5)</f>
         <v>69825</v>
       </c>
@@ -2813,22 +2839,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2836,23 +2862,23 @@
       <c r="A2" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="27">
         <f>'Revenue Schedule'!B16</f>
         <v>1546000</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="27">
         <f>'Revenue Schedule'!C16</f>
         <v>2522800</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="27">
         <f>'Revenue Schedule'!D16</f>
         <v>3784600</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="27">
         <f>'Revenue Schedule'!E16</f>
         <v>4759125</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="27">
         <f>'Revenue Schedule'!F16</f>
         <v>5184400</v>
       </c>
@@ -2861,23 +2887,23 @@
       <c r="A3" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>'Staffing &amp; Personnel'!B28</f>
         <v>1026431</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <f>'Staffing &amp; Personnel'!C28</f>
         <v>1231718</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <f>'Staffing &amp; Personnel'!D28</f>
         <v>1231718</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <f>'Staffing &amp; Personnel'!E28</f>
         <v>1231718</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <f>'Staffing &amp; Personnel'!F28</f>
         <v>1231718</v>
       </c>
@@ -2886,23 +2912,23 @@
       <c r="A4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>'Operating Expenses'!B23</f>
         <v>654000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>'Operating Expenses'!C23</f>
         <v>887860</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>'Operating Expenses'!D23</f>
         <v>1190519</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>'Operating Expenses'!E23</f>
         <v>1439088</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>'Operating Expenses'!F23</f>
         <v>1554922</v>
       </c>
@@ -2911,23 +2937,23 @@
       <c r="A5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>'Capital &amp; Debt'!B6</f>
         <v>164825</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>'Capital &amp; Debt'!C6</f>
         <v>89825</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>'Capital &amp; Debt'!D6</f>
         <v>89825</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>'Capital &amp; Debt'!E6</f>
         <v>74825</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>'Capital &amp; Debt'!F6</f>
         <v>69825</v>
       </c>
@@ -2936,23 +2962,23 @@
       <c r="A6" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>B3+B4+B5</f>
         <v>1845256</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>C3+C4+C5</f>
         <v>2209403</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>D3+D4+D5</f>
         <v>2512062</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>E3+E4+E5</f>
         <v>2745631</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>F3+F4+F5</f>
         <v>2856465</v>
       </c>
@@ -2961,23 +2987,23 @@
       <c r="A7" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>B2-B6</f>
         <v>-299256</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>C2-C6</f>
         <v>313397</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>D2-D6</f>
         <v>1272538</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <f>E2-E6</f>
         <v>2013494</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <f>F2-F6</f>
         <v>2327935</v>
       </c>
@@ -2986,23 +3012,23 @@
       <c r="A8" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <f>B7</f>
         <v>-299256</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>B8+C7</f>
         <v>14141</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>C8+D7</f>
         <v>1286679</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>D8+E7</f>
         <v>3300173</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>E8+F7</f>
         <v>5628108</v>
       </c>
@@ -3011,23 +3037,23 @@
       <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34" t="str">
+      <c r="B9" s="36" t="str">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="36">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>0.0768044580368543</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="36">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>6.146404029836844</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="36">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>14.42367018729028</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="36">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>23.643663059060763</v>
       </c>
@@ -3055,17 +3081,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="38" t="s">
         <v>151</v>
       </c>
     </row>
@@ -3083,7 +3109,7 @@
       <c r="A5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="33" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3091,7 +3117,7 @@
       <c r="A6" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="33" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3099,7 +3125,7 @@
       <c r="A7" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="33" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3107,7 +3133,7 @@
       <c r="A8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="33" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3115,7 +3141,7 @@
       <c r="A9" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3123,7 +3149,7 @@
       <c r="A10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="33" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3131,7 +3157,7 @@
       <c r="A11" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="33" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3139,7 +3165,7 @@
       <c r="A12" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="33" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3154,22 +3180,22 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3177,23 +3203,23 @@
       <c r="A16" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>'Revenue Schedule'!B2</f>
         <v>120</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>'Revenue Schedule'!C2</f>
         <v>200</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <f>'Revenue Schedule'!D2</f>
         <v>300</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>'Revenue Schedule'!E2</f>
         <v>375</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <f>'Revenue Schedule'!F2</f>
         <v>400</v>
       </c>
@@ -3205,40 +3231,40 @@
       <c r="B17" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="39">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="39">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="39">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.25</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="39">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3246,23 +3272,23 @@
       <c r="A20" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <f>'Financial Model'!B2</f>
         <v>1546000</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <f>'Financial Model'!C2</f>
         <v>2522800</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f>'Financial Model'!D2</f>
         <v>3784600</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f>'Financial Model'!E2</f>
         <v>4759125</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f>'Financial Model'!F2</f>
         <v>5184400</v>
       </c>
@@ -3271,23 +3297,23 @@
       <c r="A21" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>'Financial Model'!B3</f>
         <v>1026431</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>'Financial Model'!C3</f>
         <v>1231718</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>'Financial Model'!D3</f>
         <v>1231718</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f>'Financial Model'!E3</f>
         <v>1231718</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="27">
         <f>'Financial Model'!F3</f>
         <v>1231718</v>
       </c>
@@ -3296,23 +3322,23 @@
       <c r="A22" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <f>'Financial Model'!B4</f>
         <v>654000</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>'Financial Model'!C4</f>
         <v>887860</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <f>'Financial Model'!D4</f>
         <v>1190519</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <f>'Financial Model'!E4</f>
         <v>1439088</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="27">
         <f>'Financial Model'!F4</f>
         <v>1554922</v>
       </c>
@@ -3321,48 +3347,48 @@
       <c r="A23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="28">
         <f>'Financial Model'!B6</f>
         <v>1845256</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="28">
         <f>'Financial Model'!C6</f>
         <v>2209403</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>'Financial Model'!D6</f>
         <v>2512062</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>'Financial Model'!E6</f>
         <v>2745631</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="28">
         <f>'Financial Model'!F6</f>
         <v>2856465</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="38">
+      <c r="B24" s="40">
         <f>'Financial Model'!B7</f>
         <v>-299256</v>
       </c>
-      <c r="C24" s="39">
+      <c r="C24" s="41">
         <f>'Financial Model'!C7</f>
         <v>313397</v>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="41">
         <f>'Financial Model'!D7</f>
         <v>1272538</v>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="41">
         <f>'Financial Model'!E7</f>
         <v>2013494</v>
       </c>
-      <c r="F24" s="39">
+      <c r="F24" s="41">
         <f>'Financial Model'!F7</f>
         <v>2327935</v>
       </c>
@@ -3371,36 +3397,36 @@
       <c r="A25" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <f>'Financial Model'!B8</f>
         <v>-299256</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <f>'Financial Model'!C8</f>
         <v>14141</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <f>'Financial Model'!D8</f>
         <v>1286679</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <f>'Financial Model'!E8</f>
         <v>3300173</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="27">
         <f>'Financial Model'!F8</f>
         <v>5628108</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="40" t="str">
+      <c r="B26" s="42" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
-      <c r="C26" s="40">
+      <c r="C26" s="42">
         <f>'Financial Model'!C9</f>
         <v>0.0768044580368543</v>
       </c>
@@ -3431,23 +3457,23 @@
       <c r="A29" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="27">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>12883.333333333334</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="27">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>12614</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="27">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>12615.333333333334</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="27">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>12691</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="27">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>12961</v>
       </c>
@@ -3456,23 +3482,23 @@
       <c r="A30" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="B30" s="37">
+      <c r="B30" s="39">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.6639269081500647</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="39">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.4882345013477089</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="39">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.3254552660783174</v>
       </c>
-      <c r="E30" s="37">
+      <c r="E30" s="39">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.25881186142410634</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="39">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.23758159092662604</v>
       </c>
@@ -3481,32 +3507,32 @@
       <c r="A31" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="39">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.4230271668822768</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="39">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.35193435864912004</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="39">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.31456930719230564</v>
       </c>
-      <c r="E31" s="37">
+      <c r="E31" s="39">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.3023849972421401</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="39">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.299923231232158</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="B32" s="41">
+      <c r="B32" s="43">
         <f>IF(B20=0,0,B24/B20)</f>
         <v>-0.1935679172056921</v>
       </c>
@@ -3541,19 +3567,19 @@
       <c r="A35" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="39">
         <v>0.02328589909443726</v>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="39">
         <v>0.024496591089265895</v>
       </c>
-      <c r="D35" s="37">
+      <c r="D35" s="39">
         <v>0.025207419542355863</v>
       </c>
-      <c r="E35" s="37">
+      <c r="E35" s="39">
         <v>0.025845087069576864</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="39">
         <v>0.026078234704112337</v>
       </c>
     </row>
@@ -3561,19 +3587,19 @@
       <c r="A36" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="37">
+      <c r="B36" s="39">
         <v>0.8926261319534282</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="39">
         <v>0.9299191374663073</v>
       </c>
-      <c r="D36" s="37">
+      <c r="D36" s="39">
         <v>0.9483697088199545</v>
       </c>
-      <c r="E36" s="37">
+      <c r="E36" s="39">
         <v>0.9615475533842881</v>
       </c>
-      <c r="F36" s="37">
+      <c r="F36" s="39">
         <v>0.9604197207005633</v>
       </c>
     </row>
@@ -3581,19 +3607,19 @@
       <c r="A37" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="39">
         <v>0.08408796895213454</v>
       </c>
-      <c r="C37" s="37">
+      <c r="C37" s="39">
         <v>0.045584271444426824</v>
       </c>
-      <c r="D37" s="37">
+      <c r="D37" s="39">
         <v>0.026422871637689586</v>
       </c>
-      <c r="E37" s="37">
+      <c r="E37" s="39">
         <v>0.012607359546135056</v>
       </c>
-      <c r="F37" s="37">
+      <c r="F37" s="39">
         <v>0.013502044595324435</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="166">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -105,6 +105,12 @@
     <t>SchoolStack Budget - Assumptions</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
     <t>SCHOOL INFORMATION</t>
   </si>
   <si>
@@ -223,9 +229,6 @@
   </si>
   <si>
     <t>5 Years</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Year 1</t>
@@ -543,7 +546,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -616,6 +619,12 @@
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -746,7 +755,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -766,33 +775,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="18" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1148,222 +1159,230 @@
       </c>
       <c r="B1" s="18"/>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>26</v>
+      <c r="A5" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>28</v>
+      <c r="A6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>30</v>
+      <c r="A7" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>32</v>
+      <c r="A8" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>34</v>
+      <c r="A9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="20">
+      <c r="A10" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="22">
         <v>2026</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="20">
+      <c r="A11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="20">
+      <c r="A12" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="22">
         <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>39</v>
+      <c r="A13" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="20">
+      <c r="A14" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="22">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>42</v>
+      <c r="A15" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>44</v>
+      <c r="A16" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>46</v>
+      <c r="A17" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>48</v>
+      <c r="A18" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>50</v>
+      <c r="A19" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" s="8"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="21">
+      <c r="A22" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="23">
         <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="21">
+      <c r="A23" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="23">
         <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="21">
+      <c r="A24" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="23">
         <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="21">
+      <c r="A25" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="23">
         <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="21">
+      <c r="A26" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="23">
         <v>400</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="8"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="22">
+      <c r="A29" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="22">
+      <c r="A30" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="23">
+      <c r="A31" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="25">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>62</v>
+      <c r="A32" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1392,53 +1411,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="28">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="28">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="28">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="28">
         <f>Assumptions!B25</f>
         <v>375</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="28">
         <f>Assumptions!B26</f>
         <v>400</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1447,108 +1466,108 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="29">
         <f>9500*Assumptions!B22</f>
         <v>1140000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>9690*Assumptions!B23</f>
         <v>1938000</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>9884*Assumptions!B24</f>
         <v>2965200</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>10081*Assumptions!B25</f>
         <v>3780375</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>10283*Assumptions!B26</f>
         <v>4113200</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="27">
+      <c r="A5" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="29">
         <f>800*Assumptions!B22</f>
         <v>96000</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <f>816*Assumptions!B23</f>
         <v>163200</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>832*Assumptions!B24</f>
         <v>249600</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="29">
         <f>849*Assumptions!B25</f>
         <v>318375</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <f>866*Assumptions!B26</f>
         <v>346400</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="27">
+      <c r="A6" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="29">
         <f>1200*Assumptions!B22</f>
         <v>144000</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="29">
         <f>1224*Assumptions!B23</f>
         <v>244800</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="29">
         <f>1248*Assumptions!B24</f>
         <v>374400</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="29">
         <f>1273*Assumptions!B25</f>
         <v>477375</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="29">
         <f>1299*Assumptions!B26</f>
         <v>519600</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="28">
+        <v>75</v>
+      </c>
+      <c r="B7" s="30">
         <f>SUM(B4:B6)</f>
         <v>1380000</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="30">
         <f>SUM(C4:C6)</f>
         <v>2346000</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="30">
         <f>SUM(D4:D6)</f>
         <v>3589200</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="30">
         <f>SUM(E4:E6)</f>
         <v>4576125</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="30">
         <f>SUM(F4:F6)</f>
         <v>4979200</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1557,73 +1576,73 @@
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="27">
+      <c r="A9" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="29">
         <v>100000</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="29">
         <v>75000</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="29">
         <v>50000</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="29">
         <v>0</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="27">
+      <c r="A10" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="29">
         <v>30000</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="29">
         <v>40000</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="29">
         <v>50000</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="29">
         <v>60000</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="29">
         <v>70000</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="28" t="str">
+        <v>79</v>
+      </c>
+      <c r="B11" s="30" t="str">
         <f>SUM(B9:B10)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="28" t="str">
+      <c r="C11" s="30" t="str">
         <f>SUM(C9:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="28" t="str">
+      <c r="D11" s="30" t="str">
         <f>SUM(D9:D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="28" t="str">
+      <c r="E11" s="30" t="str">
         <f>SUM(E9:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="28" t="str">
+      <c r="F11" s="30" t="str">
         <f>SUM(F9:F10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -1632,76 +1651,76 @@
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="27">
+      <c r="A13" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="29">
         <f>300*Assumptions!B22</f>
         <v>36000</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="29">
         <f>309*Assumptions!B23</f>
         <v>61800</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="29">
         <f>318*Assumptions!B24</f>
         <v>95400</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="29">
         <f>328*Assumptions!B25</f>
         <v>123000</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="29">
         <f>338*Assumptions!B26</f>
         <v>135200</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="28">
+        <v>82</v>
+      </c>
+      <c r="B14" s="30">
         <f>SUM(B13:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="30">
         <f>SUM(C13:C13)</f>
         <v>61800</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="30">
         <f>SUM(D13:D13)</f>
         <v>95400</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="30">
         <f>SUM(E13:E13)</f>
         <v>123000</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="30">
         <f>SUM(F13:F13)</f>
         <v>135200</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="28">
+        <v>83</v>
+      </c>
+      <c r="B16" s="30">
         <f>B7+B11+B14</f>
         <v>1546000</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="30">
         <f>C7+C11+C14</f>
         <v>2522800</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="30">
         <f>D7+D11+D14</f>
         <v>3784600</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="30">
         <f>E7+E11+E14</f>
         <v>4759125</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="30">
         <f>F7+F11+F14</f>
         <v>5184400</v>
       </c>
@@ -1730,7 +1749,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1741,51 +1760,51 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="25" t="s">
+      <c r="A3" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="C3" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="D3" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="F3" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="G3" s="27" t="s">
         <v>91</v>
       </c>
+      <c r="H3" s="27" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="29">
+      <c r="C4" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="25">
         <v>1</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>110000</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="24">
         <v>0.28</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="24">
         <v>0.0765</v>
       </c>
       <c r="H4" s="32">
@@ -1793,25 +1812,25 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>1</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>90000</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="24">
         <v>0.28</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="24">
         <v>0.0765</v>
       </c>
       <c r="H5" s="32">
@@ -1819,25 +1838,25 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="19" t="s">
+      <c r="A6" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="29">
+      <c r="C6" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="25">
         <v>1</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>72000</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="24">
         <v>0.28</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="24">
         <v>0.0765</v>
       </c>
       <c r="H6" s="32">
@@ -1845,25 +1864,25 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="19" t="s">
+      <c r="A7" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="29">
+      <c r="B7" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="25">
         <v>6</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>52000</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="24">
         <v>0.28</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="24">
         <v>0.0765</v>
       </c>
       <c r="H7" s="32">
@@ -1871,25 +1890,25 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="29">
+      <c r="C8" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>55000</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="24">
         <v>0.28</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="24">
         <v>0.0765</v>
       </c>
       <c r="H8" s="32">
@@ -1897,25 +1916,25 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="29">
+      <c r="A9" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="25">
         <v>3</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>30000</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="24">
         <v>0.2</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="24">
         <v>0.0765</v>
       </c>
       <c r="H9" s="32">
@@ -1923,25 +1942,25 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="29">
+      <c r="B10" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="25">
         <v>1</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>55000</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="24">
         <v>0.28</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="24">
         <v>0.0765</v>
       </c>
       <c r="H10" s="32">
@@ -1949,25 +1968,25 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="19" t="s">
+      <c r="A11" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="29">
+      <c r="B11" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="25">
         <v>1</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>55000</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="24">
         <v>0.28</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="24">
         <v>0.0765</v>
       </c>
       <c r="H11" s="32">
@@ -1975,25 +1994,25 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="19" t="s">
+      <c r="A12" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" s="29">
+      <c r="B12" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="25">
         <v>2</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>38000</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="24">
         <v>0.25</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="24">
         <v>0.0765</v>
       </c>
       <c r="H12" s="32">
@@ -2002,7 +2021,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2013,64 +2032,64 @@
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>108</v>
+      <c r="A15" s="21" t="s">
+        <v>109</v>
       </c>
       <c r="B15" s="33">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>109</v>
+      <c r="A16" s="21" t="s">
+        <v>110</v>
       </c>
       <c r="B16" s="33">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" s="30">
+      <c r="A17" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="34">
         <v>915000</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="30">
+      <c r="A18" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="34">
         <v>246720</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="30">
+      <c r="A19" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="34">
         <v>69998</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" s="30">
+      <c r="A20" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="34">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="32">
+        <v>115</v>
+      </c>
+      <c r="B21" s="35">
         <v>1231718</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -2079,112 +2098,112 @@
       <c r="F23" s="8"/>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="25" t="s">
+      <c r="A24" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="C24" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="D24" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="E24" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F24" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" s="27">
+      <c r="A25" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="29">
         <v>1231718</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="29">
         <v>1231718</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="29">
         <v>1231718</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="29">
         <v>1231718</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="29">
         <v>1231718</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" s="34">
+      <c r="A26" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="36">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="36">
         <f>(1+Assumptions!B29)^1</f>
         <v>1</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="36">
         <f>(1+Assumptions!B29)^2</f>
         <v>1</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="36">
         <f>(1+Assumptions!B29)^3</f>
         <v>1</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="36">
         <f>(1+Assumptions!B29)^4</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="35">
+      <c r="A27" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="37">
         <f>Assumptions!B31</f>
         <v>0.8333333333333334</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="37">
         <v>1</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="37">
         <v>1</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="37">
         <v>1</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="37">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="28">
+        <v>120</v>
+      </c>
+      <c r="B28" s="30">
         <f>B25*B26*B27</f>
         <v>1026431</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="30">
         <f>C25*C26*C27</f>
         <v>1231718</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="30">
         <f>D25*D26*D27</f>
         <v>1231718</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="30">
         <f>E25*E26*E27</f>
         <v>1231718</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="30">
         <f>F25*F26*F27</f>
         <v>1231718</v>
       </c>
@@ -2215,53 +2234,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="28">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="28">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="28">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="28">
         <f>Assumptions!B25</f>
         <v>375</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="28">
         <f>Assumptions!B26</f>
         <v>400</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2270,58 +2289,58 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="29">
         <f>700*Assumptions!B22</f>
         <v>84000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>721*Assumptions!B23</f>
         <v>144200</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>743*Assumptions!B24</f>
         <v>222900</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>765*Assumptions!B25</f>
         <v>286875</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>788*Assumptions!B26</f>
         <v>315200</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5" s="28">
+        <v>123</v>
+      </c>
+      <c r="B5" s="30">
         <f>SUM(B4:B4)</f>
         <v>84000</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="30">
         <f>SUM(C4:C4)</f>
         <v>144200</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="30">
         <f>SUM(D4:D4)</f>
         <v>222900</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="30">
         <f>SUM(E4:E4)</f>
         <v>286875</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="30">
         <f>SUM(F4:F4)</f>
         <v>315200</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2330,58 +2349,58 @@
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="27">
+      <c r="A7" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="29">
         <f>500*Assumptions!B22</f>
         <v>60000</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="29">
         <f>515*Assumptions!B23</f>
         <v>103000</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="29">
         <f>530*Assumptions!B24</f>
         <v>159000</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="29">
         <f>546*Assumptions!B25</f>
         <v>204750</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="29">
         <f>562*Assumptions!B26</f>
         <v>224800</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="28">
+        <v>126</v>
+      </c>
+      <c r="B8" s="30">
         <f>SUM(B7:B7)</f>
         <v>60000</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="30">
         <f>SUM(C7:C7)</f>
         <v>103000</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="30">
         <f>SUM(D7:D7)</f>
         <v>159000</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="30">
         <f>SUM(E7:E7)</f>
         <v>204750</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="30">
         <f>SUM(F7:F7)</f>
         <v>224800</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2390,128 +2409,128 @@
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="27">
+      <c r="A10" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="29">
         <f>18000*12</f>
         <v>216000</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="29">
         <f>18540*12</f>
         <v>222480</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="29">
         <f>19096*12</f>
         <v>229152</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="29">
         <f>19669*12</f>
         <v>236028</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="29">
         <f>20259*12</f>
         <v>243108</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="27">
+      <c r="A11" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="29">
         <f>2500*12</f>
         <v>30000</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="29">
         <f>2575*12</f>
         <v>30900</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="29">
         <f>2652*12</f>
         <v>31824</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="29">
         <f>2732*12</f>
         <v>32784</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="29">
         <f>2814*12</f>
         <v>33768</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B12" s="27">
+      <c r="A12" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="29">
         <v>18000</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="29">
         <v>18540</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="29">
         <v>19096</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="29">
         <v>19669</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="29">
         <v>20259</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="B13" s="27">
+      <c r="A13" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="29">
         <f>1500*12</f>
         <v>18000</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="29">
         <f>1545*12</f>
         <v>18540</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="29">
         <f>1591*12</f>
         <v>19092</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="29">
         <f>1639*12</f>
         <v>19668</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="29">
         <f>1688*12</f>
         <v>20256</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" s="28">
+        <v>132</v>
+      </c>
+      <c r="B14" s="30">
         <f>SUM(B10:B13)</f>
         <v>282000</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="30">
         <f>SUM(C10:C13)</f>
         <v>290460</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="30">
         <f>SUM(D10:D13)</f>
         <v>299164</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="30">
         <f>SUM(E10:E13)</f>
         <v>308149</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="30">
         <f>SUM(F10:F13)</f>
         <v>317391</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -2520,161 +2539,161 @@
       <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B16" s="27">
+      <c r="A16" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="29">
         <v>25000</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="29">
         <v>25750</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="29">
         <v>26523</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="29">
         <v>27318</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="29">
         <v>28138</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="B17" s="27">
+      <c r="A17" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="29">
         <v>15000</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="29">
         <v>15450</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="29">
         <v>15914</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="29">
         <v>16391</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="29">
         <v>16883</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" s="27">
+      <c r="A18" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B18" s="29">
         <v>20000</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="29">
         <v>20600</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="29">
         <v>21218</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="29">
         <v>21855</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="29">
         <v>22510</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" s="27">
+      <c r="A19" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" s="29">
         <f>800*Assumptions!B22</f>
         <v>96000</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="29">
         <f>824*Assumptions!B23</f>
         <v>164800</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="29">
         <f>849*Assumptions!B24</f>
         <v>254700</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="29">
         <f>874*Assumptions!B25</f>
         <v>327750</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="29">
         <f>900*Assumptions!B26</f>
         <v>360000</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="B20" s="27">
+      <c r="A20" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="29">
         <f>600*Assumptions!B22</f>
         <v>72000</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="29">
         <f>618*Assumptions!B23</f>
         <v>123600</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="29">
         <f>637*Assumptions!B24</f>
         <v>191100</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="29">
         <f>656*Assumptions!B25</f>
         <v>246000</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="29">
         <f>675*Assumptions!B26</f>
         <v>270000</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B21" s="28">
+        <v>139</v>
+      </c>
+      <c r="B21" s="30">
         <f>SUM(B16:B20)</f>
         <v>228000</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="30">
         <f>SUM(C16:C20)</f>
         <v>350200</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="30">
         <f>SUM(D16:D20)</f>
         <v>509455</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="30">
         <f>SUM(E16:E20)</f>
         <v>639314</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="30">
         <f>SUM(F16:F20)</f>
         <v>697531</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B23" s="28">
+        <v>140</v>
+      </c>
+      <c r="B23" s="30">
         <f>B5+B8+B14+B21</f>
         <v>654000</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="30">
         <f>C5+C8+C14+C21</f>
         <v>887860</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="30">
         <f>D5+D8+D14+D21</f>
         <v>1190519</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="30">
         <f>E5+E8+E14+E21</f>
         <v>1439088</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="30">
         <f>F5+F8+F14+F21</f>
         <v>1554922</v>
       </c>
@@ -2702,28 +2721,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2732,86 +2751,86 @@
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="27">
+      <c r="A3" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="29">
         <v>49824.605221179416</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="29">
         <v>49824.605221179416</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="29">
         <v>49824.605221179416</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="29">
         <v>49824.605221179416</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="29">
         <v>49824.605221179416</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="29">
         <v>75000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <v>25000</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <v>30000</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <v>15000</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <v>10000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="27">
+      <c r="A5" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="29">
         <v>40000</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <v>15000</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <v>10000</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="29">
         <v>10000</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <v>10000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" s="28">
+        <v>145</v>
+      </c>
+      <c r="B6" s="30">
         <f>SUM(B3:B5)</f>
         <v>164825</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="30">
         <f>SUM(C3:C5)</f>
         <v>89825</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="30">
         <f>SUM(D3:D5)</f>
         <v>89825</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="30">
         <f>SUM(E3:E5)</f>
         <v>74825</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="30">
         <f>SUM(F3:F5)</f>
         <v>69825</v>
       </c>
@@ -2839,221 +2858,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B2" s="27">
+      <c r="A2" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="29">
         <f>'Revenue Schedule'!B16</f>
         <v>1546000</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="29">
         <f>'Revenue Schedule'!C16</f>
         <v>2522800</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="29">
         <f>'Revenue Schedule'!D16</f>
         <v>3784600</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="29">
         <f>'Revenue Schedule'!E16</f>
         <v>4759125</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="29">
         <f>'Revenue Schedule'!F16</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="B3" s="27">
+      <c r="A3" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="29">
         <f>'Staffing &amp; Personnel'!B28</f>
         <v>1026431</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="29">
         <f>'Staffing &amp; Personnel'!C28</f>
         <v>1231718</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="29">
         <f>'Staffing &amp; Personnel'!D28</f>
         <v>1231718</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="29">
         <f>'Staffing &amp; Personnel'!E28</f>
         <v>1231718</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="29">
         <f>'Staffing &amp; Personnel'!F28</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="29">
         <f>'Operating Expenses'!B23</f>
         <v>654000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>'Operating Expenses'!C23</f>
         <v>887860</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>'Operating Expenses'!D23</f>
         <v>1190519</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>'Operating Expenses'!E23</f>
         <v>1439088</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>'Operating Expenses'!F23</f>
         <v>1554922</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="29">
         <f>'Capital &amp; Debt'!B6</f>
         <v>164825</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <f>'Capital &amp; Debt'!C6</f>
         <v>89825</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>'Capital &amp; Debt'!D6</f>
         <v>89825</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="29">
         <f>'Capital &amp; Debt'!E6</f>
         <v>74825</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <f>'Capital &amp; Debt'!F6</f>
         <v>69825</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="28">
+        <v>148</v>
+      </c>
+      <c r="B6" s="30">
         <f>B3+B4+B5</f>
         <v>1845256</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="30">
         <f>C3+C4+C5</f>
         <v>2209403</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="30">
         <f>D3+D4+D5</f>
         <v>2512062</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="30">
         <f>E3+E4+E5</f>
         <v>2745631</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="30">
         <f>F3+F4+F5</f>
         <v>2856465</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="28">
+        <v>149</v>
+      </c>
+      <c r="B7" s="30">
         <f>B2-B6</f>
         <v>-299256</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="30">
         <f>C2-C6</f>
         <v>313397</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="30">
         <f>D2-D6</f>
         <v>1272538</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="30">
         <f>E2-E6</f>
         <v>2013494</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="30">
         <f>F2-F6</f>
         <v>2327935</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" s="27">
+      <c r="A8" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="29">
         <f>B7</f>
         <v>-299256</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="29">
         <f>B8+C7</f>
         <v>14141</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="29">
         <f>C8+D7</f>
         <v>1286679</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="29">
         <f>D8+E7</f>
         <v>3300173</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="29">
         <f>E8+F7</f>
         <v>5628108</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="36" t="str">
+      <c r="B9" s="38" t="str">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="38">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>0.0768044580368543</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="38">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>6.146404029836844</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="38">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>14.42367018729028</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="38">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>23.643663059060763</v>
       </c>
@@ -3081,23 +3100,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="A1" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>151</v>
+      <c r="A2" s="40" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -3106,72 +3125,72 @@
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>24</v>
+      <c r="A5" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B10" s="33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>38</v>
+      <c r="A11" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B11" s="33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>37</v>
-      </c>
       <c r="B12" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3180,240 +3199,240 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="25" t="s">
+      <c r="A15" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="C15" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="D15" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="E15" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F15" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="26">
+      <c r="A16" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="28">
         <f>'Revenue Schedule'!B2</f>
         <v>120</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="28">
         <f>'Revenue Schedule'!C2</f>
         <v>200</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="28">
         <f>'Revenue Schedule'!D2</f>
         <v>300</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="28">
         <f>'Revenue Schedule'!E2</f>
         <v>375</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="28">
         <f>'Revenue Schedule'!F2</f>
         <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>154</v>
+      <c r="A17" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C17" s="39">
+        <v>156</v>
+      </c>
+      <c r="C17" s="41">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="41">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="41">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.25</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="41">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="25" t="s">
+      <c r="A19" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="C19" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="D19" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="E19" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F19" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B20" s="27">
+      <c r="A20" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="29">
         <f>'Financial Model'!B2</f>
         <v>1546000</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="29">
         <f>'Financial Model'!C2</f>
         <v>2522800</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="29">
         <f>'Financial Model'!D2</f>
         <v>3784600</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="29">
         <f>'Financial Model'!E2</f>
         <v>4759125</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="29">
         <f>'Financial Model'!F2</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="B21" s="27">
+      <c r="A21" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="29">
         <f>'Financial Model'!B3</f>
         <v>1026431</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="29">
         <f>'Financial Model'!C3</f>
         <v>1231718</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="29">
         <f>'Financial Model'!D3</f>
         <v>1231718</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="29">
         <f>'Financial Model'!E3</f>
         <v>1231718</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="29">
         <f>'Financial Model'!F3</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="29">
         <f>'Financial Model'!B4</f>
         <v>654000</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="29">
         <f>'Financial Model'!C4</f>
         <v>887860</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="29">
         <f>'Financial Model'!D4</f>
         <v>1190519</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="29">
         <f>'Financial Model'!E4</f>
         <v>1439088</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="29">
         <f>'Financial Model'!F4</f>
         <v>1554922</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B23" s="28">
+        <v>148</v>
+      </c>
+      <c r="B23" s="30">
         <f>'Financial Model'!B6</f>
         <v>1845256</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="30">
         <f>'Financial Model'!C6</f>
         <v>2209403</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="30">
         <f>'Financial Model'!D6</f>
         <v>2512062</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="30">
         <f>'Financial Model'!E6</f>
         <v>2745631</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="30">
         <f>'Financial Model'!F6</f>
         <v>2856465</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="40">
+        <v>149</v>
+      </c>
+      <c r="B24" s="42">
         <f>'Financial Model'!B7</f>
         <v>-299256</v>
       </c>
-      <c r="C24" s="41">
+      <c r="C24" s="43">
         <f>'Financial Model'!C7</f>
         <v>313397</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="43">
         <f>'Financial Model'!D7</f>
         <v>1272538</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="43">
         <f>'Financial Model'!E7</f>
         <v>2013494</v>
       </c>
-      <c r="F24" s="41">
+      <c r="F24" s="43">
         <f>'Financial Model'!F7</f>
         <v>2327935</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B25" s="27">
+      <c r="A25" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="29">
         <f>'Financial Model'!B8</f>
         <v>-299256</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="29">
         <f>'Financial Model'!C8</f>
         <v>14141</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="29">
         <f>'Financial Model'!D8</f>
         <v>1286679</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="29">
         <f>'Financial Model'!E8</f>
         <v>3300173</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="29">
         <f>'Financial Model'!F8</f>
         <v>5628108</v>
       </c>
@@ -3422,11 +3441,11 @@
       <c r="A26" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="42" t="str">
+      <c r="B26" s="44" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
-      <c r="C26" s="42">
+      <c r="C26" s="44">
         <f>'Financial Model'!C9</f>
         <v>0.0768044580368543</v>
       </c>
@@ -3445,7 +3464,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3454,85 +3473,85 @@
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="B29" s="27">
+      <c r="A29" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" s="29">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>12883.333333333334</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="29">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>12614</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="29">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>12615.333333333334</v>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="29">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>12691</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="29">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>12961</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="B30" s="39">
+      <c r="A30" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" s="41">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.6639269081500647</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="41">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.4882345013477089</v>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="41">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.3254552660783174</v>
       </c>
-      <c r="E30" s="39">
+      <c r="E30" s="41">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.25881186142410634</v>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="41">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.23758159092662604</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B31" s="39">
+      <c r="A31" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" s="41">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.4230271668822768</v>
       </c>
-      <c r="C31" s="39">
+      <c r="C31" s="41">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.35193435864912004</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="41">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.31456930719230564</v>
       </c>
-      <c r="E31" s="39">
+      <c r="E31" s="41">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.3023849972421401</v>
       </c>
-      <c r="F31" s="39">
+      <c r="F31" s="41">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.299923231232158</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="B32" s="43">
+        <v>161</v>
+      </c>
+      <c r="B32" s="45">
         <f>IF(B20=0,0,B24/B20)</f>
         <v>-0.1935679172056921</v>
       </c>
@@ -3555,7 +3574,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3564,62 +3583,62 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" s="39">
+      <c r="A35" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="41">
         <v>0.02328589909443726</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="41">
         <v>0.024496591089265895</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="41">
         <v>0.025207419542355863</v>
       </c>
-      <c r="E35" s="39">
+      <c r="E35" s="41">
         <v>0.025845087069576864</v>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="41">
         <v>0.026078234704112337</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="B36" s="39">
+      <c r="A36" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="41">
         <v>0.8926261319534282</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="41">
         <v>0.9299191374663073</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="41">
         <v>0.9483697088199545</v>
       </c>
-      <c r="E36" s="39">
+      <c r="E36" s="41">
         <v>0.9615475533842881</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="41">
         <v>0.9604197207005633</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="B37" s="39">
+      <c r="A37" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="41">
         <v>0.08408796895213454</v>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="41">
         <v>0.045584271444426824</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="41">
         <v>0.026422871637689586</v>
       </c>
-      <c r="E37" s="39">
+      <c r="E37" s="41">
         <v>0.012607359546135056</v>
       </c>
-      <c r="F37" s="39">
+      <c r="F37" s="41">
         <v>0.013502044595324435</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -14,7 +14,7 @@
     <sheet sheetId="7" name="Summary" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$B32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="167">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL INFORMATION</t>
@@ -662,7 +665,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -686,6 +689,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
@@ -695,7 +703,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -737,6 +745,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
       </left>
@@ -755,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -777,13 +794,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -800,10 +818,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1146,7 +1164,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1159,230 +1177,236 @@
       </c>
       <c r="B1" s="18"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>24</v>
       </c>
+      <c r="D2" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="22" t="s">
+      <c r="A5" s="22" t="s">
         <v>28</v>
       </c>
+      <c r="B5" s="23" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="22" t="s">
+      <c r="A6" s="22" t="s">
         <v>30</v>
       </c>
+      <c r="B6" s="23" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="22" t="s">
+      <c r="A7" s="22" t="s">
         <v>32</v>
       </c>
+      <c r="B7" s="23" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="22" t="s">
+      <c r="A8" s="22" t="s">
         <v>34</v>
       </c>
+      <c r="B8" s="23" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="22" t="s">
+      <c r="A9" s="22" t="s">
         <v>36</v>
       </c>
+      <c r="B9" s="23" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="A10" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="23">
         <v>2026</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="A11" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="22">
+      <c r="A12" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="23">
         <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="22" t="s">
+      <c r="A13" s="22" t="s">
         <v>41</v>
       </c>
+      <c r="B13" s="23" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="22">
+      <c r="A14" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="22" t="s">
         <v>44</v>
       </c>
+      <c r="B15" s="23" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="22" t="s">
         <v>46</v>
       </c>
+      <c r="B16" s="23" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="22" t="s">
         <v>48</v>
       </c>
+      <c r="B17" s="23" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="22" t="s">
         <v>50</v>
       </c>
+      <c r="B18" s="23" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="22" t="s">
+      <c r="A19" s="22" t="s">
         <v>52</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="8"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="23">
+      <c r="A22" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="24">
         <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="23">
+      <c r="A23" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="24">
         <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="23">
+      <c r="A24" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="24">
         <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="23">
+      <c r="A25" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="24">
         <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="23">
+      <c r="A26" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="24">
         <v>400</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="8"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="24">
+      <c r="A29" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="24">
+      <c r="A30" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="25">
+      <c r="A31" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="26">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="26" t="s">
+      <c r="A32" s="22" t="s">
         <v>64</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1411,53 +1435,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="28">
+      <c r="A2" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="29">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <f>Assumptions!B25</f>
         <v>375</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <f>Assumptions!B26</f>
         <v>400</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1466,108 +1490,108 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="30">
         <f>9500*Assumptions!B22</f>
         <v>1140000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>9690*Assumptions!B23</f>
         <v>1938000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>9884*Assumptions!B24</f>
         <v>2965200</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>10081*Assumptions!B25</f>
         <v>3780375</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>10283*Assumptions!B26</f>
         <v>4113200</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="29">
+      <c r="A5" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="30">
         <f>800*Assumptions!B22</f>
         <v>96000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <f>816*Assumptions!B23</f>
         <v>163200</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <f>832*Assumptions!B24</f>
         <v>249600</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>849*Assumptions!B25</f>
         <v>318375</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>866*Assumptions!B26</f>
         <v>346400</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="29">
+      <c r="A6" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="30">
         <f>1200*Assumptions!B22</f>
         <v>144000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <f>1224*Assumptions!B23</f>
         <v>244800</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <f>1248*Assumptions!B24</f>
         <v>374400</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <f>1273*Assumptions!B25</f>
         <v>477375</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <f>1299*Assumptions!B26</f>
         <v>519600</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="30">
+        <v>76</v>
+      </c>
+      <c r="B7" s="31">
         <f>SUM(B4:B6)</f>
         <v>1380000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>SUM(C4:C6)</f>
         <v>2346000</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>SUM(D4:D6)</f>
         <v>3589200</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>SUM(E4:E6)</f>
         <v>4576125</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>SUM(F4:F6)</f>
         <v>4979200</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1576,73 +1600,73 @@
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="29">
+      <c r="A9" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="30">
         <v>100000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>75000</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>50000</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>0</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="29">
+      <c r="A10" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="30">
         <v>30000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>40000</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>50000</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>60000</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>70000</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="30" t="str">
+        <v>80</v>
+      </c>
+      <c r="B11" s="31" t="str">
         <f>SUM(B9:B10)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="30" t="str">
+      <c r="C11" s="31" t="str">
         <f>SUM(C9:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="30" t="str">
+      <c r="D11" s="31" t="str">
         <f>SUM(D9:D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="30" t="str">
+      <c r="E11" s="31" t="str">
         <f>SUM(E9:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="30" t="str">
+      <c r="F11" s="31" t="str">
         <f>SUM(F9:F10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -1651,76 +1675,76 @@
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="29">
+      <c r="A13" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="30">
         <f>300*Assumptions!B22</f>
         <v>36000</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>309*Assumptions!B23</f>
         <v>61800</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>318*Assumptions!B24</f>
         <v>95400</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>328*Assumptions!B25</f>
         <v>123000</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>338*Assumptions!B26</f>
         <v>135200</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="30">
+        <v>83</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B13:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>SUM(C13:C13)</f>
         <v>61800</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>SUM(D13:D13)</f>
         <v>95400</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>SUM(E13:E13)</f>
         <v>123000</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>SUM(F13:F13)</f>
         <v>135200</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="30">
+        <v>84</v>
+      </c>
+      <c r="B16" s="31">
         <f>B7+B11+B14</f>
         <v>1546000</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>C7+C11+C14</f>
         <v>2522800</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <f>D7+D11+D14</f>
         <v>3784600</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <f>E7+E11+E14</f>
         <v>4759125</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <f>F7+F11+F14</f>
         <v>5184400</v>
       </c>
@@ -1749,7 +1773,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1760,268 +1784,268 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="27" t="s">
+      <c r="A3" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="B3" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="C3" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="D3" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="E3" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="F3" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="G3" s="28" t="s">
         <v>92</v>
       </c>
+      <c r="H3" s="28" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="25">
+      <c r="C4" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="26">
         <v>1</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <v>110000</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="25">
         <v>0.28</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="33">
         <v>149215</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="21" t="s">
+      <c r="D5" s="26">
+        <v>1</v>
+      </c>
+      <c r="E5" s="32">
+        <v>90000</v>
+      </c>
+      <c r="F5" s="25">
+        <v>0.28</v>
+      </c>
+      <c r="G5" s="25">
+        <v>0.0765</v>
+      </c>
+      <c r="H5" s="33">
+        <v>122085</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="25">
+      <c r="C6" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="26">
         <v>1</v>
       </c>
-      <c r="E5" s="31">
-        <v>90000</v>
-      </c>
-      <c r="F5" s="24">
+      <c r="E6" s="32">
+        <v>72000</v>
+      </c>
+      <c r="F6" s="25">
         <v>0.28</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G6" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H5" s="32">
-        <v>122085</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="25">
+      <c r="H6" s="33">
+        <v>97668</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="26">
+        <v>6</v>
+      </c>
+      <c r="E7" s="32">
+        <v>52000</v>
+      </c>
+      <c r="F7" s="25">
+        <v>0.28</v>
+      </c>
+      <c r="G7" s="25">
+        <v>0.0765</v>
+      </c>
+      <c r="H7" s="33">
+        <v>423228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="26">
         <v>1</v>
       </c>
-      <c r="E6" s="31">
-        <v>72000</v>
-      </c>
-      <c r="F6" s="24">
+      <c r="E8" s="32">
+        <v>55000</v>
+      </c>
+      <c r="F8" s="25">
         <v>0.28</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G8" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H6" s="32">
-        <v>97668</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="25">
-        <v>6</v>
-      </c>
-      <c r="E7" s="31">
-        <v>52000</v>
-      </c>
-      <c r="F7" s="24">
+      <c r="H8" s="33">
+        <v>74607.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="26">
+        <v>3</v>
+      </c>
+      <c r="E9" s="32">
+        <v>30000</v>
+      </c>
+      <c r="F9" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="25">
+        <v>0.0765</v>
+      </c>
+      <c r="H9" s="33">
+        <v>114885</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="26">
+        <v>1</v>
+      </c>
+      <c r="E10" s="32">
+        <v>55000</v>
+      </c>
+      <c r="F10" s="25">
         <v>0.28</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G10" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H7" s="32">
-        <v>423228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="H10" s="33">
+        <v>74607.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="26">
         <v>1</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E11" s="32">
         <v>55000</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F11" s="25">
         <v>0.28</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G11" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H11" s="33">
         <v>74607.5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="25">
-        <v>3</v>
-      </c>
-      <c r="E9" s="31">
-        <v>30000</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.2</v>
-      </c>
-      <c r="G9" s="24">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="26">
+        <v>2</v>
+      </c>
+      <c r="E12" s="32">
+        <v>38000</v>
+      </c>
+      <c r="F12" s="25">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H9" s="32">
-        <v>114885</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="25">
-        <v>1</v>
-      </c>
-      <c r="E10" s="31">
-        <v>55000</v>
-      </c>
-      <c r="F10" s="24">
-        <v>0.28</v>
-      </c>
-      <c r="G10" s="24">
-        <v>0.0765</v>
-      </c>
-      <c r="H10" s="32">
-        <v>74607.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="25">
-        <v>1</v>
-      </c>
-      <c r="E11" s="31">
-        <v>55000</v>
-      </c>
-      <c r="F11" s="24">
-        <v>0.28</v>
-      </c>
-      <c r="G11" s="24">
-        <v>0.0765</v>
-      </c>
-      <c r="H11" s="32">
-        <v>74607.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" s="25">
-        <v>2</v>
-      </c>
-      <c r="E12" s="31">
-        <v>38000</v>
-      </c>
-      <c r="F12" s="24">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="24">
-        <v>0.0765</v>
-      </c>
-      <c r="H12" s="32">
+      <c r="H12" s="33">
         <v>100814</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2032,64 +2056,64 @@
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" s="33">
+      <c r="A15" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="34">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" s="33">
+      <c r="A16" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="34">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" s="34">
+      <c r="A17" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="35">
         <v>915000</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B18" s="34">
+      <c r="A18" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="35">
         <v>246720</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="B19" s="34">
+      <c r="A19" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="35">
         <v>69998</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" s="34">
+      <c r="A20" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" s="35">
+      <c r="A21" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="36">
         <v>1231718</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -2098,112 +2122,112 @@
       <c r="F23" s="8"/>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="27" t="s">
+      <c r="B24" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="C24" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="D24" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="27" t="s">
+      <c r="E24" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F24" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="30">
         <v>1231718</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>1231718</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>1231718</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>1231718</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>1231718</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" s="36">
+      <c r="A26" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="37">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="37">
         <f>(1+Assumptions!B29)^1</f>
         <v>1</v>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="37">
         <f>(1+Assumptions!B29)^2</f>
         <v>1</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="37">
         <f>(1+Assumptions!B29)^3</f>
         <v>1</v>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="37">
         <f>(1+Assumptions!B29)^4</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" s="37">
+      <c r="A27" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="38">
         <f>Assumptions!B31</f>
         <v>0.8333333333333334</v>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="38">
         <v>1</v>
       </c>
-      <c r="D27" s="37">
+      <c r="D27" s="38">
         <v>1</v>
       </c>
-      <c r="E27" s="37">
+      <c r="E27" s="38">
         <v>1</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="38">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B28" s="30">
+        <v>121</v>
+      </c>
+      <c r="B28" s="31">
         <f>B25*B26*B27</f>
         <v>1026431</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <f>C25*C26*C27</f>
         <v>1231718</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="31">
         <f>D25*D26*D27</f>
         <v>1231718</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="31">
         <f>E25*E26*E27</f>
         <v>1231718</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="31">
         <f>F25*F26*F27</f>
         <v>1231718</v>
       </c>
@@ -2234,53 +2258,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="28">
+      <c r="A2" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="29">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <f>Assumptions!B25</f>
         <v>375</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <f>Assumptions!B26</f>
         <v>400</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2289,58 +2313,58 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="30">
         <f>700*Assumptions!B22</f>
         <v>84000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>721*Assumptions!B23</f>
         <v>144200</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>743*Assumptions!B24</f>
         <v>222900</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>765*Assumptions!B25</f>
         <v>286875</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>788*Assumptions!B26</f>
         <v>315200</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" s="30">
+        <v>124</v>
+      </c>
+      <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
         <v>84000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>SUM(C4:C4)</f>
         <v>144200</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>SUM(D4:D4)</f>
         <v>222900</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>SUM(E4:E4)</f>
         <v>286875</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>SUM(F4:F4)</f>
         <v>315200</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2349,58 +2373,58 @@
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" s="29">
+      <c r="A7" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="30">
         <f>500*Assumptions!B22</f>
         <v>60000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <f>515*Assumptions!B23</f>
         <v>103000</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>530*Assumptions!B24</f>
         <v>159000</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <f>546*Assumptions!B25</f>
         <v>204750</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>562*Assumptions!B26</f>
         <v>224800</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="30">
+        <v>127</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
         <v>60000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C7:C7)</f>
         <v>103000</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D7:D7)</f>
         <v>159000</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E7:E7)</f>
         <v>204750</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F7:F7)</f>
         <v>224800</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2409,128 +2433,128 @@
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B10" s="29">
+      <c r="A10" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="30">
         <f>18000*12</f>
         <v>216000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>18540*12</f>
         <v>222480</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>19096*12</f>
         <v>229152</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>19669*12</f>
         <v>236028</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>20259*12</f>
         <v>243108</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="B11" s="29">
+      <c r="A11" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="30">
         <f>2500*12</f>
         <v>30000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>2575*12</f>
         <v>30900</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>2652*12</f>
         <v>31824</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>2732*12</f>
         <v>32784</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>2814*12</f>
         <v>33768</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="29">
+      <c r="A12" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="30">
         <v>18000</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>18540</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>19096</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>19669</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>20259</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B13" s="29">
+      <c r="A13" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="30">
         <f>1500*12</f>
         <v>18000</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>1545*12</f>
         <v>18540</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>1591*12</f>
         <v>19092</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>1639*12</f>
         <v>19668</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>1688*12</f>
         <v>20256</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B14" s="30">
+        <v>133</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B10:B13)</f>
         <v>282000</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>SUM(C10:C13)</f>
         <v>290460</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>SUM(D10:D13)</f>
         <v>299164</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>SUM(E10:E13)</f>
         <v>308149</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>SUM(F10:F13)</f>
         <v>317391</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -2539,161 +2563,161 @@
       <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="B16" s="29">
+      <c r="A16" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" s="30">
         <v>25000</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>25750</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>26523</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>27318</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>28138</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="B17" s="29">
+      <c r="A17" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="30">
         <v>15000</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>15450</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>15914</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>16391</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>16883</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="B18" s="29">
+      <c r="A18" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18" s="30">
         <v>20000</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>20600</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>21218</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <v>21855</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <v>22510</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" s="29">
+      <c r="A19" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" s="30">
         <f>800*Assumptions!B22</f>
         <v>96000</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <f>824*Assumptions!B23</f>
         <v>164800</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <f>849*Assumptions!B24</f>
         <v>254700</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <f>874*Assumptions!B25</f>
         <v>327750</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <f>900*Assumptions!B26</f>
         <v>360000</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="A20" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="30">
         <f>600*Assumptions!B22</f>
         <v>72000</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>618*Assumptions!B23</f>
         <v>123600</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <f>637*Assumptions!B24</f>
         <v>191100</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <f>656*Assumptions!B25</f>
         <v>246000</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <f>675*Assumptions!B26</f>
         <v>270000</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B21" s="30">
+        <v>140</v>
+      </c>
+      <c r="B21" s="31">
         <f>SUM(B16:B20)</f>
         <v>228000</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>SUM(C16:C20)</f>
         <v>350200</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <f>SUM(D16:D20)</f>
         <v>509455</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <f>SUM(E16:E20)</f>
         <v>639314</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <f>SUM(F16:F20)</f>
         <v>697531</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23" s="30">
+        <v>141</v>
+      </c>
+      <c r="B23" s="31">
         <f>B5+B8+B14+B21</f>
         <v>654000</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <f>C5+C8+C14+C21</f>
         <v>887860</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <f>D5+D8+D14+D21</f>
         <v>1190519</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <f>E5+E8+E14+E21</f>
         <v>1439088</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <f>F5+F8+F14+F21</f>
         <v>1554922</v>
       </c>
@@ -2721,28 +2745,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2751,86 +2775,86 @@
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" s="29">
+      <c r="A3" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="30">
         <v>49824.605221179416</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <v>49824.605221179416</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="30">
         <v>49824.605221179416</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="30">
         <v>49824.605221179416</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="30">
         <v>49824.605221179416</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="30">
         <v>75000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <v>25000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>30000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>15000</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <v>10000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="29">
+      <c r="A5" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="30">
         <v>40000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>15000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>10000</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>10000</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>10000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B6" s="30">
+        <v>146</v>
+      </c>
+      <c r="B6" s="31">
         <f>SUM(B3:B5)</f>
         <v>164825</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>SUM(C3:C5)</f>
         <v>89825</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>SUM(D3:D5)</f>
         <v>89825</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>SUM(E3:E5)</f>
         <v>74825</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>SUM(F3:F5)</f>
         <v>69825</v>
       </c>
@@ -2858,221 +2882,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="29">
+      <c r="A2" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="30">
         <f>'Revenue Schedule'!B16</f>
         <v>1546000</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="30">
         <f>'Revenue Schedule'!C16</f>
         <v>2522800</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="30">
         <f>'Revenue Schedule'!D16</f>
         <v>3784600</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="30">
         <f>'Revenue Schedule'!E16</f>
         <v>4759125</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="30">
         <f>'Revenue Schedule'!F16</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="29">
+      <c r="A3" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B28</f>
         <v>1026431</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <f>'Staffing &amp; Personnel'!C28</f>
         <v>1231718</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="30">
         <f>'Staffing &amp; Personnel'!D28</f>
         <v>1231718</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="30">
         <f>'Staffing &amp; Personnel'!E28</f>
         <v>1231718</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="30">
         <f>'Staffing &amp; Personnel'!F28</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="30">
         <f>'Operating Expenses'!B23</f>
         <v>654000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>'Operating Expenses'!C23</f>
         <v>887860</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>'Operating Expenses'!D23</f>
         <v>1190519</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>'Operating Expenses'!E23</f>
         <v>1439088</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>'Operating Expenses'!F23</f>
         <v>1554922</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <f>'Capital &amp; Debt'!B6</f>
         <v>164825</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <f>'Capital &amp; Debt'!C6</f>
         <v>89825</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <f>'Capital &amp; Debt'!D6</f>
         <v>89825</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>'Capital &amp; Debt'!E6</f>
         <v>74825</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>'Capital &amp; Debt'!F6</f>
         <v>69825</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="30">
+        <v>149</v>
+      </c>
+      <c r="B6" s="31">
         <f>B3+B4+B5</f>
         <v>1845256</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>C3+C4+C5</f>
         <v>2209403</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>D3+D4+D5</f>
         <v>2512062</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>E3+E4+E5</f>
         <v>2745631</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>F3+F4+F5</f>
         <v>2856465</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="30">
+        <v>150</v>
+      </c>
+      <c r="B7" s="31">
         <f>B2-B6</f>
         <v>-299256</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>C2-C6</f>
         <v>313397</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>D2-D6</f>
         <v>1272538</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>E2-E6</f>
         <v>2013494</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>F2-F6</f>
         <v>2327935</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="B8" s="29">
+      <c r="A8" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="30">
         <f>B7</f>
         <v>-299256</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>B8+C7</f>
         <v>14141</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>C8+D7</f>
         <v>1286679</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>D8+E7</f>
         <v>3300173</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>E8+F7</f>
         <v>5628108</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="38" t="str">
+      <c r="B9" s="39" t="str">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="39">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>0.0768044580368543</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="39">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>6.146404029836844</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="39">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>14.42367018729028</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="39">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>23.643663059060763</v>
       </c>
@@ -3100,23 +3124,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="A1" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
-        <v>152</v>
+      <c r="A2" s="41" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -3125,72 +3149,72 @@
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="34" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>153</v>
+      <c r="B12" s="34" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3199,253 +3223,253 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="C15" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="D15" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="E15" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F15" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="28">
+      <c r="A16" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="29">
         <f>'Revenue Schedule'!B2</f>
         <v>120</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>'Revenue Schedule'!C2</f>
         <v>200</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>'Revenue Schedule'!D2</f>
         <v>300</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>'Revenue Schedule'!E2</f>
         <v>375</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>'Revenue Schedule'!F2</f>
         <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>155</v>
+      <c r="A17" s="22" t="s">
+        <v>156</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C17" s="41">
+        <v>157</v>
+      </c>
+      <c r="C17" s="42">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="42">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="42">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.25</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="42">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="27" t="s">
+      <c r="B19" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="C19" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="D19" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="E19" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F19" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="A20" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="30">
         <f>'Financial Model'!B2</f>
         <v>1546000</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>'Financial Model'!C2</f>
         <v>2522800</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <f>'Financial Model'!D2</f>
         <v>3784600</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <f>'Financial Model'!E2</f>
         <v>4759125</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <f>'Financial Model'!F2</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="30">
         <f>'Financial Model'!B3</f>
         <v>1026431</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <f>'Financial Model'!C3</f>
         <v>1231718</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <f>'Financial Model'!D3</f>
         <v>1231718</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <f>'Financial Model'!E3</f>
         <v>1231718</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <f>'Financial Model'!F3</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="30">
         <f>'Financial Model'!B4</f>
         <v>654000</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <f>'Financial Model'!C4</f>
         <v>887860</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <f>'Financial Model'!D4</f>
         <v>1190519</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <f>'Financial Model'!E4</f>
         <v>1439088</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <f>'Financial Model'!F4</f>
         <v>1554922</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B23" s="30">
+        <v>149</v>
+      </c>
+      <c r="B23" s="31">
         <f>'Financial Model'!B6</f>
         <v>1845256</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <f>'Financial Model'!C6</f>
         <v>2209403</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <f>'Financial Model'!D6</f>
         <v>2512062</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <f>'Financial Model'!E6</f>
         <v>2745631</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <f>'Financial Model'!F6</f>
         <v>2856465</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="42">
+      <c r="A24" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="43">
         <f>'Financial Model'!B7</f>
         <v>-299256</v>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="44">
         <f>'Financial Model'!C7</f>
         <v>313397</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="44">
         <f>'Financial Model'!D7</f>
         <v>1272538</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="44">
         <f>'Financial Model'!E7</f>
         <v>2013494</v>
       </c>
-      <c r="F24" s="43">
+      <c r="F24" s="44">
         <f>'Financial Model'!F7</f>
         <v>2327935</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="30">
         <f>'Financial Model'!B8</f>
         <v>-299256</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <f>'Financial Model'!C8</f>
         <v>14141</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <f>'Financial Model'!D8</f>
         <v>1286679</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <f>'Financial Model'!E8</f>
         <v>3300173</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <f>'Financial Model'!F8</f>
         <v>5628108</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="44" t="str">
+      <c r="B26" s="45" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
-      <c r="C26" s="44">
+      <c r="C26" s="45">
         <f>'Financial Model'!C9</f>
         <v>0.0768044580368543</v>
       </c>
@@ -3464,7 +3488,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3473,85 +3497,85 @@
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="B29" s="29">
+      <c r="A29" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>12883.333333333334</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>12614</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>12615.333333333334</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>12691</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>12961</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="B30" s="41">
+      <c r="A30" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="42">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.6639269081500647</v>
       </c>
-      <c r="C30" s="41">
+      <c r="C30" s="42">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.4882345013477089</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="42">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.3254552660783174</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="42">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.25881186142410634</v>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="42">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.23758159092662604</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="B31" s="41">
+      <c r="A31" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" s="42">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.4230271668822768</v>
       </c>
-      <c r="C31" s="41">
+      <c r="C31" s="42">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.35193435864912004</v>
       </c>
-      <c r="D31" s="41">
+      <c r="D31" s="42">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.31456930719230564</v>
       </c>
-      <c r="E31" s="41">
+      <c r="E31" s="42">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.3023849972421401</v>
       </c>
-      <c r="F31" s="41">
+      <c r="F31" s="42">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.299923231232158</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32" s="45">
+      <c r="A32" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="46">
         <f>IF(B20=0,0,B24/B20)</f>
         <v>-0.1935679172056921</v>
       </c>
@@ -3574,7 +3598,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3583,62 +3607,62 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="B35" s="41">
+      <c r="A35" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" s="42">
         <v>0.02328589909443726</v>
       </c>
-      <c r="C35" s="41">
+      <c r="C35" s="42">
         <v>0.024496591089265895</v>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="42">
         <v>0.025207419542355863</v>
       </c>
-      <c r="E35" s="41">
+      <c r="E35" s="42">
         <v>0.025845087069576864</v>
       </c>
-      <c r="F35" s="41">
+      <c r="F35" s="42">
         <v>0.026078234704112337</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B36" s="41">
+      <c r="A36" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" s="42">
         <v>0.8926261319534282</v>
       </c>
-      <c r="C36" s="41">
+      <c r="C36" s="42">
         <v>0.9299191374663073</v>
       </c>
-      <c r="D36" s="41">
+      <c r="D36" s="42">
         <v>0.9483697088199545</v>
       </c>
-      <c r="E36" s="41">
+      <c r="E36" s="42">
         <v>0.9615475533842881</v>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="42">
         <v>0.9604197207005633</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="41">
+      <c r="A37" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="B37" s="42">
         <v>0.08408796895213454</v>
       </c>
-      <c r="C37" s="41">
+      <c r="C37" s="42">
         <v>0.045584271444426824</v>
       </c>
-      <c r="D37" s="41">
+      <c r="D37" s="42">
         <v>0.026422871637689586</v>
       </c>
-      <c r="E37" s="41">
+      <c r="E37" s="42">
         <v>0.012607359546135056</v>
       </c>
-      <c r="F37" s="41">
+      <c r="F37" s="42">
         <v>0.013502044595324435</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -12,6 +12,7 @@
     <sheet sheetId="5" name="Capital &amp; Debt" state="visible" r:id="rId9"/>
     <sheet sheetId="6" name="Financial Model" state="visible" r:id="rId10"/>
     <sheet sheetId="7" name="Summary" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Financial Health" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
@@ -28,13 +29,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="224">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -535,21 +538,193 @@
   </si>
   <si>
     <t>Philanthropy %</t>
+  </si>
+  <si>
+    <t>Civic Scholars Charter — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Debt Service</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>0 months</t>
+  </si>
+  <si>
+    <t>60+ months</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>○ Needs attention</t>
+  </si>
+  <si>
+    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+  </si>
+  <si>
+    <t>Secure a line of credit or bridge funding before operations begin.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 24% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 9% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 48.12x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>23.8 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>6 Healthy  |  0 Watch  |  1 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0;#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -664,6 +839,18 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -772,7 +959,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -822,11 +1009,235 @@
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3856,4 +4267,677 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:H35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="51" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="52">
+        <v>120</v>
+      </c>
+      <c r="D7" s="52">
+        <v>200</v>
+      </c>
+      <c r="E7" s="52">
+        <v>300</v>
+      </c>
+      <c r="F7" s="52">
+        <v>375</v>
+      </c>
+      <c r="G7" s="52">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="53">
+        <v>1546000</v>
+      </c>
+      <c r="D8" s="53">
+        <v>2522800</v>
+      </c>
+      <c r="E8" s="53">
+        <v>3784600</v>
+      </c>
+      <c r="F8" s="53">
+        <v>4759125</v>
+      </c>
+      <c r="G8" s="53">
+        <v>5184400</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="53">
+        <v>1026431</v>
+      </c>
+      <c r="D9" s="53">
+        <v>1231718</v>
+      </c>
+      <c r="E9" s="53">
+        <v>1231718</v>
+      </c>
+      <c r="F9" s="53">
+        <v>1231718</v>
+      </c>
+      <c r="G9" s="53">
+        <v>1231718</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="53">
+        <v>654000</v>
+      </c>
+      <c r="D10" s="53">
+        <v>887860</v>
+      </c>
+      <c r="E10" s="53">
+        <v>1190519</v>
+      </c>
+      <c r="F10" s="53">
+        <v>1439088</v>
+      </c>
+      <c r="G10" s="53">
+        <v>1554922</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="53">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="D11" s="53">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="E11" s="53">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="F11" s="53">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="G11" s="53">
+        <v>49824.605221179416</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="55">
+        <v>-299256</v>
+      </c>
+      <c r="D12" s="56">
+        <v>313397</v>
+      </c>
+      <c r="E12" s="56">
+        <v>1272538</v>
+      </c>
+      <c r="F12" s="56">
+        <v>2013494</v>
+      </c>
+      <c r="G12" s="56">
+        <v>2327935</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" s="55">
+        <v>-299256</v>
+      </c>
+      <c r="D13" s="56">
+        <v>14141</v>
+      </c>
+      <c r="E13" s="56">
+        <v>1286679</v>
+      </c>
+      <c r="F13" s="56">
+        <v>3300173</v>
+      </c>
+      <c r="G13" s="56">
+        <v>5628108</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="57">
+        <v>-0.1935679172056921</v>
+      </c>
+      <c r="D14" s="58">
+        <v>0.12422586015538291</v>
+      </c>
+      <c r="E14" s="58">
+        <v>0.3362410822808223</v>
+      </c>
+      <c r="F14" s="58">
+        <v>0.42308071336642766</v>
+      </c>
+      <c r="G14" s="58">
+        <v>0.4490268883573798</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="59">
+        <v>12883.333333333334</v>
+      </c>
+      <c r="D15" s="59">
+        <v>12614</v>
+      </c>
+      <c r="E15" s="59">
+        <v>12615.333333333334</v>
+      </c>
+      <c r="F15" s="59">
+        <v>12691</v>
+      </c>
+      <c r="G15" s="59">
+        <v>12961</v>
+      </c>
+      <c r="H15" s="60" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="C16" s="57">
+        <v>0.6639269081500647</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0.4882345013477089</v>
+      </c>
+      <c r="E16" s="58">
+        <v>0.3254552660783174</v>
+      </c>
+      <c r="F16" s="58">
+        <v>0.25881186142410634</v>
+      </c>
+      <c r="G16" s="58">
+        <v>0.23758159092662604</v>
+      </c>
+      <c r="H16" s="60" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="58">
+        <v>0.12690815006468306</v>
+      </c>
+      <c r="D17" s="58">
+        <v>0.10558030759473601</v>
+      </c>
+      <c r="E17" s="58">
+        <v>0.0943707921576917</v>
+      </c>
+      <c r="F17" s="58">
+        <v>0.09071549917264202</v>
+      </c>
+      <c r="G17" s="58">
+        <v>0.0899769693696474</v>
+      </c>
+      <c r="H17" s="60" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="57">
+        <v>-0.08695407503234152</v>
+      </c>
+      <c r="D18" s="58">
+        <v>0.15983114000317108</v>
+      </c>
+      <c r="E18" s="58">
+        <v>0.35997542672937693</v>
+      </c>
+      <c r="F18" s="58">
+        <v>0.4388031413337536</v>
+      </c>
+      <c r="G18" s="58">
+        <v>0.46249517784121597</v>
+      </c>
+      <c r="H18" s="60" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="54" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="61">
+        <v>3</v>
+      </c>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="60" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="54" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="62">
+        <v>-2.6980845990297206</v>
+      </c>
+      <c r="D20" s="63">
+        <v>8.092828798342362</v>
+      </c>
+      <c r="E20" s="63">
+        <v>27.343177009677287</v>
+      </c>
+      <c r="F20" s="63">
+        <v>41.91340785801748</v>
+      </c>
+      <c r="G20" s="63">
+        <v>48.1240140158855</v>
+      </c>
+      <c r="H20" s="60" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="54" t="s">
+        <v>191</v>
+      </c>
+      <c r="C21" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="60" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="60" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="E25" s="68"/>
+      <c r="F25" s="69" t="s">
+        <v>202</v>
+      </c>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="66" t="s">
+        <v>203</v>
+      </c>
+      <c r="C26" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="68"/>
+      <c r="F26" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" s="68"/>
+      <c r="F27" s="69" t="s">
+        <v>209</v>
+      </c>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="66" t="s">
+        <v>210</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D28" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="E28" s="68"/>
+      <c r="F28" s="69" t="s">
+        <v>212</v>
+      </c>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="66" t="s">
+        <v>213</v>
+      </c>
+      <c r="C29" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="E29" s="68"/>
+      <c r="F29" s="69" t="s">
+        <v>215</v>
+      </c>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="66" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30" s="68" t="s">
+        <v>217</v>
+      </c>
+      <c r="E30" s="68"/>
+      <c r="F30" s="69" t="s">
+        <v>218</v>
+      </c>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="66" t="s">
+        <v>219</v>
+      </c>
+      <c r="C31" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="68"/>
+      <c r="F31" s="69" t="s">
+        <v>221</v>
+      </c>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="71" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C14&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C14&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C14&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&gt;=10000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&gt;=7000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&lt;7000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BCivic Scholars Charter&amp;R&amp;8&amp;IFinancial Health</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="226">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -493,6 +493,12 @@
   </si>
   <si>
     <t>Cumulative Net Income</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>Financial Model Summary</t>
@@ -959,7 +965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1002,6 +1008,12 @@
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1049,9 +1061,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3285,7 +3294,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3510,6 +3519,26 @@
       <c r="F9" s="39">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>23.643663059060763</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3535,18 +3564,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="A1" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
-        <v>153</v>
+      <c r="A2" s="43" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3620,12 +3649,12 @@
         <v>40</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3680,24 +3709,24 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" s="42">
+        <v>159</v>
+      </c>
+      <c r="C17" s="44">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="44">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="44">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.25</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="44">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.06666666666666667</v>
       </c>
@@ -3826,23 +3855,23 @@
       <c r="A24" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="B24" s="43">
+      <c r="B24" s="45">
         <f>'Financial Model'!B7</f>
         <v>-299256</v>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="46">
         <f>'Financial Model'!C7</f>
         <v>313397</v>
       </c>
-      <c r="D24" s="44">
+      <c r="D24" s="46">
         <f>'Financial Model'!D7</f>
         <v>1272538</v>
       </c>
-      <c r="E24" s="44">
+      <c r="E24" s="46">
         <f>'Financial Model'!E7</f>
         <v>2013494</v>
       </c>
-      <c r="F24" s="44">
+      <c r="F24" s="46">
         <f>'Financial Model'!F7</f>
         <v>2327935</v>
       </c>
@@ -3876,11 +3905,11 @@
       <c r="A26" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="45" t="str">
+      <c r="B26" s="47" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
-      <c r="C26" s="45">
+      <c r="C26" s="47">
         <f>'Financial Model'!C9</f>
         <v>0.0768044580368543</v>
       </c>
@@ -3899,7 +3928,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3909,7 +3938,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B29" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
@@ -3934,59 +3963,59 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="B30" s="42">
+        <v>162</v>
+      </c>
+      <c r="B30" s="44">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.6639269081500647</v>
       </c>
-      <c r="C30" s="42">
+      <c r="C30" s="44">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.4882345013477089</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="44">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.3254552660783174</v>
       </c>
-      <c r="E30" s="42">
+      <c r="E30" s="44">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.25881186142410634</v>
       </c>
-      <c r="F30" s="42">
+      <c r="F30" s="44">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.23758159092662604</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="B31" s="42">
+        <v>163</v>
+      </c>
+      <c r="B31" s="44">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.4230271668822768</v>
       </c>
-      <c r="C31" s="42">
+      <c r="C31" s="44">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.35193435864912004</v>
       </c>
-      <c r="D31" s="42">
+      <c r="D31" s="44">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.31456930719230564</v>
       </c>
-      <c r="E31" s="42">
+      <c r="E31" s="44">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.3023849972421401</v>
       </c>
-      <c r="F31" s="42">
+      <c r="F31" s="44">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.299923231232158</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="B32" s="46">
+        <v>164</v>
+      </c>
+      <c r="B32" s="48">
         <f>IF(B20=0,0,B24/B20)</f>
         <v>-0.1935679172056921</v>
       </c>
@@ -4009,7 +4038,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -4019,61 +4048,61 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B35" s="42">
+        <v>166</v>
+      </c>
+      <c r="B35" s="44">
         <v>0.02328589909443726</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="44">
         <v>0.024496591089265895</v>
       </c>
-      <c r="D35" s="42">
+      <c r="D35" s="44">
         <v>0.025207419542355863</v>
       </c>
-      <c r="E35" s="42">
+      <c r="E35" s="44">
         <v>0.025845087069576864</v>
       </c>
-      <c r="F35" s="42">
+      <c r="F35" s="44">
         <v>0.026078234704112337</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B36" s="42">
+        <v>167</v>
+      </c>
+      <c r="B36" s="44">
         <v>0.8926261319534282</v>
       </c>
-      <c r="C36" s="42">
+      <c r="C36" s="44">
         <v>0.9299191374663073</v>
       </c>
-      <c r="D36" s="42">
+      <c r="D36" s="44">
         <v>0.9483697088199545</v>
       </c>
-      <c r="E36" s="42">
+      <c r="E36" s="44">
         <v>0.9615475533842881</v>
       </c>
-      <c r="F36" s="42">
+      <c r="F36" s="44">
         <v>0.9604197207005633</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="B37" s="42">
+        <v>168</v>
+      </c>
+      <c r="B37" s="44">
         <v>0.08408796895213454</v>
       </c>
-      <c r="C37" s="42">
+      <c r="C37" s="44">
         <v>0.045584271444426824</v>
       </c>
-      <c r="D37" s="42">
+      <c r="D37" s="44">
         <v>0.026422871637689586</v>
       </c>
-      <c r="E37" s="42">
+      <c r="E37" s="44">
         <v>0.012607359546135056</v>
       </c>
-      <c r="F37" s="42">
+      <c r="F37" s="44">
         <v>0.013502044595324435</v>
       </c>
     </row>
@@ -4286,118 +4315,118 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="B2" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="47" t="s">
-        <v>168</v>
-      </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="B3" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="48" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="F4" s="50" t="s">
+      <c r="B4" s="50" t="s">
         <v>171</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="G6" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="51" t="s">
-        <v>173</v>
+      <c r="H6" s="53" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="52">
+        <v>176</v>
+      </c>
+      <c r="C7" s="54">
         <v>120</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="54">
         <v>200</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="54">
         <v>300</v>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="54">
         <v>375</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="54">
         <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="53">
+        <v>177</v>
+      </c>
+      <c r="C8" s="55">
         <v>1546000</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="55">
         <v>2522800</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="55">
         <v>3784600</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="55">
         <v>4759125</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="55">
         <v>5184400</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="53">
+        <v>178</v>
+      </c>
+      <c r="C9" s="55">
         <v>1026431</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="55">
         <v>1231718</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="55">
         <v>1231718</v>
       </c>
-      <c r="F9" s="53">
+      <c r="F9" s="55">
         <v>1231718</v>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="55">
         <v>1231718</v>
       </c>
     </row>
@@ -4405,419 +4434,419 @@
       <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="55">
         <v>654000</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="55">
         <v>887860</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="55">
         <v>1190519</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="55">
         <v>1439088</v>
       </c>
-      <c r="G10" s="53">
+      <c r="G10" s="55">
         <v>1554922</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" s="53">
+        <v>179</v>
+      </c>
+      <c r="C11" s="55">
         <v>49824.605221179416</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="55">
         <v>49824.605221179416</v>
       </c>
-      <c r="E11" s="53">
+      <c r="E11" s="55">
         <v>49824.605221179416</v>
       </c>
-      <c r="F11" s="53">
+      <c r="F11" s="55">
         <v>49824.605221179416</v>
       </c>
-      <c r="G11" s="53">
+      <c r="G11" s="55">
         <v>49824.605221179416</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="55">
+      <c r="C12" s="57">
         <v>-299256</v>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="58">
         <v>313397</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="58">
         <v>1272538</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="58">
         <v>2013494</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="58">
         <v>2327935</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="54" t="s">
-        <v>178</v>
-      </c>
-      <c r="C13" s="55">
+      <c r="B13" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="57">
         <v>-299256</v>
       </c>
-      <c r="D13" s="56">
+      <c r="D13" s="58">
         <v>14141</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E13" s="58">
         <v>1286679</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="58">
         <v>3300173</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G13" s="58">
         <v>5628108</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="54" t="s">
-        <v>179</v>
-      </c>
-      <c r="C14" s="57">
+      <c r="B14" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="59">
         <v>-0.1935679172056921</v>
       </c>
-      <c r="D14" s="58">
+      <c r="D14" s="60">
         <v>0.12422586015538291</v>
       </c>
-      <c r="E14" s="58">
+      <c r="E14" s="60">
         <v>0.3362410822808223</v>
       </c>
-      <c r="F14" s="58">
+      <c r="F14" s="60">
         <v>0.42308071336642766</v>
       </c>
-      <c r="G14" s="58">
+      <c r="G14" s="60">
         <v>0.4490268883573798</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="54" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="59">
+      <c r="B15" s="56" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="61">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="61">
         <v>12614</v>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="61">
         <v>12615.333333333334</v>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="61">
         <v>12691</v>
       </c>
-      <c r="G15" s="59">
+      <c r="G15" s="61">
         <v>12961</v>
       </c>
-      <c r="H15" s="60" t="s">
-        <v>180</v>
+      <c r="H15" s="62" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="54" t="s">
-        <v>181</v>
-      </c>
-      <c r="C16" s="57">
+      <c r="B16" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="59">
         <v>0.6639269081500647</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D16" s="60">
         <v>0.4882345013477089</v>
       </c>
-      <c r="E16" s="58">
+      <c r="E16" s="60">
         <v>0.3254552660783174</v>
       </c>
-      <c r="F16" s="58">
+      <c r="F16" s="60">
         <v>0.25881186142410634</v>
       </c>
-      <c r="G16" s="58">
+      <c r="G16" s="60">
         <v>0.23758159092662604</v>
       </c>
-      <c r="H16" s="60" t="s">
-        <v>182</v>
+      <c r="H16" s="62" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="54" t="s">
-        <v>183</v>
-      </c>
-      <c r="C17" s="58">
+      <c r="B17" s="56" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="60">
         <v>0.12690815006468306</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D17" s="60">
         <v>0.10558030759473601</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E17" s="60">
         <v>0.0943707921576917</v>
       </c>
-      <c r="F17" s="58">
+      <c r="F17" s="60">
         <v>0.09071549917264202</v>
       </c>
-      <c r="G17" s="58">
+      <c r="G17" s="60">
         <v>0.0899769693696474</v>
       </c>
-      <c r="H17" s="60" t="s">
-        <v>184</v>
+      <c r="H17" s="62" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="C18" s="57">
+      <c r="B18" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="59">
         <v>-0.08695407503234152</v>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="60">
         <v>0.15983114000317108</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="60">
         <v>0.35997542672937693</v>
       </c>
-      <c r="F18" s="58">
+      <c r="F18" s="60">
         <v>0.4388031413337536</v>
       </c>
-      <c r="G18" s="58">
+      <c r="G18" s="60">
         <v>0.46249517784121597</v>
       </c>
-      <c r="H18" s="60" t="s">
-        <v>186</v>
+      <c r="H18" s="62" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="54" t="s">
-        <v>187</v>
-      </c>
-      <c r="C19" s="61">
+      <c r="B19" s="56" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="63">
         <v>3</v>
       </c>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="60" t="s">
-        <v>188</v>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="62" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="54" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="62">
+      <c r="B20" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20" s="64">
         <v>-2.6980845990297206</v>
       </c>
-      <c r="D20" s="63">
+      <c r="D20" s="65">
         <v>8.092828798342362</v>
       </c>
-      <c r="E20" s="63">
+      <c r="E20" s="65">
         <v>27.343177009677287</v>
       </c>
-      <c r="F20" s="63">
+      <c r="F20" s="65">
         <v>41.91340785801748</v>
       </c>
-      <c r="G20" s="63">
+      <c r="G20" s="65">
         <v>48.1240140158855</v>
       </c>
-      <c r="H20" s="60" t="s">
-        <v>190</v>
+      <c r="H20" s="62" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="54" t="s">
-        <v>191</v>
-      </c>
-      <c r="C21" s="64" t="s">
+      <c r="B21" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="60" t="s">
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="62" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>192</v>
-      </c>
-      <c r="C22" s="65" t="s">
-        <v>193</v>
-      </c>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="60" t="s">
+      <c r="B22" s="56" t="s">
         <v>194</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="62" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="66" t="s">
-        <v>199</v>
-      </c>
-      <c r="C25" s="67" t="s">
-        <v>200</v>
-      </c>
-      <c r="D25" s="68" t="s">
+      <c r="B25" s="68" t="s">
         <v>201</v>
       </c>
-      <c r="E25" s="68"/>
-      <c r="F25" s="69" t="s">
+      <c r="C25" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
+      <c r="D25" s="69" t="s">
+        <v>203</v>
+      </c>
+      <c r="E25" s="69"/>
+      <c r="F25" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="66" t="s">
-        <v>203</v>
-      </c>
-      <c r="C26" s="70" t="s">
-        <v>204</v>
-      </c>
-      <c r="D26" s="68" t="s">
+      <c r="B26" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="E26" s="68"/>
-      <c r="F26" s="69" t="s">
+      <c r="C26" s="71" t="s">
         <v>206</v>
       </c>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
+      <c r="D26" s="69" t="s">
+        <v>207</v>
+      </c>
+      <c r="E26" s="69"/>
+      <c r="F26" s="70" t="s">
+        <v>208</v>
+      </c>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="66" t="s">
-        <v>207</v>
-      </c>
-      <c r="C27" s="67" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="68" t="s">
-        <v>208</v>
-      </c>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69" t="s">
+      <c r="B27" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
+      <c r="C27" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D27" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="E27" s="69"/>
+      <c r="F27" s="70" t="s">
+        <v>211</v>
+      </c>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="66" t="s">
-        <v>210</v>
-      </c>
-      <c r="C28" s="67" t="s">
-        <v>200</v>
-      </c>
-      <c r="D28" s="68" t="s">
-        <v>211</v>
-      </c>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69" t="s">
+      <c r="B28" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
+      <c r="C28" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D28" s="69" t="s">
+        <v>213</v>
+      </c>
+      <c r="E28" s="69"/>
+      <c r="F28" s="70" t="s">
+        <v>214</v>
+      </c>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="66" t="s">
-        <v>213</v>
-      </c>
-      <c r="C29" s="67" t="s">
-        <v>200</v>
-      </c>
-      <c r="D29" s="68" t="s">
-        <v>214</v>
-      </c>
-      <c r="E29" s="68"/>
-      <c r="F29" s="69" t="s">
+      <c r="B29" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
+      <c r="C29" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>216</v>
+      </c>
+      <c r="E29" s="69"/>
+      <c r="F29" s="70" t="s">
+        <v>217</v>
+      </c>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="66" t="s">
-        <v>216</v>
-      </c>
-      <c r="C30" s="67" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="68" t="s">
-        <v>217</v>
-      </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69" t="s">
+      <c r="B30" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
+      <c r="C30" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" s="69" t="s">
+        <v>219</v>
+      </c>
+      <c r="E30" s="69"/>
+      <c r="F30" s="70" t="s">
+        <v>220</v>
+      </c>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="66" t="s">
-        <v>219</v>
-      </c>
-      <c r="C31" s="67" t="s">
-        <v>200</v>
-      </c>
-      <c r="D31" s="68" t="s">
-        <v>220</v>
-      </c>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69" t="s">
+      <c r="B31" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
+      <c r="C31" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D31" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" s="69"/>
+      <c r="F31" s="70" t="s">
+        <v>223</v>
+      </c>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="66" t="s">
+      <c r="B33" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="54" t="s">
-        <v>222</v>
-      </c>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
+      <c r="C33" s="56" t="s">
+        <v>224</v>
+      </c>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="71" t="s">
-        <v>223</v>
-      </c>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
+      <c r="B35" s="72" t="s">
+        <v>225</v>
+      </c>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -4956,10 +4956,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="226">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -1058,7 +1058,9 @@
     <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4664,13 +4666,26 @@
       <c r="B21" s="56" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
+      <c r="C21" s="66" t="str">
+        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="41" t="str">
+        <f>IF('Financial Model'!C8&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E21" s="66" t="str">
+        <f>IF('Financial Model'!D8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="66" t="str">
+        <f>IF('Financial Model'!E8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="66" t="str">
+        <f>IF('Financial Model'!F8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="62" t="s">
         <v>66</v>
       </c>
@@ -4849,11 +4864,10 @@
       <c r="H35" s="72"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -4934,10 +4948,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="225">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -621,13 +621,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>0 months</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -858,7 +855,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -893,6 +890,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -965,7 +967,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1051,7 +1053,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="170" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1061,7 +1065,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4631,10 +4640,18 @@
       <c r="C19" s="63">
         <v>3</v>
       </c>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
+      <c r="D19" s="63">
+        <v>3</v>
+      </c>
+      <c r="E19" s="63">
+        <v>3</v>
+      </c>
+      <c r="F19" s="63">
+        <v>3</v>
+      </c>
+      <c r="G19" s="63">
+        <v>3</v>
+      </c>
       <c r="H19" s="62" t="s">
         <v>190</v>
       </c>
@@ -4671,19 +4688,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="41" t="str">
-        <f>IF('Financial Model'!C8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
       <c r="E21" s="66" t="str">
-        <f>IF('Financial Model'!D8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="66" t="str">
-        <f>IF('Financial Model'!E8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="66" t="str">
-        <f>IF('Financial Model'!F8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="62" t="s">
@@ -4694,181 +4711,187 @@
       <c r="B22" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="C22" s="67" t="s">
+      <c r="C22" s="67">
+        <v>-2</v>
+      </c>
+      <c r="D22" s="67">
+        <v>0</v>
+      </c>
+      <c r="E22" s="67">
+        <v>6</v>
+      </c>
+      <c r="F22" s="68">
+        <v>15</v>
+      </c>
+      <c r="G22" s="63">
+        <v>24</v>
+      </c>
+      <c r="H22" s="62" t="s">
         <v>195</v>
-      </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="62" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>198</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>199</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="69" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="D25" s="70" t="s">
         <v>202</v>
       </c>
-      <c r="D25" s="69" t="s">
+      <c r="E25" s="70"/>
+      <c r="F25" s="71" t="s">
         <v>203</v>
       </c>
-      <c r="E25" s="69"/>
-      <c r="F25" s="70" t="s">
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="68" t="s">
+      <c r="C26" s="72" t="s">
         <v>205</v>
       </c>
-      <c r="C26" s="71" t="s">
+      <c r="D26" s="70" t="s">
         <v>206</v>
       </c>
-      <c r="D26" s="69" t="s">
+      <c r="E26" s="70"/>
+      <c r="F26" s="71" t="s">
         <v>207</v>
       </c>
-      <c r="E26" s="69"/>
-      <c r="F26" s="70" t="s">
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="69" t="s">
         <v>208</v>
       </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="68" t="s">
+      <c r="C27" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="70" t="s">
         <v>209</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D27" s="69" t="s">
+      <c r="E27" s="70"/>
+      <c r="F27" s="71" t="s">
         <v>210</v>
       </c>
-      <c r="E27" s="69"/>
-      <c r="F27" s="70" t="s">
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="69" t="s">
         <v>211</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="68" t="s">
+      <c r="C28" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D28" s="70" t="s">
         <v>212</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D28" s="69" t="s">
+      <c r="E28" s="70"/>
+      <c r="F28" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="E28" s="69"/>
-      <c r="F28" s="70" t="s">
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="69" t="s">
         <v>214</v>
       </c>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="68" t="s">
+      <c r="C29" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D29" s="70" t="s">
         <v>215</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D29" s="69" t="s">
+      <c r="E29" s="70"/>
+      <c r="F29" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="E29" s="69"/>
-      <c r="F29" s="70" t="s">
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="69" t="s">
         <v>217</v>
       </c>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="68" t="s">
+      <c r="C30" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" s="70" t="s">
         <v>218</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D30" s="69" t="s">
+      <c r="E30" s="70"/>
+      <c r="F30" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="E30" s="69"/>
-      <c r="F30" s="70" t="s">
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="69" t="s">
         <v>220</v>
       </c>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="68" t="s">
+      <c r="C31" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="70" t="s">
         <v>221</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D31" s="69" t="s">
+      <c r="E31" s="70"/>
+      <c r="F31" s="71" t="s">
         <v>222</v>
       </c>
-      <c r="E31" s="69"/>
-      <c r="F31" s="70" t="s">
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="56" t="s">
         <v>223</v>
-      </c>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="68" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="56" t="s">
-        <v>224</v>
       </c>
       <c r="D33" s="56"/>
       <c r="E33" s="56"/>
       <c r="F33" s="56"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="72" t="s">
-        <v>225</v>
-      </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
+      <c r="B35" s="73" t="s">
+        <v>224</v>
+      </c>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -675,7 +675,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 9% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 6% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -967,7 +967,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1053,6 +1053,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4591,20 +4594,20 @@
       <c r="B17" s="56" t="s">
         <v>185</v>
       </c>
-      <c r="C17" s="60">
-        <v>0.12690815006468306</v>
+      <c r="C17" s="63">
+        <v>0.18240620957309184</v>
       </c>
       <c r="D17" s="60">
-        <v>0.10558030759473601</v>
+        <v>0.1151339781195497</v>
       </c>
       <c r="E17" s="60">
-        <v>0.0943707921576917</v>
+        <v>0.07904835385509698</v>
       </c>
       <c r="F17" s="60">
-        <v>0.09071549917264202</v>
+        <v>0.06474930412628371</v>
       </c>
       <c r="G17" s="60">
-        <v>0.0899769693696474</v>
+        <v>0.06122075900007716</v>
       </c>
       <c r="H17" s="62" t="s">
         <v>186</v>
@@ -4637,19 +4640,19 @@
       <c r="B19" s="56" t="s">
         <v>189</v>
       </c>
-      <c r="C19" s="63">
+      <c r="C19" s="64">
         <v>3</v>
       </c>
-      <c r="D19" s="63">
+      <c r="D19" s="64">
         <v>3</v>
       </c>
-      <c r="E19" s="63">
+      <c r="E19" s="64">
         <v>3</v>
       </c>
-      <c r="F19" s="63">
+      <c r="F19" s="64">
         <v>3</v>
       </c>
-      <c r="G19" s="63">
+      <c r="G19" s="64">
         <v>3</v>
       </c>
       <c r="H19" s="62" t="s">
@@ -4660,19 +4663,19 @@
       <c r="B20" s="56" t="s">
         <v>191</v>
       </c>
-      <c r="C20" s="64">
+      <c r="C20" s="65">
         <v>-2.6980845990297206</v>
       </c>
-      <c r="D20" s="65">
+      <c r="D20" s="66">
         <v>8.092828798342362</v>
       </c>
-      <c r="E20" s="65">
+      <c r="E20" s="66">
         <v>27.343177009677287</v>
       </c>
-      <c r="F20" s="65">
+      <c r="F20" s="66">
         <v>41.91340785801748</v>
       </c>
-      <c r="G20" s="65">
+      <c r="G20" s="66">
         <v>48.1240140158855</v>
       </c>
       <c r="H20" s="62" t="s">
@@ -4683,7 +4686,7 @@
       <c r="B21" s="56" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="66" t="str">
+      <c r="C21" s="67" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -4691,15 +4694,15 @@
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="66" t="str">
+      <c r="E21" s="67" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="66" t="str">
+      <c r="F21" s="67" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="66" t="str">
+      <c r="G21" s="67" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -4711,19 +4714,19 @@
       <c r="B22" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="C22" s="67">
+      <c r="C22" s="68">
         <v>-2</v>
       </c>
-      <c r="D22" s="67">
+      <c r="D22" s="68">
         <v>0</v>
       </c>
-      <c r="E22" s="67">
+      <c r="E22" s="68">
         <v>6</v>
       </c>
-      <c r="F22" s="68">
+      <c r="F22" s="69">
         <v>15</v>
       </c>
-      <c r="G22" s="63">
+      <c r="G22" s="64">
         <v>24</v>
       </c>
       <c r="H22" s="62" t="s">
@@ -4748,126 +4751,126 @@
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="70" t="s">
         <v>200</v>
       </c>
       <c r="C25" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="71" t="s">
         <v>202</v>
       </c>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71" t="s">
+      <c r="E25" s="71"/>
+      <c r="F25" s="72" t="s">
         <v>203</v>
       </c>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="70" t="s">
         <v>204</v>
       </c>
-      <c r="C26" s="72" t="s">
+      <c r="C26" s="73" t="s">
         <v>205</v>
       </c>
-      <c r="D26" s="70" t="s">
+      <c r="D26" s="71" t="s">
         <v>206</v>
       </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="71" t="s">
+      <c r="E26" s="71"/>
+      <c r="F26" s="72" t="s">
         <v>207</v>
       </c>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="69" t="s">
+      <c r="B27" s="70" t="s">
         <v>208</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="70" t="s">
+      <c r="D27" s="71" t="s">
         <v>209</v>
       </c>
-      <c r="E27" s="70"/>
-      <c r="F27" s="71" t="s">
+      <c r="E27" s="71"/>
+      <c r="F27" s="72" t="s">
         <v>210</v>
       </c>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="69" t="s">
+      <c r="B28" s="70" t="s">
         <v>211</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="D28" s="70" t="s">
+      <c r="D28" s="71" t="s">
         <v>212</v>
       </c>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71" t="s">
+      <c r="E28" s="71"/>
+      <c r="F28" s="72" t="s">
         <v>213</v>
       </c>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="69" t="s">
+      <c r="B29" s="70" t="s">
         <v>214</v>
       </c>
       <c r="C29" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="D29" s="70" t="s">
+      <c r="D29" s="71" t="s">
         <v>215</v>
       </c>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71" t="s">
+      <c r="E29" s="71"/>
+      <c r="F29" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="69" t="s">
+      <c r="B30" s="70" t="s">
         <v>217</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="D30" s="70" t="s">
+      <c r="D30" s="71" t="s">
         <v>218</v>
       </c>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71" t="s">
+      <c r="E30" s="71"/>
+      <c r="F30" s="72" t="s">
         <v>219</v>
       </c>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="69" t="s">
+      <c r="B31" s="70" t="s">
         <v>220</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="D31" s="70" t="s">
+      <c r="D31" s="71" t="s">
         <v>221</v>
       </c>
-      <c r="E31" s="70"/>
-      <c r="F31" s="71" t="s">
+      <c r="E31" s="71"/>
+      <c r="F31" s="72" t="s">
         <v>222</v>
       </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="70" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="56" t="s">
@@ -4878,15 +4881,15 @@
       <c r="F33" s="56"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="73" t="s">
+      <c r="B35" s="74" t="s">
         <v>224</v>
       </c>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -57,7 +57,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 26, 2026</t>
+    <t>March 27, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -549,7 +549,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -2077,25 +2077,25 @@
       <c r="A11" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="31" t="str">
+      <c r="B11" s="31">
         <f>SUM(B9:B10)</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="31" t="str">
+        <v>130000</v>
+      </c>
+      <c r="C11" s="31">
         <f>SUM(C9:C10)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="31" t="str">
+        <v>115000</v>
+      </c>
+      <c r="D11" s="31">
         <f>SUM(D9:D10)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="31" t="str">
+        <v>100000</v>
+      </c>
+      <c r="E11" s="31">
         <f>SUM(E9:E10)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="31" t="str">
+        <v>60000</v>
+      </c>
+      <c r="F11" s="31">
         <f>SUM(F9:F10)</f>
-        <v>0</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="227">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -625,6 +625,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -4318,7 +4324,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4733,170 +4739,191 @@
         <v>195</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="56" t="s">
         <v>196</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C23" s="68">
+        <v>0</v>
+      </c>
+      <c r="D23" s="68">
+        <v>2</v>
+      </c>
+      <c r="E23" s="64">
+        <v>190</v>
+      </c>
+      <c r="F23" s="64">
+        <v>443</v>
+      </c>
+      <c r="G23" s="64">
+        <v>724</v>
+      </c>
+      <c r="H23" s="62" t="s">
         <v>197</v>
       </c>
-      <c r="D24" s="8" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="70" t="s">
+      <c r="D25" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="E25" s="8"/>
+      <c r="F25" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="71" t="s">
-        <v>202</v>
-      </c>
-      <c r="E25" s="71"/>
-      <c r="F25" s="72" t="s">
-        <v>203</v>
-      </c>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="71" t="s">
         <v>204</v>
-      </c>
-      <c r="C26" s="73" t="s">
-        <v>205</v>
-      </c>
-      <c r="D26" s="71" t="s">
-        <v>206</v>
       </c>
       <c r="E26" s="71"/>
       <c r="F26" s="72" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G26" s="72"/>
       <c r="H26" s="72"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="70" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" s="73" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" s="71" t="s">
         <v>208</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D27" s="71" t="s">
-        <v>209</v>
       </c>
       <c r="E27" s="71"/>
       <c r="F27" s="72" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G27" s="72"/>
       <c r="H27" s="72"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="70" t="s">
+        <v>210</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="D28" s="71" t="s">
         <v>211</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D28" s="71" t="s">
-        <v>212</v>
       </c>
       <c r="E28" s="71"/>
       <c r="F28" s="72" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G28" s="72"/>
       <c r="H28" s="72"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="70" t="s">
+        <v>213</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="D29" s="71" t="s">
         <v>214</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D29" s="71" t="s">
-        <v>215</v>
       </c>
       <c r="E29" s="71"/>
       <c r="F29" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G29" s="72"/>
       <c r="H29" s="72"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="70" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="71" t="s">
         <v>217</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D30" s="71" t="s">
-        <v>218</v>
       </c>
       <c r="E30" s="71"/>
       <c r="F30" s="72" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G30" s="72"/>
       <c r="H30" s="72"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="70" t="s">
+        <v>219</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="71" t="s">
         <v>220</v>
-      </c>
-      <c r="C31" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="71" t="s">
-        <v>221</v>
       </c>
       <c r="E31" s="71"/>
       <c r="F31" s="72" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G31" s="72"/>
       <c r="H31" s="72"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="70" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="70" t="s">
+        <v>222</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="71" t="s">
+        <v>223</v>
+      </c>
+      <c r="E32" s="71"/>
+      <c r="F32" s="72" t="s">
+        <v>224</v>
+      </c>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="56" t="s">
-        <v>223</v>
-      </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="74" t="s">
-        <v>224</v>
-      </c>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="74"/>
+      <c r="C34" s="56" t="s">
+        <v>225</v>
+      </c>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="74" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="74"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="74"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -4911,8 +4938,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="232">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -586,6 +586,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -973,7 +988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1059,6 +1074,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4324,7 +4351,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4573,365 +4600,440 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="56" t="s">
         <v>183</v>
       </c>
-      <c r="C16" s="59">
-        <v>0.6639269081500647</v>
-      </c>
-      <c r="D16" s="60">
-        <v>0.4882345013477089</v>
-      </c>
-      <c r="E16" s="60">
-        <v>0.3254552660783174</v>
-      </c>
-      <c r="F16" s="60">
-        <v>0.25881186142410634</v>
-      </c>
-      <c r="G16" s="60">
-        <v>0.23758159092662604</v>
-      </c>
-      <c r="H16" s="62" t="s">
+      <c r="C16" s="63">
+        <v>14418.796710176493</v>
+      </c>
+      <c r="D16" s="63">
+        <v>10847.013026105897</v>
+      </c>
+      <c r="E16" s="63">
+        <v>8240.205350737264</v>
+      </c>
+      <c r="F16" s="63">
+        <v>7255.014947256478</v>
+      </c>
+      <c r="G16" s="63">
+        <v>7091.161513052948</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="56" t="s">
+      <c r="C17" s="55">
+        <v>700</v>
+      </c>
+      <c r="D17" s="55">
+        <v>721</v>
+      </c>
+      <c r="E17" s="55">
+        <v>743</v>
+      </c>
+      <c r="F17" s="55">
+        <v>765</v>
+      </c>
+      <c r="G17" s="55">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C17" s="63">
-        <v>0.18240620957309184</v>
-      </c>
-      <c r="D17" s="60">
-        <v>0.1151339781195497</v>
-      </c>
-      <c r="E17" s="60">
-        <v>0.07904835385509698</v>
-      </c>
-      <c r="F17" s="60">
-        <v>0.06474930412628371</v>
-      </c>
-      <c r="G17" s="60">
-        <v>0.06122075900007716</v>
-      </c>
-      <c r="H17" s="62" t="s">
+      <c r="C18" s="64">
+        <v>2350</v>
+      </c>
+      <c r="D18" s="61">
+        <v>1452.3</v>
+      </c>
+      <c r="E18" s="61">
+        <v>997.2213333333334</v>
+      </c>
+      <c r="F18" s="61">
+        <v>821.7334186666667</v>
+      </c>
+      <c r="G18" s="61">
+        <v>793.4822574000001</v>
+      </c>
+      <c r="H18" s="62" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="56" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="59">
-        <v>-0.08695407503234152</v>
-      </c>
-      <c r="D18" s="60">
-        <v>0.15983114000317108</v>
-      </c>
-      <c r="E18" s="60">
-        <v>0.35997542672937693</v>
-      </c>
-      <c r="F18" s="60">
-        <v>0.4388031413337536</v>
-      </c>
-      <c r="G18" s="60">
-        <v>0.46249517784121597</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="C19" s="64">
-        <v>3</v>
-      </c>
-      <c r="D19" s="64">
-        <v>3</v>
-      </c>
-      <c r="E19" s="64">
-        <v>3</v>
-      </c>
-      <c r="F19" s="64">
-        <v>3</v>
-      </c>
-      <c r="G19" s="64">
-        <v>3</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>190</v>
+      <c r="C19" s="65">
+        <v>-2493.8</v>
+      </c>
+      <c r="D19" s="66">
+        <v>1566.985</v>
+      </c>
+      <c r="E19" s="66">
+        <v>4241.793333333333</v>
+      </c>
+      <c r="F19" s="66">
+        <v>5369.317333333333</v>
+      </c>
+      <c r="G19" s="66">
+        <v>5819.8375</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="56" t="s">
-        <v>191</v>
-      </c>
-      <c r="C20" s="65">
-        <v>-2.6980845990297206</v>
-      </c>
-      <c r="D20" s="66">
-        <v>8.092828798342362</v>
-      </c>
-      <c r="E20" s="66">
-        <v>27.343177009677287</v>
-      </c>
-      <c r="F20" s="66">
-        <v>41.91340785801748</v>
-      </c>
-      <c r="G20" s="66">
-        <v>48.1240140158855</v>
+        <v>188</v>
+      </c>
+      <c r="C20" s="59">
+        <v>0.6639269081500647</v>
+      </c>
+      <c r="D20" s="60">
+        <v>0.4882345013477089</v>
+      </c>
+      <c r="E20" s="60">
+        <v>0.3254552660783174</v>
+      </c>
+      <c r="F20" s="60">
+        <v>0.25881186142410634</v>
+      </c>
+      <c r="G20" s="60">
+        <v>0.23758159092662604</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C21" s="67">
+        <v>0.18240620957309184</v>
+      </c>
+      <c r="D21" s="60">
+        <v>0.1151339781195497</v>
+      </c>
+      <c r="E21" s="60">
+        <v>0.07904835385509698</v>
+      </c>
+      <c r="F21" s="60">
+        <v>0.06474930412628371</v>
+      </c>
+      <c r="G21" s="60">
+        <v>0.06122075900007716</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="59">
+        <v>-0.08695407503234152</v>
+      </c>
+      <c r="D22" s="60">
+        <v>0.15983114000317108</v>
+      </c>
+      <c r="E22" s="60">
+        <v>0.35997542672937693</v>
+      </c>
+      <c r="F22" s="60">
+        <v>0.4388031413337536</v>
+      </c>
+      <c r="G22" s="60">
+        <v>0.46249517784121597</v>
+      </c>
+      <c r="H22" s="62" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="67" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="56" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="68">
+        <v>3</v>
+      </c>
+      <c r="D23" s="68">
+        <v>3</v>
+      </c>
+      <c r="E23" s="68">
+        <v>3</v>
+      </c>
+      <c r="F23" s="68">
+        <v>3</v>
+      </c>
+      <c r="G23" s="68">
+        <v>3</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" s="69">
+        <v>-2.6980845990297206</v>
+      </c>
+      <c r="D24" s="70">
+        <v>8.092828798342362</v>
+      </c>
+      <c r="E24" s="70">
+        <v>27.343177009677287</v>
+      </c>
+      <c r="F24" s="70">
+        <v>41.91340785801748</v>
+      </c>
+      <c r="G24" s="70">
+        <v>48.1240140158855</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" s="71" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="41" t="str">
+      <c r="D25" s="41" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="67" t="str">
+      <c r="E25" s="71" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="67" t="str">
+      <c r="F25" s="71" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="67" t="str">
+      <c r="G25" s="71" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="62" t="s">
+      <c r="H25" s="62" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="56" t="s">
-        <v>194</v>
-      </c>
-      <c r="C22" s="68">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="C26" s="72">
         <v>-2</v>
       </c>
-      <c r="D22" s="68">
+      <c r="D26" s="72">
         <v>0</v>
       </c>
-      <c r="E22" s="68">
+      <c r="E26" s="72">
         <v>6</v>
       </c>
-      <c r="F22" s="69">
+      <c r="F26" s="73">
         <v>15</v>
       </c>
-      <c r="G22" s="64">
+      <c r="G26" s="68">
         <v>24</v>
       </c>
-      <c r="H22" s="62" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="56" t="s">
-        <v>196</v>
-      </c>
-      <c r="C23" s="68">
+      <c r="H26" s="62" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="72">
         <v>0</v>
       </c>
-      <c r="D23" s="68">
+      <c r="D27" s="72">
         <v>2</v>
       </c>
-      <c r="E23" s="64">
+      <c r="E27" s="68">
         <v>190</v>
       </c>
-      <c r="F23" s="64">
+      <c r="F27" s="68">
         <v>443</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G27" s="68">
         <v>724</v>
       </c>
-      <c r="H23" s="62" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="70" t="s">
+      <c r="H27" s="62" t="s">
         <v>202</v>
       </c>
-      <c r="C26" s="41" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="C29" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="E26" s="71"/>
-      <c r="F26" s="72" t="s">
+      <c r="D29" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="70" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C27" s="73" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="D27" s="71" t="s">
+      <c r="C30" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="E27" s="71"/>
-      <c r="F27" s="72" t="s">
+      <c r="D30" s="75" t="s">
         <v>209</v>
       </c>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="70" t="s">
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="D28" s="71" t="s">
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="74" t="s">
         <v>211</v>
       </c>
-      <c r="E28" s="71"/>
-      <c r="F28" s="72" t="s">
+      <c r="C31" s="77" t="s">
         <v>212</v>
       </c>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="70" t="s">
+      <c r="D31" s="75" t="s">
         <v>213</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="D29" s="71" t="s">
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
         <v>214</v>
       </c>
-      <c r="E29" s="71"/>
-      <c r="F29" s="72" t="s">
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="74" t="s">
         <v>215</v>
       </c>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="70" t="s">
+      <c r="C32" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D32" s="75" t="s">
         <v>216</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="D30" s="71" t="s">
+      <c r="E32" s="75"/>
+      <c r="F32" s="76" t="s">
         <v>217</v>
       </c>
-      <c r="E30" s="71"/>
-      <c r="F30" s="72" t="s">
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="70" t="s">
+      <c r="C33" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D33" s="75" t="s">
         <v>219</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="D31" s="71" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="E31" s="71"/>
-      <c r="F31" s="72" t="s">
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="74" t="s">
         <v>221</v>
       </c>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="70" t="s">
+      <c r="C34" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D34" s="75" t="s">
         <v>222</v>
       </c>
-      <c r="C32" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="D32" s="71" t="s">
+      <c r="E34" s="75"/>
+      <c r="F34" s="76" t="s">
         <v>223</v>
       </c>
-      <c r="E32" s="71"/>
-      <c r="F32" s="72" t="s">
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="74" t="s">
         <v>224</v>
       </c>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="70" t="s">
+      <c r="C35" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D35" s="75" t="s">
+        <v>225</v>
+      </c>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76" t="s">
+        <v>226</v>
+      </c>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="74" t="s">
+        <v>227</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D36" s="75" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" s="75"/>
+      <c r="F36" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="56" t="s">
-        <v>225</v>
-      </c>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="74" t="s">
-        <v>226</v>
-      </c>
-      <c r="C36" s="74"/>
-      <c r="D36" s="74"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="74"/>
+      <c r="C38" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -4940,8 +5042,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4987,48 +5097,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="225">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -588,21 +588,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -640,12 +625,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>Days Cash on Hand</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -988,7 +967,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1074,18 +1053,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4351,7 +4318,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4600,458 +4567,352 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="56" t="s">
         <v>183</v>
       </c>
-      <c r="C16" s="63">
-        <v>14418.796710176493</v>
-      </c>
-      <c r="D16" s="63">
-        <v>10847.013026105897</v>
-      </c>
-      <c r="E16" s="63">
-        <v>8240.205350737264</v>
-      </c>
-      <c r="F16" s="63">
-        <v>7255.014947256478</v>
-      </c>
-      <c r="G16" s="63">
-        <v>7091.161513052948</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="C16" s="59">
+        <v>0.6639269081500647</v>
+      </c>
+      <c r="D16" s="60">
+        <v>0.4882345013477089</v>
+      </c>
+      <c r="E16" s="60">
+        <v>0.3254552660783174</v>
+      </c>
+      <c r="F16" s="60">
+        <v>0.25881186142410634</v>
+      </c>
+      <c r="G16" s="60">
+        <v>0.23758159092662604</v>
+      </c>
+      <c r="H16" s="62" t="s">
         <v>184</v>
       </c>
-      <c r="C17" s="55">
-        <v>700</v>
-      </c>
-      <c r="D17" s="55">
-        <v>721</v>
-      </c>
-      <c r="E17" s="55">
-        <v>743</v>
-      </c>
-      <c r="F17" s="55">
-        <v>765</v>
-      </c>
-      <c r="G17" s="55">
-        <v>788</v>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="56" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="63">
+        <v>0.18240620957309184</v>
+      </c>
+      <c r="D17" s="60">
+        <v>0.1151339781195497</v>
+      </c>
+      <c r="E17" s="60">
+        <v>0.07904835385509698</v>
+      </c>
+      <c r="F17" s="60">
+        <v>0.06474930412628371</v>
+      </c>
+      <c r="G17" s="60">
+        <v>0.06122075900007716</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C18" s="64">
-        <v>2350</v>
-      </c>
-      <c r="D18" s="61">
-        <v>1452.3</v>
-      </c>
-      <c r="E18" s="61">
-        <v>997.2213333333334</v>
-      </c>
-      <c r="F18" s="61">
-        <v>821.7334186666667</v>
-      </c>
-      <c r="G18" s="61">
-        <v>793.4822574000001</v>
+      <c r="B18" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="59">
+        <v>-0.08695407503234152</v>
+      </c>
+      <c r="D18" s="60">
+        <v>0.15983114000317108</v>
+      </c>
+      <c r="E18" s="60">
+        <v>0.35997542672937693</v>
+      </c>
+      <c r="F18" s="60">
+        <v>0.4388031413337536</v>
+      </c>
+      <c r="G18" s="60">
+        <v>0.46249517784121597</v>
       </c>
       <c r="H18" s="62" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="56" t="s">
-        <v>187</v>
-      </c>
-      <c r="C19" s="65">
-        <v>-2493.8</v>
-      </c>
-      <c r="D19" s="66">
-        <v>1566.985</v>
-      </c>
-      <c r="E19" s="66">
-        <v>4241.793333333333</v>
-      </c>
-      <c r="F19" s="66">
-        <v>5369.317333333333</v>
-      </c>
-      <c r="G19" s="66">
-        <v>5819.8375</v>
+        <v>189</v>
+      </c>
+      <c r="C19" s="64">
+        <v>3</v>
+      </c>
+      <c r="D19" s="64">
+        <v>3</v>
+      </c>
+      <c r="E19" s="64">
+        <v>3</v>
+      </c>
+      <c r="F19" s="64">
+        <v>3</v>
+      </c>
+      <c r="G19" s="64">
+        <v>3</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="56" t="s">
-        <v>188</v>
-      </c>
-      <c r="C20" s="59">
-        <v>0.6639269081500647</v>
-      </c>
-      <c r="D20" s="60">
-        <v>0.4882345013477089</v>
-      </c>
-      <c r="E20" s="60">
-        <v>0.3254552660783174</v>
-      </c>
-      <c r="F20" s="60">
-        <v>0.25881186142410634</v>
-      </c>
-      <c r="G20" s="60">
-        <v>0.23758159092662604</v>
+        <v>191</v>
+      </c>
+      <c r="C20" s="65">
+        <v>-2.6980845990297206</v>
+      </c>
+      <c r="D20" s="66">
+        <v>8.092828798342362</v>
+      </c>
+      <c r="E20" s="66">
+        <v>27.343177009677287</v>
+      </c>
+      <c r="F20" s="66">
+        <v>41.91340785801748</v>
+      </c>
+      <c r="G20" s="66">
+        <v>48.1240140158855</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="56" t="s">
-        <v>190</v>
-      </c>
-      <c r="C21" s="67">
-        <v>0.18240620957309184</v>
-      </c>
-      <c r="D21" s="60">
-        <v>0.1151339781195497</v>
-      </c>
-      <c r="E21" s="60">
-        <v>0.07904835385509698</v>
-      </c>
-      <c r="F21" s="60">
-        <v>0.06474930412628371</v>
-      </c>
-      <c r="G21" s="60">
-        <v>0.06122075900007716</v>
+        <v>193</v>
+      </c>
+      <c r="C21" s="67" t="str">
+        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="41" t="str">
+        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E21" s="67" t="str">
+        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="67" t="str">
+        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="67" t="str">
+        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="62" t="s">
-        <v>191</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="56" t="s">
-        <v>192</v>
-      </c>
-      <c r="C22" s="59">
-        <v>-0.08695407503234152</v>
-      </c>
-      <c r="D22" s="60">
-        <v>0.15983114000317108</v>
-      </c>
-      <c r="E22" s="60">
-        <v>0.35997542672937693</v>
-      </c>
-      <c r="F22" s="60">
-        <v>0.4388031413337536</v>
-      </c>
-      <c r="G22" s="60">
-        <v>0.46249517784121597</v>
+        <v>194</v>
+      </c>
+      <c r="C22" s="68">
+        <v>-2</v>
+      </c>
+      <c r="D22" s="68">
+        <v>0</v>
+      </c>
+      <c r="E22" s="68">
+        <v>6</v>
+      </c>
+      <c r="F22" s="69">
+        <v>15</v>
+      </c>
+      <c r="G22" s="64">
+        <v>24</v>
       </c>
       <c r="H22" s="62" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="56" t="s">
-        <v>194</v>
-      </c>
-      <c r="C23" s="68">
-        <v>3</v>
-      </c>
-      <c r="D23" s="68">
-        <v>3</v>
-      </c>
-      <c r="E23" s="68">
-        <v>3</v>
-      </c>
-      <c r="F23" s="68">
-        <v>3</v>
-      </c>
-      <c r="G23" s="68">
-        <v>3</v>
-      </c>
-      <c r="H23" s="62" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="56" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C24" s="69">
-        <v>-2.6980845990297206</v>
-      </c>
-      <c r="D24" s="70">
-        <v>8.092828798342362</v>
-      </c>
-      <c r="E24" s="70">
-        <v>27.343177009677287</v>
-      </c>
-      <c r="F24" s="70">
-        <v>41.91340785801748</v>
-      </c>
-      <c r="G24" s="70">
-        <v>48.1240140158855</v>
-      </c>
-      <c r="H24" s="62" t="s">
+      <c r="C24" s="8" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="56" t="s">
+      <c r="D24" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C25" s="71" t="str">
-        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="41" t="str">
-        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="E25" s="71" t="str">
-        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="71" t="str">
-        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="71" t="str">
-        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="56" t="s">
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C26" s="72">
-        <v>-2</v>
-      </c>
-      <c r="D26" s="72">
-        <v>0</v>
-      </c>
-      <c r="E26" s="72">
-        <v>6</v>
-      </c>
-      <c r="F26" s="73">
-        <v>15</v>
-      </c>
-      <c r="G26" s="68">
-        <v>24</v>
-      </c>
-      <c r="H26" s="62" t="s">
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="70" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="56" t="s">
+      <c r="C25" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="C27" s="72">
-        <v>0</v>
-      </c>
-      <c r="D27" s="72">
-        <v>2</v>
-      </c>
-      <c r="E27" s="68">
-        <v>190</v>
-      </c>
-      <c r="F27" s="68">
-        <v>443</v>
-      </c>
-      <c r="G27" s="68">
-        <v>724</v>
-      </c>
-      <c r="H27" s="62" t="s">
+      <c r="D25" s="71" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="E25" s="71"/>
+      <c r="F25" s="72" t="s">
         <v>203</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="70" t="s">
         <v>204</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="C26" s="73" t="s">
         <v>205</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
+      <c r="D26" s="71" t="s">
         <v>206</v>
       </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="72" t="s">
+        <v>207</v>
+      </c>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="70" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="E27" s="71"/>
+      <c r="F27" s="72" t="s">
+        <v>210</v>
+      </c>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="70" t="s">
+        <v>211</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="71"/>
+      <c r="F28" s="72" t="s">
+        <v>213</v>
+      </c>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="70" t="s">
+        <v>214</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D29" s="71" t="s">
+        <v>215</v>
+      </c>
+      <c r="E29" s="71"/>
+      <c r="F29" s="72" t="s">
+        <v>216</v>
+      </c>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="74" t="s">
-        <v>207</v>
+      <c r="B30" s="70" t="s">
+        <v>217</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>209</v>
-      </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
-        <v>210</v>
-      </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
+        <v>201</v>
+      </c>
+      <c r="D30" s="71" t="s">
+        <v>218</v>
+      </c>
+      <c r="E30" s="71"/>
+      <c r="F30" s="72" t="s">
+        <v>219</v>
+      </c>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="74" t="s">
-        <v>211</v>
-      </c>
-      <c r="C31" s="77" t="s">
-        <v>212</v>
-      </c>
-      <c r="D31" s="75" t="s">
-        <v>213</v>
-      </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="74" t="s">
-        <v>215</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="D32" s="75" t="s">
-        <v>216</v>
-      </c>
-      <c r="E32" s="75"/>
-      <c r="F32" s="76" t="s">
-        <v>217</v>
-      </c>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="74" t="s">
-        <v>218</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="D33" s="75" t="s">
-        <v>219</v>
-      </c>
-      <c r="E33" s="75"/>
-      <c r="F33" s="76" t="s">
+      <c r="B31" s="70" t="s">
         <v>220</v>
       </c>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="74" t="s">
+      <c r="C31" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="71" t="s">
         <v>221</v>
       </c>
-      <c r="C34" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="D34" s="75" t="s">
+      <c r="E31" s="71"/>
+      <c r="F31" s="72" t="s">
         <v>222</v>
       </c>
-      <c r="E34" s="75"/>
-      <c r="F34" s="76" t="s">
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="56" t="s">
         <v>223</v>
       </c>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="74" t="s">
         <v>224</v>
       </c>
-      <c r="C35" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="D35" s="75" t="s">
-        <v>225</v>
-      </c>
-      <c r="E35" s="75"/>
-      <c r="F35" s="76" t="s">
-        <v>226</v>
-      </c>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="74" t="s">
-        <v>227</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="D36" s="75" t="s">
-        <v>228</v>
-      </c>
-      <c r="E36" s="75"/>
-      <c r="F36" s="76" t="s">
-        <v>229</v>
-      </c>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="56" t="s">
-        <v>230</v>
-      </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="78" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -5097,48 +4958,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="232">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -588,6 +588,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -625,6 +640,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -967,7 +988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1053,6 +1074,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4318,7 +4351,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4567,352 +4600,458 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="56" t="s">
         <v>183</v>
       </c>
-      <c r="C16" s="59">
-        <v>0.6639269081500647</v>
-      </c>
-      <c r="D16" s="60">
-        <v>0.4882345013477089</v>
-      </c>
-      <c r="E16" s="60">
-        <v>0.3254552660783174</v>
-      </c>
-      <c r="F16" s="60">
-        <v>0.25881186142410634</v>
-      </c>
-      <c r="G16" s="60">
-        <v>0.23758159092662604</v>
-      </c>
-      <c r="H16" s="62" t="s">
+      <c r="C16" s="63">
+        <v>14418.796710176493</v>
+      </c>
+      <c r="D16" s="63">
+        <v>10847.013026105897</v>
+      </c>
+      <c r="E16" s="63">
+        <v>8240.205350737264</v>
+      </c>
+      <c r="F16" s="63">
+        <v>7255.014947256478</v>
+      </c>
+      <c r="G16" s="63">
+        <v>7091.161513052948</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="56" t="s">
+      <c r="C17" s="55">
+        <v>700</v>
+      </c>
+      <c r="D17" s="55">
+        <v>721</v>
+      </c>
+      <c r="E17" s="55">
+        <v>743</v>
+      </c>
+      <c r="F17" s="55">
+        <v>765</v>
+      </c>
+      <c r="G17" s="55">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C17" s="63">
-        <v>0.18240620957309184</v>
-      </c>
-      <c r="D17" s="60">
-        <v>0.1151339781195497</v>
-      </c>
-      <c r="E17" s="60">
-        <v>0.07904835385509698</v>
-      </c>
-      <c r="F17" s="60">
-        <v>0.06474930412628371</v>
-      </c>
-      <c r="G17" s="60">
-        <v>0.06122075900007716</v>
-      </c>
-      <c r="H17" s="62" t="s">
+      <c r="C18" s="64">
+        <v>2350</v>
+      </c>
+      <c r="D18" s="61">
+        <v>1452.3</v>
+      </c>
+      <c r="E18" s="61">
+        <v>997.2213333333334</v>
+      </c>
+      <c r="F18" s="61">
+        <v>821.7334186666667</v>
+      </c>
+      <c r="G18" s="61">
+        <v>793.4822574000001</v>
+      </c>
+      <c r="H18" s="62" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="56" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="59">
-        <v>-0.08695407503234152</v>
-      </c>
-      <c r="D18" s="60">
-        <v>0.15983114000317108</v>
-      </c>
-      <c r="E18" s="60">
-        <v>0.35997542672937693</v>
-      </c>
-      <c r="F18" s="60">
-        <v>0.4388031413337536</v>
-      </c>
-      <c r="G18" s="60">
-        <v>0.46249517784121597</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="C19" s="64">
-        <v>3</v>
-      </c>
-      <c r="D19" s="64">
-        <v>3</v>
-      </c>
-      <c r="E19" s="64">
-        <v>3</v>
-      </c>
-      <c r="F19" s="64">
-        <v>3</v>
-      </c>
-      <c r="G19" s="64">
-        <v>3</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>190</v>
+      <c r="C19" s="65">
+        <v>-2493.8</v>
+      </c>
+      <c r="D19" s="66">
+        <v>1566.985</v>
+      </c>
+      <c r="E19" s="66">
+        <v>4241.793333333333</v>
+      </c>
+      <c r="F19" s="66">
+        <v>5369.317333333333</v>
+      </c>
+      <c r="G19" s="66">
+        <v>5819.8375</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="56" t="s">
-        <v>191</v>
-      </c>
-      <c r="C20" s="65">
-        <v>-2.6980845990297206</v>
-      </c>
-      <c r="D20" s="66">
-        <v>8.092828798342362</v>
-      </c>
-      <c r="E20" s="66">
-        <v>27.343177009677287</v>
-      </c>
-      <c r="F20" s="66">
-        <v>41.91340785801748</v>
-      </c>
-      <c r="G20" s="66">
-        <v>48.1240140158855</v>
+        <v>188</v>
+      </c>
+      <c r="C20" s="59">
+        <v>0.6639269081500647</v>
+      </c>
+      <c r="D20" s="60">
+        <v>0.4882345013477089</v>
+      </c>
+      <c r="E20" s="60">
+        <v>0.3254552660783174</v>
+      </c>
+      <c r="F20" s="60">
+        <v>0.25881186142410634</v>
+      </c>
+      <c r="G20" s="60">
+        <v>0.23758159092662604</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C21" s="67">
+        <v>0.18240620957309184</v>
+      </c>
+      <c r="D21" s="60">
+        <v>0.1151339781195497</v>
+      </c>
+      <c r="E21" s="60">
+        <v>0.07904835385509698</v>
+      </c>
+      <c r="F21" s="60">
+        <v>0.06474930412628371</v>
+      </c>
+      <c r="G21" s="60">
+        <v>0.06122075900007716</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="59">
+        <v>-0.08695407503234152</v>
+      </c>
+      <c r="D22" s="60">
+        <v>0.15983114000317108</v>
+      </c>
+      <c r="E22" s="60">
+        <v>0.35997542672937693</v>
+      </c>
+      <c r="F22" s="60">
+        <v>0.4388031413337536</v>
+      </c>
+      <c r="G22" s="60">
+        <v>0.46249517784121597</v>
+      </c>
+      <c r="H22" s="62" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="67" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="56" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="68">
+        <v>3</v>
+      </c>
+      <c r="D23" s="68">
+        <v>3</v>
+      </c>
+      <c r="E23" s="68">
+        <v>3</v>
+      </c>
+      <c r="F23" s="68">
+        <v>3</v>
+      </c>
+      <c r="G23" s="68">
+        <v>3</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" s="69">
+        <v>-2.6980845990297206</v>
+      </c>
+      <c r="D24" s="70">
+        <v>8.092828798342362</v>
+      </c>
+      <c r="E24" s="70">
+        <v>27.343177009677287</v>
+      </c>
+      <c r="F24" s="70">
+        <v>41.91340785801748</v>
+      </c>
+      <c r="G24" s="70">
+        <v>48.1240140158855</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" s="71" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="41" t="str">
+      <c r="D25" s="41" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="67" t="str">
+      <c r="E25" s="71" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="67" t="str">
+      <c r="F25" s="71" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="67" t="str">
+      <c r="G25" s="71" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="62" t="s">
+      <c r="H25" s="62" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="56" t="s">
-        <v>194</v>
-      </c>
-      <c r="C22" s="68">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="C26" s="72">
         <v>-2</v>
       </c>
-      <c r="D22" s="68">
+      <c r="D26" s="72">
         <v>0</v>
       </c>
-      <c r="E22" s="68">
+      <c r="E26" s="72">
         <v>6</v>
       </c>
-      <c r="F22" s="69">
+      <c r="F26" s="73">
         <v>15</v>
       </c>
-      <c r="G22" s="64">
+      <c r="G26" s="68">
         <v>24</v>
       </c>
-      <c r="H22" s="62" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="70" t="s">
+      <c r="H26" s="62" t="s">
         <v>200</v>
       </c>
-      <c r="C25" s="41" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="56" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="C27" s="72">
+        <v>0</v>
+      </c>
+      <c r="D27" s="72">
+        <v>2</v>
+      </c>
+      <c r="E27" s="68">
+        <v>190</v>
+      </c>
+      <c r="F27" s="68">
+        <v>443</v>
+      </c>
+      <c r="G27" s="68">
+        <v>724</v>
+      </c>
+      <c r="H27" s="62" t="s">
         <v>202</v>
       </c>
-      <c r="E25" s="71"/>
-      <c r="F25" s="72" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="70" t="s">
+      <c r="C29" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C26" s="73" t="s">
+      <c r="D29" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="E26" s="71"/>
-      <c r="F26" s="72" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="70" t="s">
+      <c r="C30" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D27" s="71" t="s">
+      <c r="D30" s="75" t="s">
         <v>209</v>
       </c>
-      <c r="E27" s="71"/>
-      <c r="F27" s="72" t="s">
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="70" t="s">
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="74" t="s">
         <v>211</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D28" s="71" t="s">
+      <c r="C31" s="77" t="s">
         <v>212</v>
       </c>
-      <c r="E28" s="71"/>
-      <c r="F28" s="72" t="s">
+      <c r="D31" s="75" t="s">
         <v>213</v>
       </c>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="70" t="s">
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
         <v>214</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D29" s="71" t="s">
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="74" t="s">
         <v>215</v>
       </c>
-      <c r="E29" s="71"/>
-      <c r="F29" s="72" t="s">
+      <c r="C32" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D32" s="75" t="s">
         <v>216</v>
       </c>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="70" t="s">
+      <c r="E32" s="75"/>
+      <c r="F32" s="76" t="s">
         <v>217</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D30" s="71" t="s">
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="E30" s="71"/>
-      <c r="F30" s="72" t="s">
+      <c r="C33" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D33" s="75" t="s">
         <v>219</v>
       </c>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="70" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="71" t="s">
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="74" t="s">
         <v>221</v>
       </c>
-      <c r="E31" s="71"/>
-      <c r="F31" s="72" t="s">
+      <c r="C34" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D34" s="75" t="s">
         <v>222</v>
       </c>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="56" t="s">
+      <c r="E34" s="75"/>
+      <c r="F34" s="76" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="74" t="s">
         <v>224</v>
       </c>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="74"/>
+      <c r="C35" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D35" s="75" t="s">
+        <v>225</v>
+      </c>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76" t="s">
+        <v>226</v>
+      </c>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="74" t="s">
+        <v>227</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D36" s="75" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" s="75"/>
+      <c r="F36" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4958,48 +5097,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -15,7 +15,7 @@
     <sheet sheetId="9" name="Financial Health" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="233">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -168,6 +168,9 @@
     <t>July</t>
   </si>
   <si>
+    <t>Accounting Basis</t>
+  </si>
+  <si>
     <t>Year 1 Operating Months</t>
   </si>
   <si>
@@ -549,7 +552,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -678,7 +681,7 @@
     <t>○ Needs attention</t>
   </si>
   <si>
-    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+    <t>Cash goes negative in month 1. The school will need outside funding to continue operating.</t>
   </si>
   <si>
     <t>Secure a line of credit or bridge funding before operations begin.</t>
@@ -1631,7 +1634,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1748,70 +1751,70 @@
       <c r="A14" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="23">
-        <v>10</v>
+      <c r="B14" s="23" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>45</v>
+      <c r="B15" s="23">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>46</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>50</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="23" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="B20" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="8"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="24">
-        <v>120</v>
-      </c>
+      <c r="B22" s="8"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>56</v>
       </c>
       <c r="B23" s="24">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1819,7 +1822,7 @@
         <v>57</v>
       </c>
       <c r="B24" s="24">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1827,7 +1830,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="24">
-        <v>375</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1835,22 +1838,22 @@
         <v>59</v>
       </c>
       <c r="B26" s="24">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="24">
         <v>400</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="8"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+    <row r="29" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="25">
-        <v>0</v>
-      </c>
+      <c r="B29" s="8"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
@@ -1864,16 +1867,24 @@
       <c r="A31" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="26">
-        <v>0.8333333333333334</v>
+      <c r="B31" s="25">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
         <v>65</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1906,49 +1917,49 @@
         <v>23</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="29">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B23</f>
         <v>120</v>
       </c>
       <c r="C2" s="29">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B24</f>
         <v>200</v>
       </c>
       <c r="D2" s="29">
-        <f>Assumptions!B24</f>
+        <f>Assumptions!B25</f>
         <v>300</v>
       </c>
       <c r="E2" s="29">
-        <f>Assumptions!B25</f>
+        <f>Assumptions!B26</f>
         <v>375</v>
       </c>
       <c r="F2" s="29">
-        <f>Assumptions!B26</f>
+        <f>Assumptions!B27</f>
         <v>400</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1958,82 +1969,82 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B4" s="30">
-        <f>9500*Assumptions!B22</f>
+        <f>9500*Assumptions!B23</f>
         <v>1140000</v>
       </c>
       <c r="C4" s="30">
-        <f>9690*Assumptions!B23</f>
+        <f>9690*Assumptions!B24</f>
         <v>1938000</v>
       </c>
       <c r="D4" s="30">
-        <f>9884*Assumptions!B24</f>
+        <f>9884*Assumptions!B25</f>
         <v>2965200</v>
       </c>
       <c r="E4" s="30">
-        <f>10081*Assumptions!B25</f>
+        <f>10081*Assumptions!B26</f>
         <v>3780375</v>
       </c>
       <c r="F4" s="30">
-        <f>10283*Assumptions!B26</f>
+        <f>10283*Assumptions!B27</f>
         <v>4113200</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="30">
-        <f>800*Assumptions!B22</f>
+        <f>800*Assumptions!B23</f>
         <v>96000</v>
       </c>
       <c r="C5" s="30">
-        <f>816*Assumptions!B23</f>
+        <f>816*Assumptions!B24</f>
         <v>163200</v>
       </c>
       <c r="D5" s="30">
-        <f>832*Assumptions!B24</f>
+        <f>832*Assumptions!B25</f>
         <v>249600</v>
       </c>
       <c r="E5" s="30">
-        <f>849*Assumptions!B25</f>
+        <f>849*Assumptions!B26</f>
         <v>318375</v>
       </c>
       <c r="F5" s="30">
-        <f>866*Assumptions!B26</f>
+        <f>866*Assumptions!B27</f>
         <v>346400</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="30">
-        <f>1200*Assumptions!B22</f>
+        <f>1200*Assumptions!B23</f>
         <v>144000</v>
       </c>
       <c r="C6" s="30">
-        <f>1224*Assumptions!B23</f>
+        <f>1224*Assumptions!B24</f>
         <v>244800</v>
       </c>
       <c r="D6" s="30">
-        <f>1248*Assumptions!B24</f>
+        <f>1248*Assumptions!B25</f>
         <v>374400</v>
       </c>
       <c r="E6" s="30">
-        <f>1273*Assumptions!B25</f>
+        <f>1273*Assumptions!B26</f>
         <v>477375</v>
       </c>
       <c r="F6" s="30">
-        <f>1299*Assumptions!B26</f>
+        <f>1299*Assumptions!B27</f>
         <v>519600</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="31">
         <f>SUM(B4:B6)</f>
@@ -2058,7 +2069,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2068,7 +2079,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B9" s="30">
         <v>100000</v>
@@ -2088,7 +2099,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="30">
         <v>30000</v>
@@ -2108,7 +2119,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B9:B10)</f>
@@ -2133,7 +2144,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2143,32 +2154,32 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="30">
-        <f>300*Assumptions!B22</f>
+        <f>300*Assumptions!B23</f>
         <v>36000</v>
       </c>
       <c r="C13" s="30">
-        <f>309*Assumptions!B23</f>
+        <f>309*Assumptions!B24</f>
         <v>61800</v>
       </c>
       <c r="D13" s="30">
-        <f>318*Assumptions!B24</f>
+        <f>318*Assumptions!B25</f>
         <v>95400</v>
       </c>
       <c r="E13" s="30">
-        <f>328*Assumptions!B25</f>
+        <f>328*Assumptions!B26</f>
         <v>123000</v>
       </c>
       <c r="F13" s="30">
-        <f>338*Assumptions!B26</f>
+        <f>338*Assumptions!B27</f>
         <v>135200</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B13:B13)</f>
@@ -2193,7 +2204,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B16" s="31">
         <f>B7+B11+B14</f>
@@ -2240,7 +2251,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -2252,39 +2263,39 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D4" s="26">
         <v>1</v>
@@ -2304,13 +2315,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>97</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>96</v>
       </c>
       <c r="D5" s="26">
         <v>1</v>
@@ -2330,13 +2341,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" s="26">
         <v>1</v>
@@ -2356,13 +2367,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" s="26">
         <v>6</v>
@@ -2382,13 +2393,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>100</v>
-      </c>
       <c r="C8" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
@@ -2408,13 +2419,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" s="26">
         <v>3</v>
@@ -2434,13 +2445,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" s="26">
         <v>1</v>
@@ -2460,13 +2471,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D11" s="26">
         <v>1</v>
@@ -2486,13 +2497,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" s="26">
         <v>2</v>
@@ -2512,7 +2523,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2524,7 +2535,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B15" s="34">
         <v>9</v>
@@ -2532,7 +2543,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" s="34">
         <v>17</v>
@@ -2540,7 +2551,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B17" s="35">
         <v>915000</v>
@@ -2548,7 +2559,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B18" s="35">
         <v>246720</v>
@@ -2556,7 +2567,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B19" s="35">
         <v>69998</v>
@@ -2564,7 +2575,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" s="35">
         <v>0</v>
@@ -2572,7 +2583,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B21" s="36">
         <v>1231718</v>
@@ -2580,7 +2591,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -2593,24 +2604,24 @@
         <v>23</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B25" s="30">
         <v>1231718</v>
@@ -2630,35 +2641,35 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B26" s="37">
-        <f>(1+Assumptions!B29)^0</f>
+        <f>(1+Assumptions!B30)^0</f>
         <v>1</v>
       </c>
       <c r="C26" s="37">
-        <f>(1+Assumptions!B29)^1</f>
+        <f>(1+Assumptions!B30)^1</f>
         <v>1</v>
       </c>
       <c r="D26" s="37">
-        <f>(1+Assumptions!B29)^2</f>
+        <f>(1+Assumptions!B30)^2</f>
         <v>1</v>
       </c>
       <c r="E26" s="37">
-        <f>(1+Assumptions!B29)^3</f>
+        <f>(1+Assumptions!B30)^3</f>
         <v>1</v>
       </c>
       <c r="F26" s="37">
-        <f>(1+Assumptions!B29)^4</f>
+        <f>(1+Assumptions!B30)^4</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B27" s="38">
-        <f>Assumptions!B31</f>
+        <f>Assumptions!B32</f>
         <v>0.8333333333333334</v>
       </c>
       <c r="C27" s="38">
@@ -2676,7 +2687,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B28" s="31">
         <f>B25*B26*B27</f>
@@ -2729,49 +2740,49 @@
         <v>23</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="29">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B23</f>
         <v>120</v>
       </c>
       <c r="C2" s="29">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B24</f>
         <v>200</v>
       </c>
       <c r="D2" s="29">
-        <f>Assumptions!B24</f>
+        <f>Assumptions!B25</f>
         <v>300</v>
       </c>
       <c r="E2" s="29">
-        <f>Assumptions!B25</f>
+        <f>Assumptions!B26</f>
         <v>375</v>
       </c>
       <c r="F2" s="29">
-        <f>Assumptions!B26</f>
+        <f>Assumptions!B27</f>
         <v>400</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2781,32 +2792,32 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B4" s="30">
-        <f>700*Assumptions!B22</f>
+        <f>700*Assumptions!B23</f>
         <v>84000</v>
       </c>
       <c r="C4" s="30">
-        <f>721*Assumptions!B23</f>
+        <f>721*Assumptions!B24</f>
         <v>144200</v>
       </c>
       <c r="D4" s="30">
-        <f>743*Assumptions!B24</f>
+        <f>743*Assumptions!B25</f>
         <v>222900</v>
       </c>
       <c r="E4" s="30">
-        <f>765*Assumptions!B25</f>
+        <f>765*Assumptions!B26</f>
         <v>286875</v>
       </c>
       <c r="F4" s="30">
-        <f>788*Assumptions!B26</f>
+        <f>788*Assumptions!B27</f>
         <v>315200</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
@@ -2831,7 +2842,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2841,32 +2852,32 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B7" s="30">
-        <f>500*Assumptions!B22</f>
+        <f>500*Assumptions!B23</f>
         <v>60000</v>
       </c>
       <c r="C7" s="30">
-        <f>515*Assumptions!B23</f>
+        <f>515*Assumptions!B24</f>
         <v>103000</v>
       </c>
       <c r="D7" s="30">
-        <f>530*Assumptions!B24</f>
+        <f>530*Assumptions!B25</f>
         <v>159000</v>
       </c>
       <c r="E7" s="30">
-        <f>546*Assumptions!B25</f>
+        <f>546*Assumptions!B26</f>
         <v>204750</v>
       </c>
       <c r="F7" s="30">
-        <f>562*Assumptions!B26</f>
+        <f>562*Assumptions!B27</f>
         <v>224800</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
@@ -2891,7 +2902,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2901,7 +2912,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B10" s="30">
         <f>18000*12</f>
@@ -2926,7 +2937,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B11" s="30">
         <f>2500*12</f>
@@ -2951,7 +2962,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B12" s="30">
         <v>18000</v>
@@ -2971,7 +2982,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B13" s="30">
         <f>1500*12</f>
@@ -2996,7 +3007,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B10:B13)</f>
@@ -3021,7 +3032,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -3031,7 +3042,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B16" s="30">
         <v>25000</v>
@@ -3051,7 +3062,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B17" s="30">
         <v>15000</v>
@@ -3071,7 +3082,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" s="30">
         <v>20000</v>
@@ -3091,57 +3102,57 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B19" s="30">
-        <f>800*Assumptions!B22</f>
+        <f>800*Assumptions!B23</f>
         <v>96000</v>
       </c>
       <c r="C19" s="30">
-        <f>824*Assumptions!B23</f>
+        <f>824*Assumptions!B24</f>
         <v>164800</v>
       </c>
       <c r="D19" s="30">
-        <f>849*Assumptions!B24</f>
+        <f>849*Assumptions!B25</f>
         <v>254700</v>
       </c>
       <c r="E19" s="30">
-        <f>874*Assumptions!B25</f>
+        <f>874*Assumptions!B26</f>
         <v>327750</v>
       </c>
       <c r="F19" s="30">
-        <f>900*Assumptions!B26</f>
+        <f>900*Assumptions!B27</f>
         <v>360000</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B20" s="30">
-        <f>600*Assumptions!B22</f>
+        <f>600*Assumptions!B23</f>
         <v>72000</v>
       </c>
       <c r="C20" s="30">
-        <f>618*Assumptions!B23</f>
+        <f>618*Assumptions!B24</f>
         <v>123600</v>
       </c>
       <c r="D20" s="30">
-        <f>637*Assumptions!B24</f>
+        <f>637*Assumptions!B25</f>
         <v>191100</v>
       </c>
       <c r="E20" s="30">
-        <f>656*Assumptions!B25</f>
+        <f>656*Assumptions!B26</f>
         <v>246000</v>
       </c>
       <c r="F20" s="30">
-        <f>675*Assumptions!B26</f>
+        <f>675*Assumptions!B27</f>
         <v>270000</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B21" s="31">
         <f>SUM(B16:B20)</f>
@@ -3166,7 +3177,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B23" s="31">
         <f>B5+B8+B14+B21</f>
@@ -3216,24 +3227,24 @@
         <v>23</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3243,7 +3254,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="30">
         <v>49824.605221179416</v>
@@ -3263,7 +3274,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" s="30">
         <v>75000</v>
@@ -3283,7 +3294,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B5" s="30">
         <v>40000</v>
@@ -3303,7 +3314,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B3:B5)</f>
@@ -3353,24 +3364,24 @@
         <v>1</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B2" s="30">
         <f>'Revenue Schedule'!B16</f>
@@ -3395,7 +3406,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B28</f>
@@ -3470,7 +3481,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" s="31">
         <f>B3+B4+B5</f>
@@ -3495,7 +3506,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" s="31">
         <f>B2-B6</f>
@@ -3520,7 +3531,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B8" s="30">
         <f>B7</f>
@@ -3570,13 +3581,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D10" s="40" t="s">
         <v>23</v>
@@ -3603,7 +3614,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3612,7 +3623,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -3622,7 +3633,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3693,134 +3704,117 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="B13" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="28" t="s">
+      <c r="B16" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="C16" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="D16" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="E16" s="28" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="F16" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="29">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="29">
         <f>'Revenue Schedule'!B2</f>
         <v>120</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f>'Revenue Schedule'!C2</f>
         <v>200</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D17" s="29">
         <f>'Revenue Schedule'!D2</f>
         <v>300</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E17" s="29">
         <f>'Revenue Schedule'!E2</f>
         <v>375</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F17" s="29">
         <f>'Revenue Schedule'!F2</f>
         <v>400</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="9" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C17" s="44">
-        <f>IF(B16=0,0,(C16-B16)/B16)</f>
+      <c r="B18" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="44">
+        <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D17" s="44">
-        <f>IF(C16=0,0,(D16-C16)/C16)</f>
+      <c r="D18" s="44">
+        <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="44">
-        <f>IF(D16=0,0,(E16-D16)/D16)</f>
+      <c r="E18" s="44">
+        <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.25</v>
       </c>
-      <c r="F17" s="44">
-        <f>IF(E16=0,0,(F16-E16)/E16)</f>
+      <c r="F18" s="44">
+        <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0.06666666666666667</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="28" t="s">
+      <c r="B20" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="C20" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="D20" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="E20" s="28" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="30">
-        <f>'Financial Model'!B2</f>
-        <v>1546000</v>
-      </c>
-      <c r="C20" s="30">
-        <f>'Financial Model'!C2</f>
-        <v>2522800</v>
-      </c>
-      <c r="D20" s="30">
-        <f>'Financial Model'!D2</f>
-        <v>3784600</v>
-      </c>
-      <c r="E20" s="30">
-        <f>'Financial Model'!E2</f>
-        <v>4759125</v>
-      </c>
-      <c r="F20" s="30">
-        <f>'Financial Model'!F2</f>
-        <v>5184400</v>
+      <c r="F20" s="28" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3828,209 +3822,209 @@
         <v>148</v>
       </c>
       <c r="B21" s="30">
+        <f>'Financial Model'!B2</f>
+        <v>1546000</v>
+      </c>
+      <c r="C21" s="30">
+        <f>'Financial Model'!C2</f>
+        <v>2522800</v>
+      </c>
+      <c r="D21" s="30">
+        <f>'Financial Model'!D2</f>
+        <v>3784600</v>
+      </c>
+      <c r="E21" s="30">
+        <f>'Financial Model'!E2</f>
+        <v>4759125</v>
+      </c>
+      <c r="F21" s="30">
+        <f>'Financial Model'!F2</f>
+        <v>5184400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B22" s="30">
         <f>'Financial Model'!B3</f>
         <v>1026431</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C22" s="30">
         <f>'Financial Model'!C3</f>
         <v>1231718</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D22" s="30">
         <f>'Financial Model'!D3</f>
         <v>1231718</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E22" s="30">
         <f>'Financial Model'!E3</f>
         <v>1231718</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F22" s="30">
         <f>'Financial Model'!F3</f>
         <v>1231718</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B23" s="30">
         <f>'Financial Model'!B4</f>
         <v>654000</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C23" s="30">
         <f>'Financial Model'!C4</f>
         <v>887860</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D23" s="30">
         <f>'Financial Model'!D4</f>
         <v>1190519</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E23" s="30">
         <f>'Financial Model'!E4</f>
         <v>1439088</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F23" s="30">
         <f>'Financial Model'!F4</f>
         <v>1554922</v>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="31">
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="31">
         <f>'Financial Model'!B6</f>
         <v>1845256</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f>'Financial Model'!C6</f>
         <v>2209403</v>
       </c>
-      <c r="D23" s="31">
+      <c r="D24" s="31">
         <f>'Financial Model'!D6</f>
         <v>2512062</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E24" s="31">
         <f>'Financial Model'!E6</f>
         <v>2745631</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F24" s="31">
         <f>'Financial Model'!F6</f>
         <v>2856465</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="B24" s="45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="45">
         <f>'Financial Model'!B7</f>
         <v>-299256</v>
       </c>
-      <c r="C24" s="46">
+      <c r="C25" s="46">
         <f>'Financial Model'!C7</f>
         <v>313397</v>
       </c>
-      <c r="D24" s="46">
+      <c r="D25" s="46">
         <f>'Financial Model'!D7</f>
         <v>1272538</v>
       </c>
-      <c r="E24" s="46">
+      <c r="E25" s="46">
         <f>'Financial Model'!E7</f>
         <v>2013494</v>
       </c>
-      <c r="F24" s="46">
+      <c r="F25" s="46">
         <f>'Financial Model'!F7</f>
         <v>2327935</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" s="30">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="30">
         <f>'Financial Model'!B8</f>
         <v>-299256</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C26" s="30">
         <f>'Financial Model'!C8</f>
         <v>14141</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D26" s="30">
         <f>'Financial Model'!D8</f>
         <v>1286679</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E26" s="30">
         <f>'Financial Model'!E8</f>
         <v>3300173</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F26" s="30">
         <f>'Financial Model'!F8</f>
         <v>5628108</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="34" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="47" t="str">
+      <c r="B27" s="47" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
-      <c r="C26" s="47">
+      <c r="C27" s="47">
         <f>'Financial Model'!C9</f>
         <v>0.0768044580368543</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D27" s="13">
         <f>'Financial Model'!D9</f>
         <v>6.146404029836844</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E27" s="13">
         <f>'Financial Model'!E9</f>
         <v>14.42367018729028</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F27" s="13">
         <f>'Financial Model'!F9</f>
         <v>23.643663059060763</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B29" s="30">
-        <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
-        <v>12883.333333333334</v>
-      </c>
-      <c r="C29" s="30">
-        <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
-        <v>12614</v>
-      </c>
-      <c r="D29" s="30">
-        <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
-        <v>12615.333333333334</v>
-      </c>
-      <c r="E29" s="30">
-        <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
-        <v>12691</v>
-      </c>
-      <c r="F29" s="30">
-        <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
-        <v>12961</v>
-      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="B30" s="44">
-        <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
-        <v>0.6639269081500647</v>
-      </c>
-      <c r="C30" s="44">
-        <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
-        <v>0.4882345013477089</v>
-      </c>
-      <c r="D30" s="44">
-        <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
-        <v>0.3254552660783174</v>
-      </c>
-      <c r="E30" s="44">
-        <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
-        <v>0.25881186142410634</v>
-      </c>
-      <c r="F30" s="44">
-        <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
-        <v>0.23758159092662604</v>
+      <c r="B30" s="30">
+        <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
+        <v>12883.333333333334</v>
+      </c>
+      <c r="C30" s="30">
+        <f>IF('Revenue Schedule'!C2=0,0,C21/'Revenue Schedule'!C2)</f>
+        <v>12614</v>
+      </c>
+      <c r="D30" s="30">
+        <f>IF('Revenue Schedule'!D2=0,0,D21/'Revenue Schedule'!D2)</f>
+        <v>12615.333333333334</v>
+      </c>
+      <c r="E30" s="30">
+        <f>IF('Revenue Schedule'!E2=0,0,E21/'Revenue Schedule'!E2)</f>
+        <v>12691</v>
+      </c>
+      <c r="F30" s="30">
+        <f>IF('Revenue Schedule'!F2=0,0,F21/'Revenue Schedule'!F2)</f>
+        <v>12961</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4038,99 +4032,104 @@
         <v>163</v>
       </c>
       <c r="B31" s="44">
-        <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
+        <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
+        <v>0.6639269081500647</v>
+      </c>
+      <c r="C31" s="44">
+        <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
+        <v>0.4882345013477089</v>
+      </c>
+      <c r="D31" s="44">
+        <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
+        <v>0.3254552660783174</v>
+      </c>
+      <c r="E31" s="44">
+        <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
+        <v>0.25881186142410634</v>
+      </c>
+      <c r="F31" s="44">
+        <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
+        <v>0.23758159092662604</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="44">
+        <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
         <v>0.4230271668822768</v>
       </c>
-      <c r="C31" s="44">
-        <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
+      <c r="C32" s="44">
+        <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
         <v>0.35193435864912004</v>
       </c>
-      <c r="D31" s="44">
-        <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
+      <c r="D32" s="44">
+        <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
         <v>0.31456930719230564</v>
       </c>
-      <c r="E31" s="44">
-        <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
+      <c r="E32" s="44">
+        <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
         <v>0.3023849972421401</v>
       </c>
-      <c r="F31" s="44">
-        <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
+      <c r="F32" s="44">
+        <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
         <v>0.299923231232158</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="B32" s="48">
-        <f>IF(B20=0,0,B24/B20)</f>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="48">
+        <f>IF(B21=0,0,B25/B21)</f>
         <v>-0.1935679172056921</v>
       </c>
-      <c r="C32" s="12">
-        <f>IF(C20=0,0,C24/C20)</f>
+      <c r="C33" s="12">
+        <f>IF(C21=0,0,C25/C21)</f>
         <v>0.12422586015538291</v>
       </c>
-      <c r="D32" s="12">
-        <f>IF(D20=0,0,D24/D20)</f>
+      <c r="D33" s="12">
+        <f>IF(D21=0,0,D25/D21)</f>
         <v>0.3362410822808223</v>
       </c>
-      <c r="E32" s="12">
-        <f>IF(E20=0,0,E24/E20)</f>
+      <c r="E33" s="12">
+        <f>IF(E21=0,0,E25/E21)</f>
         <v>0.42308071336642766</v>
       </c>
-      <c r="F32" s="12">
-        <f>IF(F20=0,0,F24/F20)</f>
+      <c r="F33" s="12">
+        <f>IF(F21=0,0,F25/F21)</f>
         <v>0.4490268883573798</v>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
+    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="44">
-        <v>0.02328589909443726</v>
-      </c>
-      <c r="C35" s="44">
-        <v>0.024496591089265895</v>
-      </c>
-      <c r="D35" s="44">
-        <v>0.025207419542355863</v>
-      </c>
-      <c r="E35" s="44">
-        <v>0.025845087069576864</v>
-      </c>
-      <c r="F35" s="44">
-        <v>0.026078234704112337</v>
-      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
         <v>167</v>
       </c>
       <c r="B36" s="44">
-        <v>0.8926261319534282</v>
+        <v>0.02328589909443726</v>
       </c>
       <c r="C36" s="44">
-        <v>0.9299191374663073</v>
+        <v>0.024496591089265895</v>
       </c>
       <c r="D36" s="44">
-        <v>0.9483697088199545</v>
+        <v>0.025207419542355863</v>
       </c>
       <c r="E36" s="44">
-        <v>0.9615475533842881</v>
+        <v>0.025845087069576864</v>
       </c>
       <c r="F36" s="44">
-        <v>0.9604197207005633</v>
+        <v>0.026078234704112337</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4138,18 +4137,38 @@
         <v>168</v>
       </c>
       <c r="B37" s="44">
+        <v>0.8926261319534282</v>
+      </c>
+      <c r="C37" s="44">
+        <v>0.9299191374663073</v>
+      </c>
+      <c r="D37" s="44">
+        <v>0.9483697088199545</v>
+      </c>
+      <c r="E37" s="44">
+        <v>0.9615475533842881</v>
+      </c>
+      <c r="F37" s="44">
+        <v>0.9604197207005633</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="B38" s="44">
         <v>0.08408796895213454</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C38" s="44">
         <v>0.045584271444426824</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D38" s="44">
         <v>0.026422871637689586</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E38" s="44">
         <v>0.012607359546135056</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F38" s="44">
         <v>0.013502044595324435</v>
       </c>
     </row>
@@ -4363,7 +4382,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
@@ -4374,7 +4393,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
@@ -4385,41 +4404,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D4" s="51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F4" s="52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" s="53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C7" s="54">
         <v>120</v>
@@ -4439,7 +4458,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C8" s="55">
         <v>1546000</v>
@@ -4459,7 +4478,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C9" s="55">
         <v>1026431</v>
@@ -4499,7 +4518,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C11" s="55">
         <v>49824.605221179416</v>
@@ -4519,7 +4538,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="57">
         <v>-299256</v>
@@ -4539,7 +4558,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="56" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C13" s="57">
         <v>-299256</v>
@@ -4559,7 +4578,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="56" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C14" s="59">
         <v>-0.1935679172056921</v>
@@ -4579,7 +4598,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="56" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C15" s="61">
         <v>12883.333333333334</v>
@@ -4597,12 +4616,12 @@
         <v>12961</v>
       </c>
       <c r="H15" s="62" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="63">
         <v>14418.796710176493</v>
@@ -4622,7 +4641,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="55">
         <v>700</v>
@@ -4642,7 +4661,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C18" s="64">
         <v>2350</v>
@@ -4660,12 +4679,12 @@
         <v>793.4822574000001</v>
       </c>
       <c r="H18" s="62" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C19" s="65">
         <v>-2493.8</v>
@@ -4685,7 +4704,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="56" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C20" s="59">
         <v>0.6639269081500647</v>
@@ -4703,12 +4722,12 @@
         <v>0.23758159092662604</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="56" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C21" s="67">
         <v>0.18240620957309184</v>
@@ -4726,12 +4745,12 @@
         <v>0.06122075900007716</v>
       </c>
       <c r="H21" s="62" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C22" s="59">
         <v>-0.08695407503234152</v>
@@ -4749,12 +4768,12 @@
         <v>0.46249517784121597</v>
       </c>
       <c r="H22" s="62" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C23" s="68">
         <v>3</v>
@@ -4772,12 +4791,12 @@
         <v>3</v>
       </c>
       <c r="H23" s="62" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="56" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C24" s="69">
         <v>-2.6980845990297206</v>
@@ -4795,12 +4814,12 @@
         <v>48.1240140158855</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C25" s="71" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
@@ -4823,12 +4842,12 @@
         <v>0</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="56" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C26" s="72">
         <v>-2</v>
@@ -4846,12 +4865,12 @@
         <v>24</v>
       </c>
       <c r="H26" s="62" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="56" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C27" s="72">
         <v>0</v>
@@ -4869,141 +4888,141 @@
         <v>724</v>
       </c>
       <c r="H27" s="62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D30" s="75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E30" s="75"/>
       <c r="F30" s="76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G30" s="76"/>
       <c r="H30" s="76"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="74" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C31" s="77" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D31" s="75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E31" s="75"/>
       <c r="F31" s="76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G31" s="76"/>
       <c r="H31" s="76"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="74" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D32" s="75" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E32" s="75"/>
       <c r="F32" s="76" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G32" s="76"/>
       <c r="H32" s="76"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E33" s="75"/>
       <c r="F33" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G33" s="76"/>
       <c r="H33" s="76"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="74" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D34" s="75" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E34" s="75"/>
       <c r="F34" s="76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G34" s="76"/>
       <c r="H34" s="76"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="74" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D35" s="75" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E35" s="75"/>
       <c r="F35" s="76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G35" s="76"/>
       <c r="H35" s="76"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="74" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D36" s="75" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E36" s="75"/>
       <c r="F36" s="76" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G36" s="76"/>
       <c r="H36" s="76"/>
@@ -5013,7 +5032,7 @@
         <v>20</v>
       </c>
       <c r="C38" s="56" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D38" s="56"/>
       <c r="E38" s="56"/>
@@ -5021,7 +5040,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="78" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C40" s="78"/>
       <c r="D40" s="78"/>
@@ -5135,10 +5154,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -564,7 +564,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -564,7 +564,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -684,7 +684,7 @@
     <t>The model reaches net income early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -1930,7 +1930,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1940,7 +1940,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
         <v>173</v>
       </c>
@@ -1950,8 +1950,9 @@
       <c r="F2" s="42"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="51" t="s">
         <v>174</v>
       </c>
@@ -1961,6 +1962,7 @@
       <c r="F3" s="51"/>
       <c r="G3" s="51"/>
       <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="52" t="s">
@@ -2451,7 +2453,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
         <v>207</v>
       </c>
@@ -2467,8 +2469,9 @@
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="76" t="s">
         <v>211</v>
       </c>
@@ -2484,8 +2487,9 @@
       </c>
       <c r="G30" s="78"/>
       <c r="H30" s="78"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="78"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="76" t="s">
         <v>215</v>
       </c>
@@ -2501,8 +2505,9 @@
       </c>
       <c r="G31" s="78"/>
       <c r="H31" s="78"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="78"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="76" t="s">
         <v>219</v>
       </c>
@@ -2518,8 +2523,9 @@
       </c>
       <c r="G32" s="78"/>
       <c r="H32" s="78"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="78"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="76" t="s">
         <v>222</v>
       </c>
@@ -2535,8 +2541,9 @@
       </c>
       <c r="G33" s="78"/>
       <c r="H33" s="78"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="78"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="76" t="s">
         <v>225</v>
       </c>
@@ -2552,8 +2559,9 @@
       </c>
       <c r="G34" s="78"/>
       <c r="H34" s="78"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="78"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="76" t="s">
         <v>228</v>
       </c>
@@ -2569,8 +2577,9 @@
       </c>
       <c r="G35" s="78"/>
       <c r="H35" s="78"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="78"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="76" t="s">
         <v>231</v>
       </c>
@@ -2586,6 +2595,7 @@
       </c>
       <c r="G36" s="78"/>
       <c r="H36" s="78"/>
+      <c r="I36" s="78"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="76" t="s">
@@ -2598,7 +2608,7 @@
       <c r="E38" s="58"/>
       <c r="F38" s="58"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="80" t="s">
         <v>235</v>
       </c>
@@ -2608,29 +2618,30 @@
       <c r="F40" s="80"/>
       <c r="G40" s="80"/>
       <c r="H40" s="80"/>
+      <c r="I40" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_Public_Funding.xlsx
@@ -20,19 +20,19 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staffing &amp; Personnel'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Operating Expenses'!$A1:$F23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$G16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="249">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 7, 2026</t>
+    <t>May 9, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -414,6 +414,27 @@
     <t>Total Personnel Cost</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION</t>
+  </si>
+  <si>
+    <t>5-Year Total</t>
+  </si>
+  <si>
+    <t>Founder Compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fully-loaded (incl. benefits + payroll tax)</t>
+  </si>
+  <si>
+    <t>Founder Compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t>Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market rate ("sweat equity"). Lenders and boards underwrite to the market-rate line; the adjustment shows the gap.</t>
+  </si>
+  <si>
     <t>INSTRUCTIONAL / PROGRAM</t>
   </si>
   <si>
@@ -504,6 +525,21 @@
     <t>Cumulative Net Income</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION (memo — already in Personnel above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market ("sweat equity"). Lenders / boards underwrite to the market-rate line.</t>
+  </si>
+  <si>
     <t>Break-even</t>
   </si>
   <si>
@@ -564,7 +600,10 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
+  </si>
+  <si>
+    <t>Built from assumptions</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -763,7 +802,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -861,6 +900,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="16"/>
@@ -888,6 +933,13 @@
       <i/>
       <color rgb="FF6B7280"/>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1009,7 +1061,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1051,6 +1103,12 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1058,23 +1116,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="166" fontId="20" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1100,7 +1159,7 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1138,10 +1197,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1930,7 +1989,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I40"/>
+  <dimension ref="B2:I41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1941,691 +2000,702 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="B2" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="52" t="s">
-        <v>175</v>
-      </c>
-      <c r="D4" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="55" t="s">
+      <c r="B3" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="54" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="56" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" s="57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D7" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E7" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F7" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G7" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="55" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C7" s="56">
-        <v>120</v>
-      </c>
-      <c r="D7" s="56">
-        <v>200</v>
-      </c>
-      <c r="E7" s="56">
-        <v>300</v>
-      </c>
-      <c r="F7" s="56">
-        <v>375</v>
-      </c>
-      <c r="G7" s="56">
-        <v>400</v>
+      <c r="H7" s="58" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C8" s="57">
-        <v>1546000</v>
-      </c>
-      <c r="D8" s="57">
-        <v>2522800</v>
-      </c>
-      <c r="E8" s="57">
-        <v>3784600</v>
-      </c>
-      <c r="F8" s="57">
-        <v>4759125</v>
-      </c>
-      <c r="G8" s="57">
-        <v>5184400</v>
+        <v>193</v>
+      </c>
+      <c r="C8" s="59">
+        <v>120</v>
+      </c>
+      <c r="D8" s="59">
+        <v>200</v>
+      </c>
+      <c r="E8" s="59">
+        <v>300</v>
+      </c>
+      <c r="F8" s="59">
+        <v>375</v>
+      </c>
+      <c r="G8" s="59">
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C9" s="57">
-        <v>1026431</v>
-      </c>
-      <c r="D9" s="57">
-        <v>1231718</v>
-      </c>
-      <c r="E9" s="57">
-        <v>1231718</v>
-      </c>
-      <c r="F9" s="57">
-        <v>1231718</v>
-      </c>
-      <c r="G9" s="57">
-        <v>1231718</v>
+        <v>194</v>
+      </c>
+      <c r="C9" s="60">
+        <v>1546000</v>
+      </c>
+      <c r="D9" s="60">
+        <v>2522800</v>
+      </c>
+      <c r="E9" s="60">
+        <v>3784600</v>
+      </c>
+      <c r="F9" s="60">
+        <v>4759125</v>
+      </c>
+      <c r="G9" s="60">
+        <v>5184400</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="57">
-        <v>654000</v>
-      </c>
-      <c r="D10" s="57">
-        <v>887860</v>
-      </c>
-      <c r="E10" s="57">
-        <v>1190519</v>
-      </c>
-      <c r="F10" s="57">
-        <v>1439088</v>
-      </c>
-      <c r="G10" s="57">
-        <v>1554922</v>
+        <v>195</v>
+      </c>
+      <c r="C10" s="60">
+        <v>1026431</v>
+      </c>
+      <c r="D10" s="60">
+        <v>1231718</v>
+      </c>
+      <c r="E10" s="60">
+        <v>1231718</v>
+      </c>
+      <c r="F10" s="60">
+        <v>1231718</v>
+      </c>
+      <c r="G10" s="60">
+        <v>1231718</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C11" s="57">
+        <v>17</v>
+      </c>
+      <c r="C11" s="60">
+        <v>654000</v>
+      </c>
+      <c r="D11" s="60">
+        <v>887860</v>
+      </c>
+      <c r="E11" s="60">
+        <v>1190519</v>
+      </c>
+      <c r="F11" s="60">
+        <v>1439088</v>
+      </c>
+      <c r="G11" s="60">
+        <v>1554922</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="60">
         <v>49824.605221179416</v>
       </c>
-      <c r="D11" s="57">
+      <c r="D12" s="60">
         <v>49824.605221179416</v>
       </c>
-      <c r="E11" s="57">
+      <c r="E12" s="60">
         <v>49824.605221179416</v>
       </c>
-      <c r="F11" s="57">
+      <c r="F12" s="60">
         <v>49824.605221179416</v>
       </c>
-      <c r="G11" s="57">
+      <c r="G12" s="60">
         <v>49824.605221179416</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="58" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" s="59">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="62">
         <v>-299256</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D13" s="63">
         <v>313397</v>
       </c>
-      <c r="E12" s="60">
+      <c r="E13" s="63">
         <v>1272538</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F13" s="63">
         <v>2013494</v>
       </c>
-      <c r="G12" s="60">
+      <c r="G13" s="63">
         <v>2327935</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C13" s="59">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="61" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" s="62">
         <v>-299256</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D14" s="63">
         <v>14141</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E14" s="63">
         <v>1286679</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F14" s="63">
         <v>3300173</v>
       </c>
-      <c r="G13" s="60">
+      <c r="G14" s="63">
         <v>5628108</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="58" t="s">
-        <v>185</v>
-      </c>
-      <c r="C14" s="61">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="61" t="s">
+        <v>198</v>
+      </c>
+      <c r="C15" s="64">
         <v>-0.1935679172056921</v>
       </c>
-      <c r="D14" s="62">
+      <c r="D15" s="65">
         <v>0.12422586015538291</v>
       </c>
-      <c r="E14" s="62">
+      <c r="E15" s="65">
         <v>0.3362410822808223</v>
       </c>
-      <c r="F14" s="62">
+      <c r="F15" s="65">
         <v>0.42308071336642766</v>
       </c>
-      <c r="G14" s="62">
+      <c r="G15" s="65">
         <v>0.4490268883573798</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C15" s="63">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" s="66">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D16" s="66">
         <v>12614</v>
       </c>
-      <c r="E15" s="63">
+      <c r="E16" s="66">
         <v>12615.333333333334</v>
       </c>
-      <c r="F15" s="63">
+      <c r="F16" s="66">
         <v>12691</v>
       </c>
-      <c r="G15" s="63">
+      <c r="G16" s="66">
         <v>12961</v>
       </c>
-      <c r="H15" s="64" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="58" t="s">
-        <v>187</v>
-      </c>
-      <c r="C16" s="65">
+      <c r="H16" s="67" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" s="68">
         <v>14418.796710176493</v>
       </c>
-      <c r="D16" s="65">
+      <c r="D17" s="68">
         <v>10847.013026105897</v>
       </c>
-      <c r="E16" s="65">
+      <c r="E17" s="68">
         <v>8240.205350737264</v>
       </c>
-      <c r="F16" s="65">
+      <c r="F17" s="68">
         <v>7255.014947256478</v>
       </c>
-      <c r="G16" s="65">
+      <c r="G17" s="68">
         <v>7091.161513052948</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" s="57">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C18" s="60">
         <v>700</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D18" s="60">
         <v>721</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E18" s="60">
         <v>743</v>
       </c>
-      <c r="F17" s="57">
+      <c r="F18" s="60">
         <v>765</v>
       </c>
-      <c r="G17" s="57">
+      <c r="G18" s="60">
         <v>788</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C18" s="66">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C19" s="69">
         <v>2350</v>
       </c>
-      <c r="D18" s="63">
+      <c r="D19" s="66">
         <v>1452.3</v>
       </c>
-      <c r="E18" s="63">
+      <c r="E19" s="66">
         <v>997.2213333333334</v>
       </c>
-      <c r="F18" s="63">
+      <c r="F19" s="66">
         <v>821.7334186666667</v>
       </c>
-      <c r="G18" s="63">
+      <c r="G19" s="66">
         <v>793.4822574000001</v>
       </c>
-      <c r="H18" s="64" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="C19" s="67">
+      <c r="H19" s="67" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="70">
         <v>-2493.8</v>
       </c>
-      <c r="D19" s="68">
+      <c r="D20" s="71">
         <v>1566.985</v>
       </c>
-      <c r="E19" s="68">
+      <c r="E20" s="71">
         <v>4241.793333333333</v>
       </c>
-      <c r="F19" s="68">
+      <c r="F20" s="71">
         <v>5369.317333333333</v>
       </c>
-      <c r="G19" s="68">
+      <c r="G20" s="71">
         <v>5819.8375</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="58" t="s">
-        <v>192</v>
-      </c>
-      <c r="C20" s="61">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="C21" s="64">
         <v>0.6639269081500647</v>
       </c>
-      <c r="D20" s="62">
+      <c r="D21" s="65">
         <v>0.4882345013477089</v>
       </c>
-      <c r="E20" s="62">
+      <c r="E21" s="65">
         <v>0.3254552660783174</v>
       </c>
-      <c r="F20" s="62">
+      <c r="F21" s="65">
         <v>0.25881186142410634</v>
       </c>
-      <c r="G20" s="62">
+      <c r="G21" s="65">
         <v>0.23758159092662604</v>
       </c>
-      <c r="H20" s="64" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="58" t="s">
-        <v>194</v>
-      </c>
-      <c r="C21" s="69">
+      <c r="H21" s="67" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="72">
         <v>0.18240620957309184</v>
       </c>
-      <c r="D21" s="62">
+      <c r="D22" s="65">
         <v>0.1151339781195497</v>
       </c>
-      <c r="E21" s="62">
+      <c r="E22" s="65">
         <v>0.07904835385509698</v>
       </c>
-      <c r="F21" s="62">
+      <c r="F22" s="65">
         <v>0.06474930412628371</v>
       </c>
-      <c r="G21" s="62">
+      <c r="G22" s="65">
         <v>0.06122075900007716</v>
       </c>
-      <c r="H21" s="64" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="58" t="s">
-        <v>196</v>
-      </c>
-      <c r="C22" s="61">
+      <c r="H22" s="67" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="C23" s="64">
         <v>-0.08695407503234152</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D23" s="65">
         <v>0.15983114000317108</v>
       </c>
-      <c r="E22" s="62">
+      <c r="E23" s="65">
         <v>0.35997542672937693</v>
       </c>
-      <c r="F22" s="62">
+      <c r="F23" s="65">
         <v>0.4388031413337536</v>
       </c>
-      <c r="G22" s="62">
+      <c r="G23" s="65">
         <v>0.46249517784121597</v>
       </c>
-      <c r="H22" s="64" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="58" t="s">
-        <v>198</v>
-      </c>
-      <c r="C23" s="70">
+      <c r="H23" s="67" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="61" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" s="73">
         <v>3</v>
       </c>
-      <c r="D23" s="70">
+      <c r="D24" s="73">
         <v>3</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E24" s="73">
         <v>3</v>
       </c>
-      <c r="F23" s="70">
+      <c r="F24" s="73">
         <v>3</v>
       </c>
-      <c r="G23" s="70">
+      <c r="G24" s="73">
         <v>3</v>
       </c>
-      <c r="H23" s="64" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="C24" s="71">
+      <c r="H24" s="67" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="61" t="s">
+        <v>213</v>
+      </c>
+      <c r="C25" s="74">
         <v>-2.6980845990297206</v>
       </c>
-      <c r="D24" s="72">
+      <c r="D25" s="75">
         <v>8.092828798342362</v>
       </c>
-      <c r="E24" s="72">
+      <c r="E25" s="75">
         <v>27.343177009677287</v>
       </c>
-      <c r="F24" s="72">
+      <c r="F25" s="75">
         <v>41.91340785801748</v>
       </c>
-      <c r="G24" s="72">
+      <c r="G25" s="75">
         <v>48.1240140158855</v>
       </c>
-      <c r="H24" s="64" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="58" t="s">
-        <v>202</v>
-      </c>
-      <c r="C25" s="73" t="str">
+      <c r="H25" s="67" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="61" t="s">
+        <v>215</v>
+      </c>
+      <c r="C26" s="76" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="41" t="str">
+      <c r="D26" s="43" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E25" s="73" t="str">
+      <c r="E26" s="76" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="73" t="str">
+      <c r="F26" s="76" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="73" t="str">
+      <c r="G26" s="76" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="64" t="s">
+      <c r="H26" s="67" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="58" t="s">
-        <v>203</v>
-      </c>
-      <c r="C26" s="74">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="C27" s="77">
         <v>-2</v>
       </c>
-      <c r="D26" s="74">
+      <c r="D27" s="77">
         <v>0</v>
       </c>
-      <c r="E26" s="74">
+      <c r="E27" s="77">
         <v>6</v>
       </c>
-      <c r="F26" s="75">
+      <c r="F27" s="78">
         <v>15</v>
       </c>
-      <c r="G26" s="70">
+      <c r="G27" s="73">
         <v>24</v>
       </c>
-      <c r="H26" s="64" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="58" t="s">
-        <v>205</v>
-      </c>
-      <c r="C27" s="74">
+      <c r="H27" s="67" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="C28" s="77">
         <v>0</v>
       </c>
-      <c r="D27" s="74">
+      <c r="D28" s="77">
         <v>2</v>
       </c>
-      <c r="E27" s="70">
+      <c r="E28" s="73">
         <v>190</v>
       </c>
-      <c r="F27" s="70">
+      <c r="F28" s="73">
         <v>443</v>
       </c>
-      <c r="G27" s="70">
+      <c r="G28" s="73">
         <v>724</v>
       </c>
-      <c r="H27" s="64" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="D30" s="77" t="s">
-        <v>213</v>
-      </c>
-      <c r="E30" s="77"/>
-      <c r="F30" s="78" t="s">
-        <v>214</v>
-      </c>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="78"/>
+      <c r="H28" s="67" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="76" t="s">
-        <v>215</v>
-      </c>
-      <c r="C31" s="79" t="s">
-        <v>216</v>
-      </c>
-      <c r="D31" s="77" t="s">
-        <v>217</v>
-      </c>
-      <c r="E31" s="77"/>
-      <c r="F31" s="78" t="s">
-        <v>218</v>
-      </c>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
+      <c r="B31" s="79" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D31" s="80" t="s">
+        <v>226</v>
+      </c>
+      <c r="E31" s="80"/>
+      <c r="F31" s="81" t="s">
+        <v>227</v>
+      </c>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="76" t="s">
-        <v>219</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="D32" s="77" t="s">
-        <v>220</v>
-      </c>
-      <c r="E32" s="77"/>
-      <c r="F32" s="78" t="s">
-        <v>221</v>
-      </c>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
+      <c r="B32" s="79" t="s">
+        <v>228</v>
+      </c>
+      <c r="C32" s="82" t="s">
+        <v>229</v>
+      </c>
+      <c r="D32" s="80" t="s">
+        <v>230</v>
+      </c>
+      <c r="E32" s="80"/>
+      <c r="F32" s="81" t="s">
+        <v>231</v>
+      </c>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="76" t="s">
-        <v>222</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="D33" s="77" t="s">
-        <v>223</v>
-      </c>
-      <c r="E33" s="77"/>
-      <c r="F33" s="78" t="s">
-        <v>224</v>
-      </c>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
+      <c r="B33" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D33" s="80" t="s">
+        <v>233</v>
+      </c>
+      <c r="E33" s="80"/>
+      <c r="F33" s="81" t="s">
+        <v>234</v>
+      </c>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="76" t="s">
+      <c r="B34" s="79" t="s">
+        <v>235</v>
+      </c>
+      <c r="C34" s="43" t="s">
         <v>225</v>
       </c>
-      <c r="C34" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="D34" s="77" t="s">
-        <v>226</v>
-      </c>
-      <c r="E34" s="77"/>
-      <c r="F34" s="78" t="s">
-        <v>227</v>
-      </c>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
+      <c r="D34" s="80" t="s">
+        <v>236</v>
+      </c>
+      <c r="E34" s="80"/>
+      <c r="F34" s="81" t="s">
+        <v>237</v>
+      </c>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="76" t="s">
-        <v>228</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="D35" s="77" t="s">
-        <v>229</v>
-      </c>
-      <c r="E35" s="77"/>
-      <c r="F35" s="78" t="s">
-        <v>230</v>
-      </c>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
-      <c r="I35" s="78"/>
+      <c r="B35" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D35" s="80" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" s="80"/>
+      <c r="F35" s="81" t="s">
+        <v>240</v>
+      </c>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="81"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="76" t="s">
-        <v>231</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="D36" s="77" t="s">
-        <v>232</v>
-      </c>
-      <c r="E36" s="77"/>
-      <c r="F36" s="78" t="s">
-        <v>233</v>
-      </c>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="76" t="s">
+      <c r="B36" s="79" t="s">
+        <v>241</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D36" s="80" t="s">
+        <v>242</v>
+      </c>
+      <c r="E36" s="80"/>
+      <c r="F36" s="81" t="s">
+        <v>243</v>
+      </c>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+    </row>
+    <row r="37" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="79" t="s">
+        <v>244</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D37" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="E37" s="80"/>
+      <c r="F37" s="81" t="s">
+        <v>246</v>
+      </c>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="58" t="s">
-        <v>234</v>
-      </c>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="80" t="s">
-        <v>235</v>
-      </c>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80"/>
+      <c r="C39" s="61" t="s">
+        <v>247</v>
+      </c>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="83" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" s="83"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="83"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
@@ -2640,95 +2710,97 @@
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:I36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B41:I41"/>
   </mergeCells>
-  <conditionalFormatting sqref="C12:G12">
+  <conditionalFormatting sqref="C13:G13">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C12&gt;=0</formula>
+      <formula>C13&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C12&gt;=-1</formula>
+      <formula>C13&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C12&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13:G13">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C13&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C13&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C13&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:G14">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C14&gt;=0.05</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>C14&gt;=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C14&lt;0</formula>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C14&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C14&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C15&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C15&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C15&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&gt;=10000</formula>
+      <formula>C16&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&gt;=7000</formula>
+      <formula>C16&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&lt;7000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:G21">
-    <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C21&lt;=0.55</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C21&lt;=0.65</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C21&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:G22">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C22&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C22&lt;=0.22</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C22&gt;0.22</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23:G23">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C23&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C23&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C23&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C25:G25">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C25&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1.15</formula>
+      <formula>C25&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1.15</formula>
+      <formula>C25&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3082,11 +3154,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3550,9 +3622,154 @@
         <v>1231718</v>
       </c>
     </row>
+    <row r="30" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="30">
+        <v>110000</v>
+      </c>
+      <c r="C31" s="30">
+        <v>110000</v>
+      </c>
+      <c r="D31" s="30">
+        <v>110000</v>
+      </c>
+      <c r="E31" s="30">
+        <v>110000</v>
+      </c>
+      <c r="F31" s="30">
+        <v>110000</v>
+      </c>
+      <c r="G31" s="30">
+        <f>SUM(B31:F31)</f>
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="30">
+        <v>149215</v>
+      </c>
+      <c r="C32" s="30">
+        <v>149215</v>
+      </c>
+      <c r="D32" s="30">
+        <v>149215</v>
+      </c>
+      <c r="E32" s="30">
+        <v>149215</v>
+      </c>
+      <c r="F32" s="30">
+        <v>149215</v>
+      </c>
+      <c r="G32" s="30">
+        <f>SUM(B32:F32)</f>
+        <v>746075</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="30">
+        <v>95000</v>
+      </c>
+      <c r="C33" s="30">
+        <v>120000</v>
+      </c>
+      <c r="D33" s="30">
+        <v>150000</v>
+      </c>
+      <c r="E33" s="30">
+        <v>150000</v>
+      </c>
+      <c r="F33" s="30">
+        <v>150000</v>
+      </c>
+      <c r="G33" s="30">
+        <f>SUM(B33:F33)</f>
+        <v>665000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="30">
+        <v>128868</v>
+      </c>
+      <c r="C34" s="30">
+        <v>162780</v>
+      </c>
+      <c r="D34" s="30">
+        <v>203475</v>
+      </c>
+      <c r="E34" s="30">
+        <v>203475</v>
+      </c>
+      <c r="F34" s="30">
+        <v>203475</v>
+      </c>
+      <c r="G34" s="30">
+        <f>SUM(B34:F34)</f>
+        <v>902073</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="10">
+        <v>-20347</v>
+      </c>
+      <c r="C35" s="10">
+        <v>13565</v>
+      </c>
+      <c r="D35" s="10">
+        <v>54260</v>
+      </c>
+      <c r="E35" s="10">
+        <v>54260</v>
+      </c>
+      <c r="F35" s="10">
+        <v>54260</v>
+      </c>
+      <c r="G35" s="10">
+        <f>SUM(B35:F35)</f>
+        <v>155998</v>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3622,7 +3839,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3632,7 +3849,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B4" s="30">
         <f>700*Assumptions!B23</f>
@@ -3657,7 +3874,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
@@ -3682,7 +3899,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3692,7 +3909,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B7" s="30">
         <f>500*Assumptions!B23</f>
@@ -3717,7 +3934,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
@@ -3742,7 +3959,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3752,7 +3969,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B10" s="30">
         <f>18000*12</f>
@@ -3777,7 +3994,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B11" s="30">
         <f>2500*12</f>
@@ -3802,7 +4019,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B12" s="30">
         <v>18000</v>
@@ -3822,7 +4039,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B13" s="30">
         <f>1500*12</f>
@@ -3847,7 +4064,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B10:B13)</f>
@@ -3872,7 +4089,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -3882,7 +4099,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B16" s="30">
         <v>25000</v>
@@ -3902,7 +4119,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B17" s="30">
         <v>15000</v>
@@ -3922,7 +4139,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B18" s="30">
         <v>20000</v>
@@ -3942,7 +4159,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B19" s="30">
         <f>800*Assumptions!B23</f>
@@ -3967,7 +4184,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B20" s="30">
         <f>600*Assumptions!B23</f>
@@ -3992,7 +4209,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B21" s="31">
         <f>SUM(B16:B20)</f>
@@ -4017,7 +4234,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B23" s="31">
         <f>B5+B8+B14+B21</f>
@@ -4084,7 +4301,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4094,7 +4311,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B3" s="30">
         <v>49824.605221179416</v>
@@ -4114,7 +4331,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B4" s="30">
         <v>75000</v>
@@ -4134,7 +4351,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B5" s="30">
         <v>40000</v>
@@ -4154,7 +4371,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B3:B5)</f>
@@ -4192,11 +4409,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4221,7 +4438,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B2" s="30">
         <f>'Revenue Schedule'!B16</f>
@@ -4246,7 +4463,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B28</f>
@@ -4321,7 +4538,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B6" s="31">
         <f>B3+B4+B5</f>
@@ -4346,7 +4563,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B7" s="31">
         <f>B2-B6</f>
@@ -4371,7 +4588,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B8" s="30">
         <f>B7</f>
@@ -4398,48 +4615,147 @@
       <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="39" t="str">
+      <c r="B9" s="41" t="str">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="41">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>0.0768044580368543</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="41">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>6.146404029836844</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="41">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>14.42367018729028</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="41">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>23.643663059060763</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="40" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="30">
+        <v>149215</v>
+      </c>
+      <c r="C12" s="30">
+        <v>149215</v>
+      </c>
+      <c r="D12" s="30">
+        <v>149215</v>
+      </c>
+      <c r="E12" s="30">
+        <v>149215</v>
+      </c>
+      <c r="F12" s="30">
+        <v>149215</v>
+      </c>
+      <c r="G12" s="30">
+        <f>SUM(B12:F12)</f>
+        <v>746075</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" s="30">
+        <v>128868</v>
+      </c>
+      <c r="C13" s="30">
+        <v>162780</v>
+      </c>
+      <c r="D13" s="30">
+        <v>203475</v>
+      </c>
+      <c r="E13" s="30">
+        <v>203475</v>
+      </c>
+      <c r="F13" s="30">
+        <v>203475</v>
+      </c>
+      <c r="G13" s="30">
+        <f>SUM(B13:F13)</f>
+        <v>902073</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B14" s="10">
+        <v>-20347</v>
+      </c>
+      <c r="C14" s="10">
+        <v>13565</v>
+      </c>
+      <c r="D14" s="10">
+        <v>54260</v>
+      </c>
+      <c r="E14" s="10">
+        <v>54260</v>
+      </c>
+      <c r="F14" s="10">
+        <v>54260</v>
+      </c>
+      <c r="G14" s="10">
+        <f>SUM(B14:F14)</f>
+        <v>155998</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="D10" s="40" t="s">
+      <c r="C16" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E16" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F16" s="42" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:G15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -4462,18 +4778,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="A1" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>157</v>
+      <c r="A2" s="45" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4555,12 +4871,12 @@
         <v>41</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -4615,24 +4931,24 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C18" s="44">
+        <v>173</v>
+      </c>
+      <c r="C18" s="46">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="46">
         <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.5</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="46">
         <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.25</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="46">
         <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0.06666666666666667</v>
       </c>
@@ -4659,7 +4975,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B21" s="30">
         <f>'Financial Model'!B2</f>
@@ -4684,7 +5000,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B22" s="30">
         <f>'Financial Model'!B3</f>
@@ -4734,7 +5050,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B24" s="31">
         <f>'Financial Model'!B6</f>
@@ -4759,32 +5075,32 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="B25" s="45">
+        <v>159</v>
+      </c>
+      <c r="B25" s="47">
         <f>'Financial Model'!B7</f>
         <v>-299256</v>
       </c>
-      <c r="C25" s="46">
+      <c r="C25" s="48">
         <f>'Financial Model'!C7</f>
         <v>313397</v>
       </c>
-      <c r="D25" s="46">
+      <c r="D25" s="48">
         <f>'Financial Model'!D7</f>
         <v>1272538</v>
       </c>
-      <c r="E25" s="46">
+      <c r="E25" s="48">
         <f>'Financial Model'!E7</f>
         <v>2013494</v>
       </c>
-      <c r="F25" s="46">
+      <c r="F25" s="48">
         <f>'Financial Model'!F7</f>
         <v>2327935</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B26" s="30">
         <f>'Financial Model'!B8</f>
@@ -4811,11 +5127,11 @@
       <c r="A27" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="47" t="str">
+      <c r="B27" s="49" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="49">
         <f>'Financial Model'!C9</f>
         <v>0.0768044580368543</v>
       </c>
@@ -4834,7 +5150,7 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4844,7 +5160,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B30" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
@@ -4869,59 +5185,59 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B31" s="44">
+        <v>176</v>
+      </c>
+      <c r="B31" s="46">
         <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
         <v>0.6639269081500647</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="46">
         <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
         <v>0.4882345013477089</v>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="46">
         <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
         <v>0.3254552660783174</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="46">
         <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
         <v>0.25881186142410634</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="46">
         <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
         <v>0.23758159092662604</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B32" s="44">
+        <v>177</v>
+      </c>
+      <c r="B32" s="46">
         <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
         <v>0.4230271668822768</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="46">
         <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
         <v>0.35193435864912004</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="46">
         <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
         <v>0.31456930719230564</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="46">
         <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
         <v>0.3023849972421401</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="46">
         <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
         <v>0.299923231232158</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="B33" s="48">
+        <v>178</v>
+      </c>
+      <c r="B33" s="50">
         <f>IF(B21=0,0,B25/B21)</f>
         <v>-0.1935679172056921</v>
       </c>
@@ -4944,7 +5260,7 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -4954,61 +5270,61 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="B36" s="44">
+        <v>180</v>
+      </c>
+      <c r="B36" s="46">
         <v>0.02328589909443726</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="46">
         <v>0.024496591089265895</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="46">
         <v>0.025207419542355863</v>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="46">
         <v>0.025845087069576864</v>
       </c>
-      <c r="F36" s="44">
+      <c r="F36" s="46">
         <v>0.026078234704112337</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="B37" s="44">
+        <v>181</v>
+      </c>
+      <c r="B37" s="46">
         <v>0.8926261319534282</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="46">
         <v>0.9299191374663073</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="46">
         <v>0.9483697088199545</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="46">
         <v>0.9615475533842881</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="46">
         <v>0.9604197207005633</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="B38" s="44">
+        <v>182</v>
+      </c>
+      <c r="B38" s="46">
         <v>0.08408796895213454</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="46">
         <v>0.045584271444426824</v>
       </c>
-      <c r="D38" s="44">
+      <c r="D38" s="46">
         <v>0.026422871637689586</v>
       </c>
-      <c r="E38" s="44">
+      <c r="E38" s="46">
         <v>0.012607359546135056</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="46">
         <v>0.013502044595324435</v>
       </c>
     </row>
@@ -5056,26 +5372,26 @@
       <c r="H1" s="18"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
+      <c r="B4" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">
